--- a/Src/Map/MapData/Map.xlsx
+++ b/Src/Map/MapData/Map.xlsx
@@ -5,16 +5,17 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6b26349b9cd3e987/デスクトップ/かるてとまｐｐ/mapppppteram/MapData/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ゲーム開発1\TeamDevlop\Src\Map\MapData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="138" documentId="8_{78683FD6-1476-4398-A77F-E00F0EC73D5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{84E0E454-91A4-4344-9D47-F0C97B4DEE07}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B32B6396-4751-445E-81D6-3BCA34749958}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6525" yWindow="1230" windowWidth="21600" windowHeight="11295" xr2:uid="{53B5AEAB-04AE-4965-81BC-49E785C84905}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{53B5AEAB-04AE-4965-81BC-49E785C84905}"/>
   </bookViews>
   <sheets>
-    <sheet name="Stage1" sheetId="1" r:id="rId1"/>
-    <sheet name="Stage2" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="3" r:id="rId1"/>
+    <sheet name="Stage1" sheetId="1" r:id="rId2"/>
+    <sheet name="Stage2" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,9 +40,13 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -57,13 +62,40 @@
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE97132"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -80,8 +112,20 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -106,14 +150,14 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FF00B050"/>
+          <bgColor theme="5"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="5"/>
+          <bgColor theme="9"/>
         </patternFill>
       </fill>
     </dxf>
@@ -446,1197 +490,2349 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF26DA9C-D84B-469D-BB4C-3116DB6599CB}">
-  <dimension ref="A1:AF12"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4282726-38FC-445F-8486-AD0C629F4764}">
+  <dimension ref="A1:BL12"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="32" width="3.875" customWidth="1"/>
+    <col min="1" max="81" width="3.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" x14ac:dyDescent="0.4">
-      <c r="A1">
-        <v>0</v>
-      </c>
-      <c r="B1">
-        <v>0</v>
-      </c>
-      <c r="C1">
-        <v>0</v>
-      </c>
-      <c r="D1">
-        <v>0</v>
-      </c>
-      <c r="E1">
-        <v>0</v>
-      </c>
-      <c r="F1">
-        <v>0</v>
-      </c>
-      <c r="G1">
-        <v>0</v>
-      </c>
-      <c r="H1">
-        <v>0</v>
-      </c>
-      <c r="I1">
-        <v>0</v>
-      </c>
-      <c r="J1">
-        <v>0</v>
-      </c>
-      <c r="K1">
-        <v>0</v>
-      </c>
-      <c r="L1">
-        <v>0</v>
-      </c>
-      <c r="M1">
-        <v>0</v>
-      </c>
-      <c r="N1">
-        <v>0</v>
-      </c>
-      <c r="O1">
-        <v>0</v>
-      </c>
-      <c r="P1">
-        <v>0</v>
-      </c>
-      <c r="Q1">
-        <v>0</v>
-      </c>
-      <c r="R1">
-        <v>0</v>
-      </c>
-      <c r="S1">
-        <v>0</v>
-      </c>
-      <c r="T1">
-        <v>0</v>
-      </c>
-      <c r="U1">
-        <v>0</v>
-      </c>
-      <c r="V1">
-        <v>0</v>
-      </c>
-      <c r="W1">
-        <v>0</v>
-      </c>
-      <c r="X1">
-        <v>0</v>
-      </c>
-      <c r="Y1">
-        <v>0</v>
-      </c>
-      <c r="Z1">
-        <v>0</v>
-      </c>
-      <c r="AA1">
-        <v>0</v>
-      </c>
-      <c r="AB1">
-        <v>0</v>
-      </c>
-      <c r="AC1">
-        <v>0</v>
-      </c>
-      <c r="AD1">
-        <v>0</v>
-      </c>
-      <c r="AE1">
-        <v>0</v>
-      </c>
-      <c r="AF1">
+    <row r="1" spans="1:64">
+      <c r="A1" s="1">
+        <v>2</v>
+      </c>
+      <c r="B1" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1">
+        <v>0</v>
+      </c>
+      <c r="D1" s="1">
+        <v>0</v>
+      </c>
+      <c r="E1" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1" s="1">
+        <v>0</v>
+      </c>
+      <c r="G1" s="1">
+        <v>0</v>
+      </c>
+      <c r="H1" s="1">
+        <v>0</v>
+      </c>
+      <c r="I1" s="1">
+        <v>0</v>
+      </c>
+      <c r="J1" s="1">
+        <v>0</v>
+      </c>
+      <c r="K1" s="1">
+        <v>0</v>
+      </c>
+      <c r="L1" s="1">
+        <v>0</v>
+      </c>
+      <c r="M1" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1" s="1">
+        <v>0</v>
+      </c>
+      <c r="P1" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1" s="1">
+        <v>0</v>
+      </c>
+      <c r="S1" s="1">
+        <v>0</v>
+      </c>
+      <c r="T1" s="1">
+        <v>0</v>
+      </c>
+      <c r="U1" s="1">
+        <v>0</v>
+      </c>
+      <c r="V1" s="1">
+        <v>0</v>
+      </c>
+      <c r="W1" s="1">
+        <v>0</v>
+      </c>
+      <c r="X1" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y1" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z1" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA1" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB1" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC1" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD1" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE1" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF1" s="1">
+        <v>2</v>
+      </c>
+      <c r="AG1" s="1">
+        <v>0</v>
+      </c>
+      <c r="AH1" s="1">
+        <v>0</v>
+      </c>
+      <c r="AI1" s="1">
+        <v>0</v>
+      </c>
+      <c r="AJ1" s="1">
+        <v>0</v>
+      </c>
+      <c r="AK1" s="1">
+        <v>0</v>
+      </c>
+      <c r="AL1" s="1">
+        <v>0</v>
+      </c>
+      <c r="AM1" s="1">
+        <v>0</v>
+      </c>
+      <c r="AN1" s="1">
+        <v>0</v>
+      </c>
+      <c r="AO1" s="1">
+        <v>0</v>
+      </c>
+      <c r="AP1" s="1">
+        <v>0</v>
+      </c>
+      <c r="AQ1" s="1">
+        <v>0</v>
+      </c>
+      <c r="AR1" s="1">
+        <v>0</v>
+      </c>
+      <c r="AS1" s="1">
+        <v>0</v>
+      </c>
+      <c r="AT1" s="1">
+        <v>0</v>
+      </c>
+      <c r="AU1" s="1">
+        <v>0</v>
+      </c>
+      <c r="AV1" s="1">
+        <v>0</v>
+      </c>
+      <c r="AW1" s="1">
+        <v>0</v>
+      </c>
+      <c r="AX1" s="1">
+        <v>0</v>
+      </c>
+      <c r="AY1" s="1">
+        <v>0</v>
+      </c>
+      <c r="AZ1" s="1">
+        <v>0</v>
+      </c>
+      <c r="BA1" s="1">
+        <v>0</v>
+      </c>
+      <c r="BB1" s="1">
+        <v>0</v>
+      </c>
+      <c r="BC1" s="1">
+        <v>0</v>
+      </c>
+      <c r="BD1" s="1">
+        <v>0</v>
+      </c>
+      <c r="BE1" s="1">
+        <v>0</v>
+      </c>
+      <c r="BF1" s="1">
+        <v>0</v>
+      </c>
+      <c r="BG1" s="1">
+        <v>0</v>
+      </c>
+      <c r="BH1" s="1">
+        <v>0</v>
+      </c>
+      <c r="BI1" s="1">
+        <v>0</v>
+      </c>
+      <c r="BJ1" s="1">
+        <v>0</v>
+      </c>
+      <c r="BK1" s="1">
+        <v>0</v>
+      </c>
+      <c r="BL1" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.4">
-      <c r="A2">
-        <v>0</v>
-      </c>
-      <c r="B2">
-        <v>0</v>
-      </c>
-      <c r="C2">
-        <v>0</v>
-      </c>
-      <c r="D2">
-        <v>0</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
-      <c r="H2">
-        <v>0</v>
-      </c>
-      <c r="I2">
-        <v>0</v>
-      </c>
-      <c r="J2">
-        <v>0</v>
-      </c>
-      <c r="K2">
-        <v>0</v>
-      </c>
-      <c r="L2">
-        <v>0</v>
-      </c>
-      <c r="M2">
-        <v>0</v>
-      </c>
-      <c r="N2">
-        <v>0</v>
-      </c>
-      <c r="O2">
-        <v>0</v>
-      </c>
-      <c r="P2">
-        <v>0</v>
-      </c>
-      <c r="Q2">
-        <v>0</v>
-      </c>
-      <c r="R2">
-        <v>0</v>
-      </c>
-      <c r="S2">
-        <v>0</v>
-      </c>
-      <c r="T2">
-        <v>0</v>
-      </c>
-      <c r="U2">
-        <v>0</v>
-      </c>
-      <c r="V2">
-        <v>0</v>
-      </c>
-      <c r="W2">
-        <v>0</v>
-      </c>
-      <c r="X2">
-        <v>0</v>
-      </c>
-      <c r="Y2">
-        <v>0</v>
-      </c>
-      <c r="Z2">
-        <v>0</v>
-      </c>
-      <c r="AA2">
-        <v>0</v>
-      </c>
-      <c r="AB2">
-        <v>0</v>
-      </c>
-      <c r="AC2">
-        <v>0</v>
-      </c>
-      <c r="AD2">
-        <v>0</v>
-      </c>
-      <c r="AE2">
-        <v>0</v>
-      </c>
-      <c r="AF2">
+    <row r="2" spans="1:64">
+      <c r="A2" s="1">
+        <v>2</v>
+      </c>
+      <c r="B2" s="1">
+        <v>0</v>
+      </c>
+      <c r="C2" s="1">
+        <v>0</v>
+      </c>
+      <c r="D2" s="1">
+        <v>0</v>
+      </c>
+      <c r="E2" s="1">
+        <v>0</v>
+      </c>
+      <c r="F2" s="1">
+        <v>0</v>
+      </c>
+      <c r="G2" s="1">
+        <v>0</v>
+      </c>
+      <c r="H2" s="1">
+        <v>0</v>
+      </c>
+      <c r="I2" s="1">
+        <v>0</v>
+      </c>
+      <c r="J2" s="1">
+        <v>0</v>
+      </c>
+      <c r="K2" s="1">
+        <v>0</v>
+      </c>
+      <c r="L2" s="1">
+        <v>0</v>
+      </c>
+      <c r="M2" s="1">
+        <v>0</v>
+      </c>
+      <c r="N2" s="1">
+        <v>0</v>
+      </c>
+      <c r="O2" s="1">
+        <v>0</v>
+      </c>
+      <c r="P2" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="1">
+        <v>0</v>
+      </c>
+      <c r="R2" s="1">
+        <v>0</v>
+      </c>
+      <c r="S2" s="1">
+        <v>0</v>
+      </c>
+      <c r="T2" s="1">
+        <v>0</v>
+      </c>
+      <c r="U2" s="1">
+        <v>0</v>
+      </c>
+      <c r="V2" s="1">
+        <v>0</v>
+      </c>
+      <c r="W2" s="1">
+        <v>0</v>
+      </c>
+      <c r="X2" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y2" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z2" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA2" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB2" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC2" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD2" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE2" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF2" s="1">
+        <v>2</v>
+      </c>
+      <c r="AG2" s="1">
+        <v>0</v>
+      </c>
+      <c r="AH2" s="1">
+        <v>0</v>
+      </c>
+      <c r="AI2" s="1">
+        <v>0</v>
+      </c>
+      <c r="AJ2" s="1">
+        <v>0</v>
+      </c>
+      <c r="AK2" s="1">
+        <v>0</v>
+      </c>
+      <c r="AL2" s="1">
+        <v>0</v>
+      </c>
+      <c r="AM2" s="1">
+        <v>0</v>
+      </c>
+      <c r="AN2" s="1">
+        <v>0</v>
+      </c>
+      <c r="AO2" s="1">
+        <v>0</v>
+      </c>
+      <c r="AP2" s="1">
+        <v>0</v>
+      </c>
+      <c r="AQ2" s="1">
+        <v>0</v>
+      </c>
+      <c r="AR2" s="1">
+        <v>0</v>
+      </c>
+      <c r="AS2" s="1">
+        <v>0</v>
+      </c>
+      <c r="AT2" s="1">
+        <v>0</v>
+      </c>
+      <c r="AU2" s="1">
+        <v>0</v>
+      </c>
+      <c r="AV2" s="1">
+        <v>0</v>
+      </c>
+      <c r="AW2" s="1">
+        <v>0</v>
+      </c>
+      <c r="AX2" s="1">
+        <v>0</v>
+      </c>
+      <c r="AY2" s="1">
+        <v>0</v>
+      </c>
+      <c r="AZ2" s="1">
+        <v>0</v>
+      </c>
+      <c r="BA2" s="1">
+        <v>0</v>
+      </c>
+      <c r="BB2" s="1">
+        <v>0</v>
+      </c>
+      <c r="BC2" s="1">
+        <v>0</v>
+      </c>
+      <c r="BD2" s="1">
+        <v>0</v>
+      </c>
+      <c r="BE2" s="1">
+        <v>0</v>
+      </c>
+      <c r="BF2" s="1">
+        <v>0</v>
+      </c>
+      <c r="BG2" s="1">
+        <v>0</v>
+      </c>
+      <c r="BH2" s="1">
+        <v>0</v>
+      </c>
+      <c r="BI2" s="1">
+        <v>0</v>
+      </c>
+      <c r="BJ2" s="1">
+        <v>0</v>
+      </c>
+      <c r="BK2" s="1">
+        <v>0</v>
+      </c>
+      <c r="BL2" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.4">
-      <c r="A3">
-        <v>0</v>
-      </c>
-      <c r="B3">
-        <v>0</v>
-      </c>
-      <c r="C3">
-        <v>0</v>
-      </c>
-      <c r="D3">
-        <v>0</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-      <c r="I3">
-        <v>0</v>
-      </c>
-      <c r="J3">
-        <v>0</v>
-      </c>
-      <c r="K3">
-        <v>0</v>
-      </c>
-      <c r="L3">
-        <v>0</v>
-      </c>
-      <c r="M3">
-        <v>0</v>
-      </c>
-      <c r="N3">
-        <v>0</v>
-      </c>
-      <c r="O3">
-        <v>0</v>
-      </c>
-      <c r="P3">
-        <v>0</v>
-      </c>
-      <c r="Q3">
-        <v>0</v>
-      </c>
-      <c r="R3">
-        <v>0</v>
-      </c>
-      <c r="S3">
-        <v>0</v>
-      </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
-      <c r="U3">
-        <v>0</v>
-      </c>
-      <c r="V3">
-        <v>0</v>
-      </c>
-      <c r="W3">
-        <v>0</v>
-      </c>
-      <c r="X3">
-        <v>0</v>
-      </c>
-      <c r="Y3">
-        <v>0</v>
-      </c>
-      <c r="Z3">
-        <v>0</v>
-      </c>
-      <c r="AA3">
-        <v>0</v>
-      </c>
-      <c r="AB3">
-        <v>0</v>
-      </c>
-      <c r="AC3">
-        <v>0</v>
-      </c>
-      <c r="AD3">
-        <v>0</v>
-      </c>
-      <c r="AE3">
-        <v>0</v>
-      </c>
-      <c r="AF3">
+    <row r="3" spans="1:64">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1">
+        <v>0</v>
+      </c>
+      <c r="C3" s="1">
+        <v>0</v>
+      </c>
+      <c r="D3" s="1">
+        <v>0</v>
+      </c>
+      <c r="E3" s="1">
+        <v>0</v>
+      </c>
+      <c r="F3" s="1">
+        <v>0</v>
+      </c>
+      <c r="G3" s="1">
+        <v>0</v>
+      </c>
+      <c r="H3" s="1">
+        <v>0</v>
+      </c>
+      <c r="I3" s="1">
+        <v>0</v>
+      </c>
+      <c r="J3" s="1">
+        <v>0</v>
+      </c>
+      <c r="K3" s="1">
+        <v>0</v>
+      </c>
+      <c r="L3" s="1">
+        <v>0</v>
+      </c>
+      <c r="M3" s="1">
+        <v>0</v>
+      </c>
+      <c r="N3" s="1">
+        <v>0</v>
+      </c>
+      <c r="O3" s="1">
+        <v>0</v>
+      </c>
+      <c r="P3" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="1">
+        <v>0</v>
+      </c>
+      <c r="R3" s="1">
+        <v>0</v>
+      </c>
+      <c r="S3" s="1">
+        <v>0</v>
+      </c>
+      <c r="T3" s="1">
+        <v>0</v>
+      </c>
+      <c r="U3" s="1">
+        <v>0</v>
+      </c>
+      <c r="V3" s="1">
+        <v>0</v>
+      </c>
+      <c r="W3" s="1">
+        <v>0</v>
+      </c>
+      <c r="X3" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y3" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z3" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA3" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB3" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC3" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD3" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE3" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF3" s="1">
+        <v>2</v>
+      </c>
+      <c r="AG3" s="1">
+        <v>0</v>
+      </c>
+      <c r="AH3" s="1">
+        <v>0</v>
+      </c>
+      <c r="AI3" s="1">
+        <v>0</v>
+      </c>
+      <c r="AJ3" s="1">
+        <v>0</v>
+      </c>
+      <c r="AK3" s="1">
+        <v>0</v>
+      </c>
+      <c r="AL3" s="1">
+        <v>0</v>
+      </c>
+      <c r="AM3" s="1">
+        <v>0</v>
+      </c>
+      <c r="AN3" s="1">
+        <v>0</v>
+      </c>
+      <c r="AO3" s="1">
+        <v>0</v>
+      </c>
+      <c r="AP3" s="1">
+        <v>0</v>
+      </c>
+      <c r="AQ3" s="1">
+        <v>0</v>
+      </c>
+      <c r="AR3" s="1">
+        <v>0</v>
+      </c>
+      <c r="AS3" s="1">
+        <v>0</v>
+      </c>
+      <c r="AT3" s="1">
+        <v>0</v>
+      </c>
+      <c r="AU3" s="1">
+        <v>0</v>
+      </c>
+      <c r="AV3" s="1">
+        <v>0</v>
+      </c>
+      <c r="AW3" s="1">
+        <v>0</v>
+      </c>
+      <c r="AX3" s="1">
+        <v>0</v>
+      </c>
+      <c r="AY3" s="1">
+        <v>0</v>
+      </c>
+      <c r="AZ3" s="1">
+        <v>0</v>
+      </c>
+      <c r="BA3" s="1">
+        <v>0</v>
+      </c>
+      <c r="BB3" s="1">
+        <v>0</v>
+      </c>
+      <c r="BC3" s="1">
+        <v>0</v>
+      </c>
+      <c r="BD3" s="1">
+        <v>0</v>
+      </c>
+      <c r="BE3" s="1">
+        <v>0</v>
+      </c>
+      <c r="BF3" s="1">
+        <v>0</v>
+      </c>
+      <c r="BG3" s="1">
+        <v>0</v>
+      </c>
+      <c r="BH3" s="1">
+        <v>0</v>
+      </c>
+      <c r="BI3" s="1">
+        <v>0</v>
+      </c>
+      <c r="BJ3" s="1">
+        <v>0</v>
+      </c>
+      <c r="BK3" s="1">
+        <v>0</v>
+      </c>
+      <c r="BL3" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.4">
-      <c r="A4">
-        <v>0</v>
-      </c>
-      <c r="B4">
-        <v>0</v>
-      </c>
-      <c r="C4">
-        <v>0</v>
-      </c>
-      <c r="D4">
-        <v>0</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4">
-        <v>0</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4">
-        <v>0</v>
-      </c>
-      <c r="L4">
-        <v>0</v>
-      </c>
-      <c r="M4">
-        <v>0</v>
-      </c>
-      <c r="N4">
-        <v>0</v>
-      </c>
-      <c r="O4">
-        <v>0</v>
-      </c>
-      <c r="P4">
-        <v>0</v>
-      </c>
-      <c r="Q4">
-        <v>0</v>
-      </c>
-      <c r="R4">
-        <v>0</v>
-      </c>
-      <c r="S4">
-        <v>0</v>
-      </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
-      <c r="U4">
-        <v>0</v>
-      </c>
-      <c r="V4">
-        <v>0</v>
-      </c>
-      <c r="W4">
-        <v>0</v>
-      </c>
-      <c r="X4">
-        <v>0</v>
-      </c>
-      <c r="Y4">
-        <v>0</v>
-      </c>
-      <c r="Z4">
-        <v>0</v>
-      </c>
-      <c r="AA4">
-        <v>0</v>
-      </c>
-      <c r="AB4">
-        <v>0</v>
-      </c>
-      <c r="AC4">
-        <v>0</v>
-      </c>
-      <c r="AD4">
-        <v>0</v>
-      </c>
-      <c r="AE4">
-        <v>0</v>
-      </c>
-      <c r="AF4">
+    <row r="4" spans="1:64">
+      <c r="A4" s="1">
+        <v>2</v>
+      </c>
+      <c r="B4" s="1">
+        <v>0</v>
+      </c>
+      <c r="C4" s="1">
+        <v>0</v>
+      </c>
+      <c r="D4" s="1">
+        <v>0</v>
+      </c>
+      <c r="E4" s="1">
+        <v>0</v>
+      </c>
+      <c r="F4" s="1">
+        <v>0</v>
+      </c>
+      <c r="G4" s="1">
+        <v>0</v>
+      </c>
+      <c r="H4" s="1">
+        <v>0</v>
+      </c>
+      <c r="I4" s="1">
+        <v>0</v>
+      </c>
+      <c r="J4" s="1">
+        <v>0</v>
+      </c>
+      <c r="K4" s="1">
+        <v>0</v>
+      </c>
+      <c r="L4" s="1">
+        <v>0</v>
+      </c>
+      <c r="M4" s="1">
+        <v>0</v>
+      </c>
+      <c r="N4" s="1">
+        <v>0</v>
+      </c>
+      <c r="O4" s="1">
+        <v>0</v>
+      </c>
+      <c r="P4" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="1">
+        <v>0</v>
+      </c>
+      <c r="R4" s="1">
+        <v>0</v>
+      </c>
+      <c r="S4" s="1">
+        <v>0</v>
+      </c>
+      <c r="T4" s="1">
+        <v>0</v>
+      </c>
+      <c r="U4" s="1">
+        <v>0</v>
+      </c>
+      <c r="V4" s="1">
+        <v>0</v>
+      </c>
+      <c r="W4" s="1">
+        <v>0</v>
+      </c>
+      <c r="X4" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z4" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA4" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB4" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC4" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD4" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE4" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF4" s="1">
+        <v>2</v>
+      </c>
+      <c r="AG4" s="1">
+        <v>0</v>
+      </c>
+      <c r="AH4" s="1">
+        <v>0</v>
+      </c>
+      <c r="AI4" s="1">
+        <v>0</v>
+      </c>
+      <c r="AJ4" s="1">
+        <v>0</v>
+      </c>
+      <c r="AK4" s="1">
+        <v>0</v>
+      </c>
+      <c r="AL4" s="1">
+        <v>0</v>
+      </c>
+      <c r="AM4" s="1">
+        <v>0</v>
+      </c>
+      <c r="AN4" s="1">
+        <v>0</v>
+      </c>
+      <c r="AO4" s="1">
+        <v>0</v>
+      </c>
+      <c r="AP4" s="1">
+        <v>0</v>
+      </c>
+      <c r="AQ4" s="1">
+        <v>0</v>
+      </c>
+      <c r="AR4" s="1">
+        <v>0</v>
+      </c>
+      <c r="AS4" s="1">
+        <v>0</v>
+      </c>
+      <c r="AT4" s="1">
+        <v>0</v>
+      </c>
+      <c r="AU4" s="1">
+        <v>0</v>
+      </c>
+      <c r="AV4" s="1">
+        <v>0</v>
+      </c>
+      <c r="AW4" s="1">
+        <v>0</v>
+      </c>
+      <c r="AX4" s="1">
+        <v>0</v>
+      </c>
+      <c r="AY4" s="1">
+        <v>0</v>
+      </c>
+      <c r="AZ4" s="1">
+        <v>0</v>
+      </c>
+      <c r="BA4" s="1">
+        <v>0</v>
+      </c>
+      <c r="BB4" s="1">
+        <v>0</v>
+      </c>
+      <c r="BC4" s="1">
+        <v>0</v>
+      </c>
+      <c r="BD4" s="1">
+        <v>0</v>
+      </c>
+      <c r="BE4" s="1">
+        <v>0</v>
+      </c>
+      <c r="BF4" s="1">
+        <v>0</v>
+      </c>
+      <c r="BG4" s="1">
+        <v>0</v>
+      </c>
+      <c r="BH4" s="1">
+        <v>0</v>
+      </c>
+      <c r="BI4" s="1">
+        <v>0</v>
+      </c>
+      <c r="BJ4" s="1">
+        <v>0</v>
+      </c>
+      <c r="BK4" s="1">
+        <v>0</v>
+      </c>
+      <c r="BL4" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.4">
-      <c r="A5">
-        <v>0</v>
-      </c>
-      <c r="B5">
-        <v>0</v>
-      </c>
-      <c r="C5">
-        <v>0</v>
-      </c>
-      <c r="D5">
-        <v>0</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5">
-        <v>0</v>
-      </c>
-      <c r="L5">
-        <v>0</v>
-      </c>
-      <c r="M5">
-        <v>0</v>
-      </c>
-      <c r="N5">
-        <v>0</v>
-      </c>
-      <c r="O5">
-        <v>0</v>
-      </c>
-      <c r="P5">
-        <v>0</v>
-      </c>
-      <c r="Q5">
-        <v>0</v>
-      </c>
-      <c r="R5">
-        <v>0</v>
-      </c>
-      <c r="S5">
-        <v>0</v>
-      </c>
-      <c r="T5">
-        <v>0</v>
-      </c>
-      <c r="U5">
-        <v>0</v>
-      </c>
-      <c r="V5">
-        <v>0</v>
-      </c>
-      <c r="W5">
-        <v>0</v>
-      </c>
-      <c r="X5">
-        <v>0</v>
-      </c>
-      <c r="Y5">
-        <v>0</v>
-      </c>
-      <c r="Z5">
-        <v>0</v>
-      </c>
-      <c r="AA5">
-        <v>0</v>
-      </c>
-      <c r="AB5">
-        <v>0</v>
-      </c>
-      <c r="AC5">
-        <v>0</v>
-      </c>
-      <c r="AD5">
-        <v>0</v>
-      </c>
-      <c r="AE5">
-        <v>0</v>
-      </c>
-      <c r="AF5">
+    <row r="5" spans="1:64">
+      <c r="A5" s="1">
+        <v>2</v>
+      </c>
+      <c r="B5" s="1">
+        <v>0</v>
+      </c>
+      <c r="C5" s="1">
+        <v>0</v>
+      </c>
+      <c r="D5" s="1">
+        <v>0</v>
+      </c>
+      <c r="E5" s="1">
+        <v>0</v>
+      </c>
+      <c r="F5" s="1">
+        <v>0</v>
+      </c>
+      <c r="G5" s="1">
+        <v>0</v>
+      </c>
+      <c r="H5" s="1">
+        <v>0</v>
+      </c>
+      <c r="I5" s="1">
+        <v>0</v>
+      </c>
+      <c r="J5" s="1">
+        <v>0</v>
+      </c>
+      <c r="K5" s="1">
+        <v>0</v>
+      </c>
+      <c r="L5" s="1">
+        <v>0</v>
+      </c>
+      <c r="M5" s="1">
+        <v>0</v>
+      </c>
+      <c r="N5" s="1">
+        <v>0</v>
+      </c>
+      <c r="O5" s="1">
+        <v>0</v>
+      </c>
+      <c r="P5" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="1">
+        <v>0</v>
+      </c>
+      <c r="R5" s="1">
+        <v>0</v>
+      </c>
+      <c r="S5" s="1">
+        <v>0</v>
+      </c>
+      <c r="T5" s="1">
+        <v>0</v>
+      </c>
+      <c r="U5" s="1">
+        <v>0</v>
+      </c>
+      <c r="V5" s="1">
+        <v>0</v>
+      </c>
+      <c r="W5" s="1">
+        <v>0</v>
+      </c>
+      <c r="X5" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y5" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z5" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA5" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB5" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC5" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD5" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE5" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF5" s="1">
+        <v>2</v>
+      </c>
+      <c r="AG5" s="1">
+        <v>0</v>
+      </c>
+      <c r="AH5" s="1">
+        <v>0</v>
+      </c>
+      <c r="AI5" s="1">
+        <v>0</v>
+      </c>
+      <c r="AJ5" s="1">
+        <v>0</v>
+      </c>
+      <c r="AK5" s="1">
+        <v>0</v>
+      </c>
+      <c r="AL5" s="1">
+        <v>0</v>
+      </c>
+      <c r="AM5" s="1">
+        <v>0</v>
+      </c>
+      <c r="AN5" s="1">
+        <v>0</v>
+      </c>
+      <c r="AO5" s="1">
+        <v>0</v>
+      </c>
+      <c r="AP5" s="1">
+        <v>0</v>
+      </c>
+      <c r="AQ5" s="1">
+        <v>0</v>
+      </c>
+      <c r="AR5" s="1">
+        <v>0</v>
+      </c>
+      <c r="AS5" s="1">
+        <v>0</v>
+      </c>
+      <c r="AT5" s="1">
+        <v>0</v>
+      </c>
+      <c r="AU5" s="1">
+        <v>0</v>
+      </c>
+      <c r="AV5" s="1">
+        <v>0</v>
+      </c>
+      <c r="AW5" s="1">
+        <v>0</v>
+      </c>
+      <c r="AX5" s="1">
+        <v>0</v>
+      </c>
+      <c r="AY5" s="1">
+        <v>0</v>
+      </c>
+      <c r="AZ5" s="1">
+        <v>0</v>
+      </c>
+      <c r="BA5" s="1">
+        <v>0</v>
+      </c>
+      <c r="BB5" s="1">
+        <v>0</v>
+      </c>
+      <c r="BC5" s="1">
+        <v>0</v>
+      </c>
+      <c r="BD5" s="1">
+        <v>0</v>
+      </c>
+      <c r="BE5" s="1">
+        <v>0</v>
+      </c>
+      <c r="BF5" s="1">
+        <v>0</v>
+      </c>
+      <c r="BG5" s="1">
+        <v>0</v>
+      </c>
+      <c r="BH5" s="1">
+        <v>0</v>
+      </c>
+      <c r="BI5" s="1">
+        <v>0</v>
+      </c>
+      <c r="BJ5" s="1">
+        <v>0</v>
+      </c>
+      <c r="BK5" s="1">
+        <v>0</v>
+      </c>
+      <c r="BL5" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.4">
-      <c r="A6">
-        <v>0</v>
-      </c>
-      <c r="B6">
-        <v>2</v>
-      </c>
-      <c r="C6">
-        <v>2</v>
-      </c>
-      <c r="D6">
-        <v>2</v>
-      </c>
-      <c r="E6">
-        <v>2</v>
-      </c>
-      <c r="F6">
-        <v>2</v>
-      </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
-      <c r="I6">
-        <v>0</v>
-      </c>
-      <c r="J6">
-        <v>0</v>
-      </c>
-      <c r="K6">
-        <v>0</v>
-      </c>
-      <c r="L6">
-        <v>0</v>
-      </c>
-      <c r="M6">
-        <v>0</v>
-      </c>
-      <c r="N6">
-        <v>0</v>
-      </c>
-      <c r="O6">
-        <v>0</v>
-      </c>
-      <c r="P6">
-        <v>0</v>
-      </c>
-      <c r="Q6">
-        <v>0</v>
-      </c>
-      <c r="R6">
-        <v>0</v>
-      </c>
-      <c r="S6">
-        <v>0</v>
-      </c>
-      <c r="T6">
-        <v>0</v>
-      </c>
-      <c r="U6">
-        <v>0</v>
-      </c>
-      <c r="V6">
-        <v>0</v>
-      </c>
-      <c r="W6">
-        <v>0</v>
-      </c>
-      <c r="X6">
-        <v>0</v>
-      </c>
-      <c r="Y6">
-        <v>0</v>
-      </c>
-      <c r="Z6">
-        <v>0</v>
-      </c>
-      <c r="AA6">
-        <v>0</v>
-      </c>
-      <c r="AB6">
-        <v>0</v>
-      </c>
-      <c r="AC6">
-        <v>0</v>
-      </c>
-      <c r="AD6">
-        <v>0</v>
-      </c>
-      <c r="AE6">
-        <v>0</v>
-      </c>
-      <c r="AF6">
+    <row r="6" spans="1:64">
+      <c r="A6" s="1">
+        <v>2</v>
+      </c>
+      <c r="B6" s="1">
+        <v>0</v>
+      </c>
+      <c r="C6" s="1">
+        <v>0</v>
+      </c>
+      <c r="D6" s="1">
+        <v>0</v>
+      </c>
+      <c r="E6" s="1">
+        <v>0</v>
+      </c>
+      <c r="F6" s="1">
+        <v>0</v>
+      </c>
+      <c r="G6" s="1">
+        <v>0</v>
+      </c>
+      <c r="H6" s="1">
+        <v>0</v>
+      </c>
+      <c r="I6" s="1">
+        <v>0</v>
+      </c>
+      <c r="J6" s="1">
+        <v>0</v>
+      </c>
+      <c r="K6" s="1">
+        <v>0</v>
+      </c>
+      <c r="L6" s="1">
+        <v>0</v>
+      </c>
+      <c r="M6" s="1">
+        <v>0</v>
+      </c>
+      <c r="N6" s="1">
+        <v>0</v>
+      </c>
+      <c r="O6" s="1">
+        <v>0</v>
+      </c>
+      <c r="P6" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="1">
+        <v>0</v>
+      </c>
+      <c r="R6" s="1">
+        <v>0</v>
+      </c>
+      <c r="S6" s="1">
+        <v>0</v>
+      </c>
+      <c r="T6" s="1">
+        <v>0</v>
+      </c>
+      <c r="U6" s="1">
+        <v>0</v>
+      </c>
+      <c r="V6" s="1">
+        <v>0</v>
+      </c>
+      <c r="W6" s="1">
+        <v>0</v>
+      </c>
+      <c r="X6" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z6" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB6" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC6" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD6" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE6" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF6" s="1">
+        <v>2</v>
+      </c>
+      <c r="AG6" s="1">
+        <v>0</v>
+      </c>
+      <c r="AH6" s="1">
+        <v>0</v>
+      </c>
+      <c r="AI6" s="1">
+        <v>0</v>
+      </c>
+      <c r="AJ6" s="1">
+        <v>0</v>
+      </c>
+      <c r="AK6" s="1">
+        <v>0</v>
+      </c>
+      <c r="AL6" s="1">
+        <v>0</v>
+      </c>
+      <c r="AM6" s="1">
+        <v>0</v>
+      </c>
+      <c r="AN6" s="1">
+        <v>0</v>
+      </c>
+      <c r="AO6" s="1">
+        <v>0</v>
+      </c>
+      <c r="AP6" s="1">
+        <v>0</v>
+      </c>
+      <c r="AQ6" s="1">
+        <v>0</v>
+      </c>
+      <c r="AR6" s="1">
+        <v>0</v>
+      </c>
+      <c r="AS6" s="1">
+        <v>0</v>
+      </c>
+      <c r="AT6" s="1">
+        <v>0</v>
+      </c>
+      <c r="AU6" s="1">
+        <v>0</v>
+      </c>
+      <c r="AV6" s="1">
+        <v>0</v>
+      </c>
+      <c r="AW6" s="1">
+        <v>0</v>
+      </c>
+      <c r="AX6" s="1">
+        <v>0</v>
+      </c>
+      <c r="AY6" s="1">
+        <v>0</v>
+      </c>
+      <c r="AZ6" s="1">
+        <v>0</v>
+      </c>
+      <c r="BA6" s="1">
+        <v>0</v>
+      </c>
+      <c r="BB6" s="1">
+        <v>0</v>
+      </c>
+      <c r="BC6" s="1">
+        <v>0</v>
+      </c>
+      <c r="BD6" s="1">
+        <v>0</v>
+      </c>
+      <c r="BE6" s="1">
+        <v>0</v>
+      </c>
+      <c r="BF6" s="1">
+        <v>0</v>
+      </c>
+      <c r="BG6" s="1">
+        <v>0</v>
+      </c>
+      <c r="BH6" s="1">
+        <v>0</v>
+      </c>
+      <c r="BI6" s="1">
+        <v>0</v>
+      </c>
+      <c r="BJ6" s="1">
+        <v>0</v>
+      </c>
+      <c r="BK6" s="1">
+        <v>0</v>
+      </c>
+      <c r="BL6" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.4">
-      <c r="A7">
-        <v>0</v>
-      </c>
-      <c r="B7">
-        <v>0</v>
-      </c>
-      <c r="C7">
-        <v>0</v>
-      </c>
-      <c r="D7">
-        <v>0</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-      <c r="F7">
-        <v>0</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7">
-        <v>0</v>
-      </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7">
-        <v>0</v>
-      </c>
-      <c r="K7">
-        <v>0</v>
-      </c>
-      <c r="L7">
-        <v>0</v>
-      </c>
-      <c r="M7">
-        <v>0</v>
-      </c>
-      <c r="N7">
-        <v>2</v>
-      </c>
-      <c r="O7">
-        <v>2</v>
-      </c>
-      <c r="P7">
-        <v>2</v>
-      </c>
-      <c r="Q7">
-        <v>2</v>
-      </c>
-      <c r="R7">
-        <v>0</v>
-      </c>
-      <c r="S7">
-        <v>0</v>
-      </c>
-      <c r="T7">
-        <v>0</v>
-      </c>
-      <c r="U7">
-        <v>0</v>
-      </c>
-      <c r="V7">
-        <v>0</v>
-      </c>
-      <c r="W7">
-        <v>0</v>
-      </c>
-      <c r="X7">
-        <v>0</v>
-      </c>
-      <c r="Y7">
-        <v>0</v>
-      </c>
-      <c r="Z7">
-        <v>0</v>
-      </c>
-      <c r="AA7">
-        <v>0</v>
-      </c>
-      <c r="AB7">
-        <v>0</v>
-      </c>
-      <c r="AC7">
-        <v>0</v>
-      </c>
-      <c r="AD7">
-        <v>0</v>
-      </c>
-      <c r="AE7">
-        <v>0</v>
-      </c>
-      <c r="AF7">
+    <row r="7" spans="1:64">
+      <c r="A7" s="1">
+        <v>2</v>
+      </c>
+      <c r="B7" s="1">
+        <v>0</v>
+      </c>
+      <c r="C7" s="1">
+        <v>0</v>
+      </c>
+      <c r="D7" s="1">
+        <v>0</v>
+      </c>
+      <c r="E7" s="1">
+        <v>0</v>
+      </c>
+      <c r="F7" s="1">
+        <v>0</v>
+      </c>
+      <c r="G7" s="1">
+        <v>0</v>
+      </c>
+      <c r="H7" s="1">
+        <v>0</v>
+      </c>
+      <c r="I7" s="1">
+        <v>0</v>
+      </c>
+      <c r="J7" s="1">
+        <v>0</v>
+      </c>
+      <c r="K7" s="1">
+        <v>0</v>
+      </c>
+      <c r="L7" s="1">
+        <v>0</v>
+      </c>
+      <c r="M7" s="1">
+        <v>0</v>
+      </c>
+      <c r="N7" s="1">
+        <v>0</v>
+      </c>
+      <c r="O7" s="1">
+        <v>0</v>
+      </c>
+      <c r="P7" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="1">
+        <v>0</v>
+      </c>
+      <c r="R7" s="1">
+        <v>0</v>
+      </c>
+      <c r="S7" s="1">
+        <v>0</v>
+      </c>
+      <c r="T7" s="1">
+        <v>0</v>
+      </c>
+      <c r="U7" s="1">
+        <v>0</v>
+      </c>
+      <c r="V7" s="1">
+        <v>0</v>
+      </c>
+      <c r="W7" s="1">
+        <v>0</v>
+      </c>
+      <c r="X7" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z7" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA7" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB7" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC7" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD7" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE7" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF7" s="1">
+        <v>2</v>
+      </c>
+      <c r="AG7" s="1">
+        <v>0</v>
+      </c>
+      <c r="AH7" s="1">
+        <v>0</v>
+      </c>
+      <c r="AI7" s="1">
+        <v>0</v>
+      </c>
+      <c r="AJ7" s="1">
+        <v>0</v>
+      </c>
+      <c r="AK7" s="1">
+        <v>0</v>
+      </c>
+      <c r="AL7" s="1">
+        <v>0</v>
+      </c>
+      <c r="AM7" s="1">
+        <v>0</v>
+      </c>
+      <c r="AN7" s="1">
+        <v>0</v>
+      </c>
+      <c r="AO7" s="1">
+        <v>0</v>
+      </c>
+      <c r="AP7" s="1">
+        <v>0</v>
+      </c>
+      <c r="AQ7" s="1">
+        <v>0</v>
+      </c>
+      <c r="AR7" s="1">
+        <v>0</v>
+      </c>
+      <c r="AS7" s="1">
+        <v>0</v>
+      </c>
+      <c r="AT7" s="1">
+        <v>0</v>
+      </c>
+      <c r="AU7" s="1">
+        <v>0</v>
+      </c>
+      <c r="AV7" s="1">
+        <v>0</v>
+      </c>
+      <c r="AW7" s="1">
+        <v>0</v>
+      </c>
+      <c r="AX7" s="1">
+        <v>0</v>
+      </c>
+      <c r="AY7" s="1">
+        <v>0</v>
+      </c>
+      <c r="AZ7" s="1">
+        <v>0</v>
+      </c>
+      <c r="BA7" s="1">
+        <v>0</v>
+      </c>
+      <c r="BB7" s="1">
+        <v>0</v>
+      </c>
+      <c r="BC7" s="1">
+        <v>0</v>
+      </c>
+      <c r="BD7" s="1">
+        <v>0</v>
+      </c>
+      <c r="BE7" s="1">
+        <v>0</v>
+      </c>
+      <c r="BF7" s="1">
+        <v>0</v>
+      </c>
+      <c r="BG7" s="1">
+        <v>0</v>
+      </c>
+      <c r="BH7" s="1">
+        <v>0</v>
+      </c>
+      <c r="BI7" s="1">
+        <v>0</v>
+      </c>
+      <c r="BJ7" s="1">
+        <v>0</v>
+      </c>
+      <c r="BK7" s="1">
+        <v>0</v>
+      </c>
+      <c r="BL7" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.4">
-      <c r="A8">
-        <v>0</v>
-      </c>
-      <c r="B8">
-        <v>0</v>
-      </c>
-      <c r="C8">
-        <v>0</v>
-      </c>
-      <c r="D8">
-        <v>0</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-      <c r="F8">
-        <v>0</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8">
-        <v>0</v>
-      </c>
-      <c r="I8">
-        <v>0</v>
-      </c>
-      <c r="J8">
-        <v>0</v>
-      </c>
-      <c r="K8">
-        <v>0</v>
-      </c>
-      <c r="L8">
-        <v>0</v>
-      </c>
-      <c r="M8">
-        <v>0</v>
-      </c>
-      <c r="N8">
-        <v>0</v>
-      </c>
-      <c r="O8">
-        <v>0</v>
-      </c>
-      <c r="P8">
-        <v>0</v>
-      </c>
-      <c r="Q8">
-        <v>0</v>
-      </c>
-      <c r="R8">
-        <v>0</v>
-      </c>
-      <c r="S8">
-        <v>0</v>
-      </c>
-      <c r="T8">
-        <v>0</v>
-      </c>
-      <c r="U8">
-        <v>0</v>
-      </c>
-      <c r="V8">
-        <v>0</v>
-      </c>
-      <c r="W8">
-        <v>0</v>
-      </c>
-      <c r="X8">
-        <v>0</v>
-      </c>
-      <c r="Y8">
-        <v>0</v>
-      </c>
-      <c r="Z8">
-        <v>0</v>
-      </c>
-      <c r="AA8">
-        <v>0</v>
-      </c>
-      <c r="AB8">
-        <v>0</v>
-      </c>
-      <c r="AC8">
-        <v>0</v>
-      </c>
-      <c r="AD8">
-        <v>0</v>
-      </c>
-      <c r="AE8">
-        <v>0</v>
-      </c>
-      <c r="AF8">
+    <row r="8" spans="1:64">
+      <c r="A8" s="1">
+        <v>2</v>
+      </c>
+      <c r="B8" s="1">
+        <v>0</v>
+      </c>
+      <c r="C8" s="1">
+        <v>0</v>
+      </c>
+      <c r="D8" s="1">
+        <v>0</v>
+      </c>
+      <c r="E8" s="1">
+        <v>0</v>
+      </c>
+      <c r="F8" s="1">
+        <v>0</v>
+      </c>
+      <c r="G8" s="1">
+        <v>0</v>
+      </c>
+      <c r="H8" s="1">
+        <v>0</v>
+      </c>
+      <c r="I8" s="1">
+        <v>0</v>
+      </c>
+      <c r="J8" s="1">
+        <v>0</v>
+      </c>
+      <c r="K8" s="1">
+        <v>0</v>
+      </c>
+      <c r="L8" s="1">
+        <v>0</v>
+      </c>
+      <c r="M8" s="1">
+        <v>0</v>
+      </c>
+      <c r="N8" s="1">
+        <v>0</v>
+      </c>
+      <c r="O8" s="1">
+        <v>0</v>
+      </c>
+      <c r="P8" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="1">
+        <v>0</v>
+      </c>
+      <c r="R8" s="1">
+        <v>0</v>
+      </c>
+      <c r="S8" s="1">
+        <v>2</v>
+      </c>
+      <c r="T8" s="1">
+        <v>2</v>
+      </c>
+      <c r="U8" s="1">
+        <v>2</v>
+      </c>
+      <c r="V8" s="1">
+        <v>2</v>
+      </c>
+      <c r="W8" s="1">
+        <v>2</v>
+      </c>
+      <c r="X8" s="1">
+        <v>2</v>
+      </c>
+      <c r="Y8" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z8" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA8" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB8" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC8" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD8" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE8" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF8" s="1">
+        <v>2</v>
+      </c>
+      <c r="AG8" s="1">
+        <v>0</v>
+      </c>
+      <c r="AH8" s="1">
+        <v>0</v>
+      </c>
+      <c r="AI8" s="1">
+        <v>0</v>
+      </c>
+      <c r="AJ8" s="1">
+        <v>0</v>
+      </c>
+      <c r="AK8" s="1">
+        <v>0</v>
+      </c>
+      <c r="AL8" s="1">
+        <v>0</v>
+      </c>
+      <c r="AM8" s="1">
+        <v>0</v>
+      </c>
+      <c r="AN8" s="1">
+        <v>0</v>
+      </c>
+      <c r="AO8" s="1">
+        <v>0</v>
+      </c>
+      <c r="AP8" s="1">
+        <v>0</v>
+      </c>
+      <c r="AQ8" s="1">
+        <v>0</v>
+      </c>
+      <c r="AR8" s="1">
+        <v>0</v>
+      </c>
+      <c r="AS8" s="1">
+        <v>0</v>
+      </c>
+      <c r="AT8" s="1">
+        <v>0</v>
+      </c>
+      <c r="AU8" s="1">
+        <v>0</v>
+      </c>
+      <c r="AV8" s="1">
+        <v>0</v>
+      </c>
+      <c r="AW8" s="1">
+        <v>0</v>
+      </c>
+      <c r="AX8" s="1">
+        <v>0</v>
+      </c>
+      <c r="AY8" s="1">
+        <v>0</v>
+      </c>
+      <c r="AZ8" s="1">
+        <v>0</v>
+      </c>
+      <c r="BA8" s="1">
+        <v>0</v>
+      </c>
+      <c r="BB8" s="1">
+        <v>0</v>
+      </c>
+      <c r="BC8" s="1">
+        <v>0</v>
+      </c>
+      <c r="BD8" s="1">
+        <v>0</v>
+      </c>
+      <c r="BE8" s="1">
+        <v>0</v>
+      </c>
+      <c r="BF8" s="1">
+        <v>0</v>
+      </c>
+      <c r="BG8" s="1">
+        <v>0</v>
+      </c>
+      <c r="BH8" s="1">
+        <v>0</v>
+      </c>
+      <c r="BI8" s="1">
+        <v>0</v>
+      </c>
+      <c r="BJ8" s="1">
+        <v>0</v>
+      </c>
+      <c r="BK8" s="1">
+        <v>0</v>
+      </c>
+      <c r="BL8" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.4">
-      <c r="A9">
-        <v>0</v>
-      </c>
-      <c r="B9">
-        <v>0</v>
-      </c>
-      <c r="C9">
-        <v>0</v>
-      </c>
-      <c r="D9">
-        <v>0</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-      <c r="F9">
-        <v>0</v>
-      </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-      <c r="H9">
-        <v>0</v>
-      </c>
-      <c r="I9">
-        <v>2</v>
-      </c>
-      <c r="J9">
-        <v>2</v>
-      </c>
-      <c r="K9">
-        <v>2</v>
-      </c>
-      <c r="L9">
-        <v>0</v>
-      </c>
-      <c r="M9">
-        <v>0</v>
-      </c>
-      <c r="N9">
-        <v>0</v>
-      </c>
-      <c r="O9">
-        <v>0</v>
-      </c>
-      <c r="P9">
-        <v>0</v>
-      </c>
-      <c r="Q9">
-        <v>0</v>
-      </c>
-      <c r="R9">
-        <v>0</v>
-      </c>
-      <c r="S9">
-        <v>0</v>
-      </c>
-      <c r="T9">
-        <v>0</v>
-      </c>
-      <c r="U9">
-        <v>0</v>
-      </c>
-      <c r="V9">
-        <v>0</v>
-      </c>
-      <c r="W9">
-        <v>0</v>
-      </c>
-      <c r="X9">
-        <v>0</v>
-      </c>
-      <c r="Y9">
-        <v>0</v>
-      </c>
-      <c r="Z9">
-        <v>0</v>
-      </c>
-      <c r="AA9">
-        <v>0</v>
-      </c>
-      <c r="AB9">
-        <v>0</v>
-      </c>
-      <c r="AC9">
-        <v>0</v>
-      </c>
-      <c r="AD9">
-        <v>0</v>
-      </c>
-      <c r="AE9">
-        <v>0</v>
-      </c>
-      <c r="AF9">
+    <row r="9" spans="1:64">
+      <c r="A9" s="1">
+        <v>2</v>
+      </c>
+      <c r="B9" s="1">
+        <v>0</v>
+      </c>
+      <c r="C9" s="1">
+        <v>0</v>
+      </c>
+      <c r="D9" s="1">
+        <v>0</v>
+      </c>
+      <c r="E9" s="1">
+        <v>0</v>
+      </c>
+      <c r="F9" s="1">
+        <v>0</v>
+      </c>
+      <c r="G9" s="1">
+        <v>0</v>
+      </c>
+      <c r="H9" s="1">
+        <v>0</v>
+      </c>
+      <c r="I9" s="1">
+        <v>0</v>
+      </c>
+      <c r="J9" s="1">
+        <v>0</v>
+      </c>
+      <c r="K9" s="1">
+        <v>0</v>
+      </c>
+      <c r="L9" s="1">
+        <v>0</v>
+      </c>
+      <c r="M9" s="1">
+        <v>0</v>
+      </c>
+      <c r="N9" s="1">
+        <v>0</v>
+      </c>
+      <c r="O9" s="1">
+        <v>0</v>
+      </c>
+      <c r="P9" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="1">
+        <v>0</v>
+      </c>
+      <c r="R9" s="1">
+        <v>0</v>
+      </c>
+      <c r="S9" s="1">
+        <v>0</v>
+      </c>
+      <c r="T9" s="1">
+        <v>0</v>
+      </c>
+      <c r="U9" s="1">
+        <v>0</v>
+      </c>
+      <c r="V9" s="1">
+        <v>0</v>
+      </c>
+      <c r="W9" s="1">
+        <v>0</v>
+      </c>
+      <c r="X9" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z9" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA9" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB9" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC9" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD9" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE9" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF9" s="1">
+        <v>2</v>
+      </c>
+      <c r="AG9" s="1">
+        <v>0</v>
+      </c>
+      <c r="AH9" s="1">
+        <v>0</v>
+      </c>
+      <c r="AI9" s="1">
+        <v>0</v>
+      </c>
+      <c r="AJ9" s="1">
+        <v>0</v>
+      </c>
+      <c r="AK9" s="1">
+        <v>0</v>
+      </c>
+      <c r="AL9" s="1">
+        <v>0</v>
+      </c>
+      <c r="AM9" s="1">
+        <v>0</v>
+      </c>
+      <c r="AN9" s="1">
+        <v>0</v>
+      </c>
+      <c r="AO9" s="1">
+        <v>0</v>
+      </c>
+      <c r="AP9" s="1">
+        <v>0</v>
+      </c>
+      <c r="AQ9" s="1">
+        <v>0</v>
+      </c>
+      <c r="AR9" s="1">
+        <v>0</v>
+      </c>
+      <c r="AS9" s="1">
+        <v>0</v>
+      </c>
+      <c r="AT9" s="1">
+        <v>0</v>
+      </c>
+      <c r="AU9" s="1">
+        <v>0</v>
+      </c>
+      <c r="AV9" s="1">
+        <v>0</v>
+      </c>
+      <c r="AW9" s="1">
+        <v>0</v>
+      </c>
+      <c r="AX9" s="1">
+        <v>0</v>
+      </c>
+      <c r="AY9" s="1">
+        <v>0</v>
+      </c>
+      <c r="AZ9" s="1">
+        <v>0</v>
+      </c>
+      <c r="BA9" s="1">
+        <v>0</v>
+      </c>
+      <c r="BB9" s="1">
+        <v>0</v>
+      </c>
+      <c r="BC9" s="1">
+        <v>0</v>
+      </c>
+      <c r="BD9" s="1">
+        <v>0</v>
+      </c>
+      <c r="BE9" s="1">
+        <v>0</v>
+      </c>
+      <c r="BF9" s="1">
+        <v>0</v>
+      </c>
+      <c r="BG9" s="1">
+        <v>0</v>
+      </c>
+      <c r="BH9" s="1">
+        <v>0</v>
+      </c>
+      <c r="BI9" s="1">
+        <v>0</v>
+      </c>
+      <c r="BJ9" s="1">
+        <v>0</v>
+      </c>
+      <c r="BK9" s="1">
+        <v>0</v>
+      </c>
+      <c r="BL9" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.4">
-      <c r="A10">
-        <v>0</v>
-      </c>
-      <c r="B10">
-        <v>0</v>
-      </c>
-      <c r="C10">
-        <v>0</v>
-      </c>
-      <c r="D10">
-        <v>0</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-      <c r="F10">
-        <v>0</v>
-      </c>
-      <c r="G10">
-        <v>0</v>
-      </c>
-      <c r="H10">
-        <v>2</v>
-      </c>
-      <c r="I10">
-        <v>1</v>
-      </c>
-      <c r="J10">
-        <v>1</v>
-      </c>
-      <c r="K10">
-        <v>1</v>
-      </c>
-      <c r="L10">
-        <v>2</v>
-      </c>
-      <c r="M10">
-        <v>0</v>
-      </c>
-      <c r="N10">
-        <v>0</v>
-      </c>
-      <c r="O10">
-        <v>0</v>
-      </c>
-      <c r="P10">
-        <v>0</v>
-      </c>
-      <c r="Q10">
-        <v>0</v>
-      </c>
-      <c r="R10">
-        <v>0</v>
-      </c>
-      <c r="S10">
-        <v>0</v>
-      </c>
-      <c r="T10">
-        <v>0</v>
-      </c>
-      <c r="U10">
-        <v>0</v>
-      </c>
-      <c r="V10">
-        <v>0</v>
-      </c>
-      <c r="W10">
-        <v>0</v>
-      </c>
-      <c r="X10">
-        <v>0</v>
-      </c>
-      <c r="Y10">
-        <v>0</v>
-      </c>
-      <c r="Z10">
-        <v>0</v>
-      </c>
-      <c r="AA10">
-        <v>0</v>
-      </c>
-      <c r="AB10">
-        <v>0</v>
-      </c>
-      <c r="AC10">
-        <v>0</v>
-      </c>
-      <c r="AD10">
-        <v>0</v>
-      </c>
-      <c r="AE10">
-        <v>0</v>
-      </c>
-      <c r="AF10">
+    <row r="10" spans="1:64">
+      <c r="A10" s="1">
+        <v>2</v>
+      </c>
+      <c r="B10" s="1">
+        <v>0</v>
+      </c>
+      <c r="C10" s="1">
+        <v>0</v>
+      </c>
+      <c r="D10" s="1">
+        <v>0</v>
+      </c>
+      <c r="E10" s="1">
+        <v>0</v>
+      </c>
+      <c r="F10" s="1">
+        <v>0</v>
+      </c>
+      <c r="G10" s="1">
+        <v>0</v>
+      </c>
+      <c r="H10" s="1">
+        <v>0</v>
+      </c>
+      <c r="I10" s="1">
+        <v>0</v>
+      </c>
+      <c r="J10" s="1">
+        <v>0</v>
+      </c>
+      <c r="K10" s="1">
+        <v>0</v>
+      </c>
+      <c r="L10" s="1">
+        <v>2</v>
+      </c>
+      <c r="M10" s="1">
+        <v>2</v>
+      </c>
+      <c r="N10" s="1">
+        <v>2</v>
+      </c>
+      <c r="O10" s="1">
+        <v>2</v>
+      </c>
+      <c r="P10" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="1">
+        <v>0</v>
+      </c>
+      <c r="R10" s="1">
+        <v>0</v>
+      </c>
+      <c r="S10" s="1">
+        <v>0</v>
+      </c>
+      <c r="T10" s="1">
+        <v>0</v>
+      </c>
+      <c r="U10" s="1">
+        <v>0</v>
+      </c>
+      <c r="V10" s="1">
+        <v>0</v>
+      </c>
+      <c r="W10" s="1">
+        <v>0</v>
+      </c>
+      <c r="X10" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y10" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z10" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA10" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB10" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC10" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD10" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE10" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF10" s="1">
+        <v>2</v>
+      </c>
+      <c r="AG10" s="1">
+        <v>0</v>
+      </c>
+      <c r="AH10" s="1">
+        <v>0</v>
+      </c>
+      <c r="AI10" s="1">
+        <v>0</v>
+      </c>
+      <c r="AJ10" s="1">
+        <v>0</v>
+      </c>
+      <c r="AK10" s="1">
+        <v>0</v>
+      </c>
+      <c r="AL10" s="1">
+        <v>0</v>
+      </c>
+      <c r="AM10" s="1">
+        <v>0</v>
+      </c>
+      <c r="AN10" s="1">
+        <v>0</v>
+      </c>
+      <c r="AO10" s="1">
+        <v>0</v>
+      </c>
+      <c r="AP10" s="1">
+        <v>0</v>
+      </c>
+      <c r="AQ10" s="1">
+        <v>0</v>
+      </c>
+      <c r="AR10" s="1">
+        <v>0</v>
+      </c>
+      <c r="AS10" s="1">
+        <v>0</v>
+      </c>
+      <c r="AT10" s="1">
+        <v>0</v>
+      </c>
+      <c r="AU10" s="1">
+        <v>0</v>
+      </c>
+      <c r="AV10" s="1">
+        <v>0</v>
+      </c>
+      <c r="AW10" s="1">
+        <v>0</v>
+      </c>
+      <c r="AX10" s="1">
+        <v>0</v>
+      </c>
+      <c r="AY10" s="1">
+        <v>0</v>
+      </c>
+      <c r="AZ10" s="1">
+        <v>0</v>
+      </c>
+      <c r="BA10" s="1">
+        <v>0</v>
+      </c>
+      <c r="BB10" s="1">
+        <v>0</v>
+      </c>
+      <c r="BC10" s="1">
+        <v>0</v>
+      </c>
+      <c r="BD10" s="1">
+        <v>0</v>
+      </c>
+      <c r="BE10" s="1">
+        <v>0</v>
+      </c>
+      <c r="BF10" s="1">
+        <v>0</v>
+      </c>
+      <c r="BG10" s="1">
+        <v>0</v>
+      </c>
+      <c r="BH10" s="1">
+        <v>0</v>
+      </c>
+      <c r="BI10" s="1">
+        <v>0</v>
+      </c>
+      <c r="BJ10" s="1">
+        <v>0</v>
+      </c>
+      <c r="BK10" s="1">
+        <v>0</v>
+      </c>
+      <c r="BL10" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.4">
-      <c r="A11">
-        <v>2</v>
-      </c>
-      <c r="B11">
-        <v>2</v>
-      </c>
-      <c r="C11">
-        <v>2</v>
-      </c>
-      <c r="D11">
-        <v>2</v>
-      </c>
-      <c r="E11">
-        <v>2</v>
-      </c>
-      <c r="F11">
-        <v>2</v>
-      </c>
-      <c r="G11">
-        <v>2</v>
-      </c>
-      <c r="H11">
-        <v>1</v>
-      </c>
-      <c r="I11">
-        <v>1</v>
-      </c>
-      <c r="J11">
-        <v>1</v>
-      </c>
-      <c r="K11">
-        <v>1</v>
-      </c>
-      <c r="L11">
-        <v>1</v>
-      </c>
-      <c r="M11">
-        <v>2</v>
-      </c>
-      <c r="N11">
-        <v>2</v>
-      </c>
-      <c r="O11">
-        <v>2</v>
-      </c>
-      <c r="P11">
-        <v>2</v>
-      </c>
-      <c r="Q11">
-        <v>2</v>
-      </c>
-      <c r="R11">
-        <v>2</v>
-      </c>
-      <c r="S11">
-        <v>2</v>
-      </c>
-      <c r="T11">
-        <v>2</v>
-      </c>
-      <c r="U11">
-        <v>2</v>
-      </c>
-      <c r="V11">
-        <v>2</v>
-      </c>
-      <c r="W11">
-        <v>2</v>
-      </c>
-      <c r="X11">
-        <v>2</v>
-      </c>
-      <c r="Y11">
-        <v>2</v>
-      </c>
-      <c r="Z11">
-        <v>2</v>
-      </c>
-      <c r="AA11">
-        <v>2</v>
-      </c>
-      <c r="AB11">
-        <v>2</v>
-      </c>
-      <c r="AC11">
-        <v>2</v>
-      </c>
-      <c r="AD11">
-        <v>2</v>
-      </c>
-      <c r="AE11">
-        <v>2</v>
-      </c>
-      <c r="AF11">
-        <v>2</v>
+    <row r="11" spans="1:64">
+      <c r="A11" s="2">
+        <v>2</v>
+      </c>
+      <c r="B11" s="2">
+        <v>2</v>
+      </c>
+      <c r="C11" s="2">
+        <v>2</v>
+      </c>
+      <c r="D11" s="2">
+        <v>2</v>
+      </c>
+      <c r="E11" s="2">
+        <v>2</v>
+      </c>
+      <c r="F11" s="2">
+        <v>2</v>
+      </c>
+      <c r="G11" s="2">
+        <v>2</v>
+      </c>
+      <c r="H11" s="2">
+        <v>2</v>
+      </c>
+      <c r="I11" s="2">
+        <v>2</v>
+      </c>
+      <c r="J11" s="2">
+        <v>2</v>
+      </c>
+      <c r="K11" s="2">
+        <v>2</v>
+      </c>
+      <c r="L11" s="2">
+        <v>1</v>
+      </c>
+      <c r="M11" s="2">
+        <v>1</v>
+      </c>
+      <c r="N11" s="2">
+        <v>1</v>
+      </c>
+      <c r="O11" s="2">
+        <v>1</v>
+      </c>
+      <c r="P11" s="2">
+        <v>2</v>
+      </c>
+      <c r="Q11" s="2">
+        <v>2</v>
+      </c>
+      <c r="R11" s="2">
+        <v>2</v>
+      </c>
+      <c r="S11" s="2">
+        <v>2</v>
+      </c>
+      <c r="T11" s="2">
+        <v>2</v>
+      </c>
+      <c r="U11" s="2">
+        <v>2</v>
+      </c>
+      <c r="V11" s="2">
+        <v>2</v>
+      </c>
+      <c r="W11" s="2">
+        <v>2</v>
+      </c>
+      <c r="X11" s="2">
+        <v>2</v>
+      </c>
+      <c r="Y11" s="2">
+        <v>2</v>
+      </c>
+      <c r="Z11" s="2">
+        <v>2</v>
+      </c>
+      <c r="AA11" s="2">
+        <v>2</v>
+      </c>
+      <c r="AB11" s="2">
+        <v>2</v>
+      </c>
+      <c r="AC11" s="2">
+        <v>2</v>
+      </c>
+      <c r="AD11" s="2">
+        <v>2</v>
+      </c>
+      <c r="AE11" s="2">
+        <v>2</v>
+      </c>
+      <c r="AF11" s="2">
+        <v>2</v>
+      </c>
+      <c r="AG11" s="1">
+        <v>0</v>
+      </c>
+      <c r="AH11" s="1">
+        <v>0</v>
+      </c>
+      <c r="AI11" s="1">
+        <v>0</v>
+      </c>
+      <c r="AJ11" s="1">
+        <v>0</v>
+      </c>
+      <c r="AK11" s="1">
+        <v>0</v>
+      </c>
+      <c r="AL11" s="1">
+        <v>0</v>
+      </c>
+      <c r="AM11" s="1">
+        <v>0</v>
+      </c>
+      <c r="AN11" s="1">
+        <v>0</v>
+      </c>
+      <c r="AO11" s="1">
+        <v>0</v>
+      </c>
+      <c r="AP11" s="1">
+        <v>0</v>
+      </c>
+      <c r="AQ11" s="1">
+        <v>0</v>
+      </c>
+      <c r="AR11" s="1">
+        <v>0</v>
+      </c>
+      <c r="AS11" s="1">
+        <v>0</v>
+      </c>
+      <c r="AT11" s="1">
+        <v>0</v>
+      </c>
+      <c r="AU11" s="1">
+        <v>0</v>
+      </c>
+      <c r="AV11" s="1">
+        <v>0</v>
+      </c>
+      <c r="AW11" s="4">
+        <v>0</v>
+      </c>
+      <c r="AX11" s="4">
+        <v>0</v>
+      </c>
+      <c r="AY11" s="4">
+        <v>0</v>
+      </c>
+      <c r="AZ11" s="4">
+        <v>0</v>
+      </c>
+      <c r="BA11" s="4">
+        <v>0</v>
+      </c>
+      <c r="BB11" s="4">
+        <v>0</v>
+      </c>
+      <c r="BC11" s="4">
+        <v>0</v>
+      </c>
+      <c r="BD11" s="4">
+        <v>0</v>
+      </c>
+      <c r="BE11" s="4">
+        <v>0</v>
+      </c>
+      <c r="BF11" s="4">
+        <v>0</v>
+      </c>
+      <c r="BG11" s="4">
+        <v>0</v>
+      </c>
+      <c r="BH11" s="4">
+        <v>0</v>
+      </c>
+      <c r="BI11" s="4">
+        <v>0</v>
+      </c>
+      <c r="BJ11" s="4">
+        <v>0</v>
+      </c>
+      <c r="BK11" s="4">
+        <v>0</v>
+      </c>
+      <c r="BL11" s="4">
+        <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.4">
-      <c r="A12">
-        <v>1</v>
-      </c>
-      <c r="B12">
-        <v>1</v>
-      </c>
-      <c r="C12">
-        <v>1</v>
-      </c>
-      <c r="D12">
-        <v>1</v>
-      </c>
-      <c r="E12">
-        <v>1</v>
-      </c>
-      <c r="F12">
-        <v>1</v>
-      </c>
-      <c r="G12">
-        <v>1</v>
-      </c>
-      <c r="H12">
-        <v>1</v>
-      </c>
-      <c r="I12">
-        <v>1</v>
-      </c>
-      <c r="J12">
-        <v>1</v>
-      </c>
-      <c r="K12">
-        <v>1</v>
-      </c>
-      <c r="L12">
-        <v>1</v>
-      </c>
-      <c r="M12">
-        <v>1</v>
-      </c>
-      <c r="N12">
-        <v>1</v>
-      </c>
-      <c r="O12">
-        <v>1</v>
-      </c>
-      <c r="P12">
-        <v>1</v>
-      </c>
-      <c r="Q12">
-        <v>1</v>
-      </c>
-      <c r="R12">
-        <v>1</v>
-      </c>
-      <c r="S12">
-        <v>1</v>
-      </c>
-      <c r="T12">
-        <v>1</v>
-      </c>
-      <c r="U12">
-        <v>1</v>
-      </c>
-      <c r="V12">
-        <v>1</v>
-      </c>
-      <c r="W12">
-        <v>1</v>
-      </c>
-      <c r="X12">
-        <v>1</v>
-      </c>
-      <c r="Y12">
-        <v>1</v>
-      </c>
-      <c r="Z12">
-        <v>1</v>
-      </c>
-      <c r="AA12">
-        <v>1</v>
-      </c>
-      <c r="AB12">
-        <v>1</v>
-      </c>
-      <c r="AC12">
-        <v>1</v>
-      </c>
-      <c r="AD12">
-        <v>1</v>
-      </c>
-      <c r="AE12">
-        <v>1</v>
-      </c>
-      <c r="AF12">
-        <v>1</v>
+    <row r="12" spans="1:64">
+      <c r="A12" s="3">
+        <v>1</v>
+      </c>
+      <c r="B12" s="3">
+        <v>1</v>
+      </c>
+      <c r="C12" s="3">
+        <v>1</v>
+      </c>
+      <c r="D12" s="3">
+        <v>1</v>
+      </c>
+      <c r="E12" s="3">
+        <v>1</v>
+      </c>
+      <c r="F12" s="3">
+        <v>1</v>
+      </c>
+      <c r="G12" s="3">
+        <v>1</v>
+      </c>
+      <c r="H12" s="3">
+        <v>1</v>
+      </c>
+      <c r="I12" s="3">
+        <v>1</v>
+      </c>
+      <c r="J12" s="3">
+        <v>1</v>
+      </c>
+      <c r="K12" s="3">
+        <v>1</v>
+      </c>
+      <c r="L12" s="3">
+        <v>1</v>
+      </c>
+      <c r="M12" s="3">
+        <v>1</v>
+      </c>
+      <c r="N12" s="3">
+        <v>1</v>
+      </c>
+      <c r="O12" s="3">
+        <v>1</v>
+      </c>
+      <c r="P12" s="3">
+        <v>1</v>
+      </c>
+      <c r="Q12" s="3">
+        <v>1</v>
+      </c>
+      <c r="R12" s="3">
+        <v>1</v>
+      </c>
+      <c r="S12" s="3">
+        <v>1</v>
+      </c>
+      <c r="T12" s="3">
+        <v>1</v>
+      </c>
+      <c r="U12" s="3">
+        <v>1</v>
+      </c>
+      <c r="V12" s="3">
+        <v>1</v>
+      </c>
+      <c r="W12" s="3">
+        <v>1</v>
+      </c>
+      <c r="X12" s="3">
+        <v>1</v>
+      </c>
+      <c r="Y12" s="3">
+        <v>1</v>
+      </c>
+      <c r="Z12" s="3">
+        <v>1</v>
+      </c>
+      <c r="AA12" s="3">
+        <v>1</v>
+      </c>
+      <c r="AB12" s="3">
+        <v>1</v>
+      </c>
+      <c r="AC12" s="3">
+        <v>1</v>
+      </c>
+      <c r="AD12" s="3">
+        <v>1</v>
+      </c>
+      <c r="AE12" s="3">
+        <v>1</v>
+      </c>
+      <c r="AF12" s="3">
+        <v>1</v>
+      </c>
+      <c r="AG12" s="1">
+        <v>0</v>
+      </c>
+      <c r="AH12" s="1">
+        <v>0</v>
+      </c>
+      <c r="AI12" s="1">
+        <v>0</v>
+      </c>
+      <c r="AJ12" s="1">
+        <v>0</v>
+      </c>
+      <c r="AK12" s="1">
+        <v>0</v>
+      </c>
+      <c r="AL12" s="1">
+        <v>0</v>
+      </c>
+      <c r="AM12" s="1">
+        <v>0</v>
+      </c>
+      <c r="AN12" s="1">
+        <v>0</v>
+      </c>
+      <c r="AO12" s="1">
+        <v>0</v>
+      </c>
+      <c r="AP12" s="1">
+        <v>0</v>
+      </c>
+      <c r="AQ12" s="1">
+        <v>0</v>
+      </c>
+      <c r="AR12" s="1">
+        <v>0</v>
+      </c>
+      <c r="AS12" s="1">
+        <v>0</v>
+      </c>
+      <c r="AT12" s="1">
+        <v>0</v>
+      </c>
+      <c r="AU12" s="1">
+        <v>0</v>
+      </c>
+      <c r="AV12" s="1">
+        <v>0</v>
+      </c>
+      <c r="AW12" s="4">
+        <v>0</v>
+      </c>
+      <c r="AX12" s="4">
+        <v>0</v>
+      </c>
+      <c r="AY12" s="4">
+        <v>0</v>
+      </c>
+      <c r="AZ12" s="4">
+        <v>0</v>
+      </c>
+      <c r="BA12" s="4">
+        <v>0</v>
+      </c>
+      <c r="BB12" s="4">
+        <v>0</v>
+      </c>
+      <c r="BC12" s="4">
+        <v>0</v>
+      </c>
+      <c r="BD12" s="4">
+        <v>0</v>
+      </c>
+      <c r="BE12" s="4">
+        <v>0</v>
+      </c>
+      <c r="BF12" s="4">
+        <v>0</v>
+      </c>
+      <c r="BG12" s="4">
+        <v>0</v>
+      </c>
+      <c r="BH12" s="4">
+        <v>0</v>
+      </c>
+      <c r="BI12" s="4">
+        <v>0</v>
+      </c>
+      <c r="BJ12" s="4">
+        <v>0</v>
+      </c>
+      <c r="BK12" s="4">
+        <v>0</v>
+      </c>
+      <c r="BL12" s="4">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
-  <conditionalFormatting sqref="A1:AF12">
+  <conditionalFormatting sqref="A1:BL12">
     <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
-      <formula>1</formula>
+      <formula>2</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
-      <formula>2</formula>
+      <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1644,14 +2840,2356 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF26DA9C-D84B-469D-BB4C-3116DB6599CB}">
+  <dimension ref="A1:BL12"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
+  <cols>
+    <col min="1" max="64" width="3.875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:64">
+      <c r="A1" s="1">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1">
+        <v>0</v>
+      </c>
+      <c r="D1" s="1">
+        <v>0</v>
+      </c>
+      <c r="E1" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1" s="1">
+        <v>0</v>
+      </c>
+      <c r="G1" s="1">
+        <v>0</v>
+      </c>
+      <c r="H1" s="1">
+        <v>0</v>
+      </c>
+      <c r="I1" s="1">
+        <v>0</v>
+      </c>
+      <c r="J1" s="1">
+        <v>0</v>
+      </c>
+      <c r="K1" s="1">
+        <v>0</v>
+      </c>
+      <c r="L1" s="1">
+        <v>0</v>
+      </c>
+      <c r="M1" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1" s="1">
+        <v>0</v>
+      </c>
+      <c r="P1" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1" s="1">
+        <v>0</v>
+      </c>
+      <c r="S1" s="1">
+        <v>0</v>
+      </c>
+      <c r="T1" s="1">
+        <v>0</v>
+      </c>
+      <c r="U1" s="1">
+        <v>0</v>
+      </c>
+      <c r="V1" s="1">
+        <v>0</v>
+      </c>
+      <c r="W1" s="1">
+        <v>0</v>
+      </c>
+      <c r="X1" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y1" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z1" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA1" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB1" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC1" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD1" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE1" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF1" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG1" s="1">
+        <v>0</v>
+      </c>
+      <c r="AH1" s="1">
+        <v>0</v>
+      </c>
+      <c r="AI1" s="1">
+        <v>0</v>
+      </c>
+      <c r="AJ1" s="1">
+        <v>0</v>
+      </c>
+      <c r="AK1" s="1">
+        <v>0</v>
+      </c>
+      <c r="AL1" s="1">
+        <v>0</v>
+      </c>
+      <c r="AM1" s="1">
+        <v>0</v>
+      </c>
+      <c r="AN1" s="1">
+        <v>0</v>
+      </c>
+      <c r="AO1" s="1">
+        <v>0</v>
+      </c>
+      <c r="AP1" s="1">
+        <v>0</v>
+      </c>
+      <c r="AQ1" s="1">
+        <v>0</v>
+      </c>
+      <c r="AR1" s="1">
+        <v>0</v>
+      </c>
+      <c r="AS1" s="1">
+        <v>0</v>
+      </c>
+      <c r="AT1" s="1">
+        <v>0</v>
+      </c>
+      <c r="AU1" s="1">
+        <v>0</v>
+      </c>
+      <c r="AV1" s="1">
+        <v>0</v>
+      </c>
+      <c r="AW1" s="1">
+        <v>0</v>
+      </c>
+      <c r="AX1" s="1">
+        <v>0</v>
+      </c>
+      <c r="AY1" s="1">
+        <v>0</v>
+      </c>
+      <c r="AZ1" s="1">
+        <v>0</v>
+      </c>
+      <c r="BA1" s="1">
+        <v>0</v>
+      </c>
+      <c r="BB1" s="1">
+        <v>0</v>
+      </c>
+      <c r="BC1" s="1">
+        <v>0</v>
+      </c>
+      <c r="BD1" s="1">
+        <v>0</v>
+      </c>
+      <c r="BE1" s="1">
+        <v>0</v>
+      </c>
+      <c r="BF1" s="1">
+        <v>0</v>
+      </c>
+      <c r="BG1" s="1">
+        <v>0</v>
+      </c>
+      <c r="BH1" s="1">
+        <v>0</v>
+      </c>
+      <c r="BI1" s="1">
+        <v>0</v>
+      </c>
+      <c r="BJ1" s="1">
+        <v>0</v>
+      </c>
+      <c r="BK1" s="1">
+        <v>0</v>
+      </c>
+      <c r="BL1" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:64">
+      <c r="A2" s="1">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1">
+        <v>0</v>
+      </c>
+      <c r="C2" s="1">
+        <v>0</v>
+      </c>
+      <c r="D2" s="1">
+        <v>0</v>
+      </c>
+      <c r="E2" s="1">
+        <v>0</v>
+      </c>
+      <c r="F2" s="1">
+        <v>0</v>
+      </c>
+      <c r="G2" s="1">
+        <v>0</v>
+      </c>
+      <c r="H2" s="1">
+        <v>0</v>
+      </c>
+      <c r="I2" s="1">
+        <v>0</v>
+      </c>
+      <c r="J2" s="1">
+        <v>0</v>
+      </c>
+      <c r="K2" s="1">
+        <v>0</v>
+      </c>
+      <c r="L2" s="1">
+        <v>0</v>
+      </c>
+      <c r="M2" s="1">
+        <v>0</v>
+      </c>
+      <c r="N2" s="1">
+        <v>0</v>
+      </c>
+      <c r="O2" s="1">
+        <v>0</v>
+      </c>
+      <c r="P2" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="1">
+        <v>0</v>
+      </c>
+      <c r="R2" s="1">
+        <v>0</v>
+      </c>
+      <c r="S2" s="1">
+        <v>0</v>
+      </c>
+      <c r="T2" s="1">
+        <v>0</v>
+      </c>
+      <c r="U2" s="1">
+        <v>0</v>
+      </c>
+      <c r="V2" s="1">
+        <v>0</v>
+      </c>
+      <c r="W2" s="1">
+        <v>0</v>
+      </c>
+      <c r="X2" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y2" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z2" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA2" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB2" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC2" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD2" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE2" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF2" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG2" s="1">
+        <v>0</v>
+      </c>
+      <c r="AH2" s="1">
+        <v>0</v>
+      </c>
+      <c r="AI2" s="1">
+        <v>0</v>
+      </c>
+      <c r="AJ2" s="1">
+        <v>0</v>
+      </c>
+      <c r="AK2" s="1">
+        <v>0</v>
+      </c>
+      <c r="AL2" s="1">
+        <v>0</v>
+      </c>
+      <c r="AM2" s="1">
+        <v>0</v>
+      </c>
+      <c r="AN2" s="1">
+        <v>0</v>
+      </c>
+      <c r="AO2" s="1">
+        <v>0</v>
+      </c>
+      <c r="AP2" s="1">
+        <v>0</v>
+      </c>
+      <c r="AQ2" s="1">
+        <v>0</v>
+      </c>
+      <c r="AR2" s="1">
+        <v>0</v>
+      </c>
+      <c r="AS2" s="1">
+        <v>0</v>
+      </c>
+      <c r="AT2" s="1">
+        <v>0</v>
+      </c>
+      <c r="AU2" s="1">
+        <v>0</v>
+      </c>
+      <c r="AV2" s="1">
+        <v>0</v>
+      </c>
+      <c r="AW2" s="1">
+        <v>0</v>
+      </c>
+      <c r="AX2" s="1">
+        <v>0</v>
+      </c>
+      <c r="AY2" s="1">
+        <v>0</v>
+      </c>
+      <c r="AZ2" s="1">
+        <v>0</v>
+      </c>
+      <c r="BA2" s="1">
+        <v>0</v>
+      </c>
+      <c r="BB2" s="1">
+        <v>0</v>
+      </c>
+      <c r="BC2" s="1">
+        <v>0</v>
+      </c>
+      <c r="BD2" s="1">
+        <v>0</v>
+      </c>
+      <c r="BE2" s="1">
+        <v>0</v>
+      </c>
+      <c r="BF2" s="1">
+        <v>0</v>
+      </c>
+      <c r="BG2" s="1">
+        <v>0</v>
+      </c>
+      <c r="BH2" s="1">
+        <v>0</v>
+      </c>
+      <c r="BI2" s="1">
+        <v>0</v>
+      </c>
+      <c r="BJ2" s="1">
+        <v>0</v>
+      </c>
+      <c r="BK2" s="1">
+        <v>0</v>
+      </c>
+      <c r="BL2" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:64">
+      <c r="A3" s="1">
+        <v>0</v>
+      </c>
+      <c r="B3" s="1">
+        <v>0</v>
+      </c>
+      <c r="C3" s="1">
+        <v>0</v>
+      </c>
+      <c r="D3" s="1">
+        <v>0</v>
+      </c>
+      <c r="E3" s="1">
+        <v>0</v>
+      </c>
+      <c r="F3" s="1">
+        <v>0</v>
+      </c>
+      <c r="G3" s="1">
+        <v>0</v>
+      </c>
+      <c r="H3" s="1">
+        <v>0</v>
+      </c>
+      <c r="I3" s="1">
+        <v>0</v>
+      </c>
+      <c r="J3" s="1">
+        <v>0</v>
+      </c>
+      <c r="K3" s="1">
+        <v>0</v>
+      </c>
+      <c r="L3" s="1">
+        <v>0</v>
+      </c>
+      <c r="M3" s="1">
+        <v>0</v>
+      </c>
+      <c r="N3" s="1">
+        <v>0</v>
+      </c>
+      <c r="O3" s="1">
+        <v>0</v>
+      </c>
+      <c r="P3" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="1">
+        <v>0</v>
+      </c>
+      <c r="R3" s="1">
+        <v>0</v>
+      </c>
+      <c r="S3" s="1">
+        <v>0</v>
+      </c>
+      <c r="T3" s="1">
+        <v>0</v>
+      </c>
+      <c r="U3" s="1">
+        <v>1</v>
+      </c>
+      <c r="V3" s="1">
+        <v>0</v>
+      </c>
+      <c r="W3" s="1">
+        <v>0</v>
+      </c>
+      <c r="X3" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y3" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z3" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA3" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB3" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC3" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD3" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE3" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF3" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG3" s="1">
+        <v>0</v>
+      </c>
+      <c r="AH3" s="1">
+        <v>0</v>
+      </c>
+      <c r="AI3" s="1">
+        <v>0</v>
+      </c>
+      <c r="AJ3" s="1">
+        <v>0</v>
+      </c>
+      <c r="AK3" s="1">
+        <v>0</v>
+      </c>
+      <c r="AL3" s="1">
+        <v>0</v>
+      </c>
+      <c r="AM3" s="1">
+        <v>0</v>
+      </c>
+      <c r="AN3" s="1">
+        <v>0</v>
+      </c>
+      <c r="AO3" s="1">
+        <v>0</v>
+      </c>
+      <c r="AP3" s="1">
+        <v>0</v>
+      </c>
+      <c r="AQ3" s="1">
+        <v>0</v>
+      </c>
+      <c r="AR3" s="1">
+        <v>0</v>
+      </c>
+      <c r="AS3" s="1">
+        <v>0</v>
+      </c>
+      <c r="AT3" s="1">
+        <v>0</v>
+      </c>
+      <c r="AU3" s="1">
+        <v>0</v>
+      </c>
+      <c r="AV3" s="1">
+        <v>0</v>
+      </c>
+      <c r="AW3" s="1">
+        <v>0</v>
+      </c>
+      <c r="AX3" s="1">
+        <v>0</v>
+      </c>
+      <c r="AY3" s="1">
+        <v>0</v>
+      </c>
+      <c r="AZ3" s="1">
+        <v>0</v>
+      </c>
+      <c r="BA3" s="1">
+        <v>0</v>
+      </c>
+      <c r="BB3" s="1">
+        <v>0</v>
+      </c>
+      <c r="BC3" s="1">
+        <v>0</v>
+      </c>
+      <c r="BD3" s="1">
+        <v>0</v>
+      </c>
+      <c r="BE3" s="1">
+        <v>0</v>
+      </c>
+      <c r="BF3" s="1">
+        <v>0</v>
+      </c>
+      <c r="BG3" s="1">
+        <v>0</v>
+      </c>
+      <c r="BH3" s="1">
+        <v>0</v>
+      </c>
+      <c r="BI3" s="1">
+        <v>0</v>
+      </c>
+      <c r="BJ3" s="1">
+        <v>0</v>
+      </c>
+      <c r="BK3" s="1">
+        <v>0</v>
+      </c>
+      <c r="BL3" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:64">
+      <c r="A4" s="1">
+        <v>0</v>
+      </c>
+      <c r="B4" s="1">
+        <v>0</v>
+      </c>
+      <c r="C4" s="1">
+        <v>0</v>
+      </c>
+      <c r="D4" s="1">
+        <v>0</v>
+      </c>
+      <c r="E4" s="1">
+        <v>0</v>
+      </c>
+      <c r="F4" s="1">
+        <v>0</v>
+      </c>
+      <c r="G4" s="1">
+        <v>0</v>
+      </c>
+      <c r="H4" s="1">
+        <v>0</v>
+      </c>
+      <c r="I4" s="1">
+        <v>0</v>
+      </c>
+      <c r="J4" s="1">
+        <v>0</v>
+      </c>
+      <c r="K4" s="1">
+        <v>0</v>
+      </c>
+      <c r="L4" s="1">
+        <v>0</v>
+      </c>
+      <c r="M4" s="1">
+        <v>0</v>
+      </c>
+      <c r="N4" s="1">
+        <v>0</v>
+      </c>
+      <c r="O4" s="1">
+        <v>0</v>
+      </c>
+      <c r="P4" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="1">
+        <v>0</v>
+      </c>
+      <c r="R4" s="1">
+        <v>0</v>
+      </c>
+      <c r="S4" s="1">
+        <v>0</v>
+      </c>
+      <c r="T4" s="1">
+        <v>0</v>
+      </c>
+      <c r="U4" s="1">
+        <v>1</v>
+      </c>
+      <c r="V4" s="1">
+        <v>0</v>
+      </c>
+      <c r="W4" s="1">
+        <v>0</v>
+      </c>
+      <c r="X4" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z4" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA4" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB4" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC4" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD4" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE4" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF4" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG4" s="1">
+        <v>0</v>
+      </c>
+      <c r="AH4" s="1">
+        <v>0</v>
+      </c>
+      <c r="AI4" s="1">
+        <v>0</v>
+      </c>
+      <c r="AJ4" s="1">
+        <v>0</v>
+      </c>
+      <c r="AK4" s="1">
+        <v>0</v>
+      </c>
+      <c r="AL4" s="1">
+        <v>0</v>
+      </c>
+      <c r="AM4" s="1">
+        <v>0</v>
+      </c>
+      <c r="AN4" s="1">
+        <v>0</v>
+      </c>
+      <c r="AO4" s="1">
+        <v>0</v>
+      </c>
+      <c r="AP4" s="1">
+        <v>0</v>
+      </c>
+      <c r="AQ4" s="1">
+        <v>0</v>
+      </c>
+      <c r="AR4" s="1">
+        <v>0</v>
+      </c>
+      <c r="AS4" s="1">
+        <v>0</v>
+      </c>
+      <c r="AT4" s="1">
+        <v>0</v>
+      </c>
+      <c r="AU4" s="1">
+        <v>0</v>
+      </c>
+      <c r="AV4" s="1">
+        <v>0</v>
+      </c>
+      <c r="AW4" s="1">
+        <v>0</v>
+      </c>
+      <c r="AX4" s="1">
+        <v>0</v>
+      </c>
+      <c r="AY4" s="1">
+        <v>0</v>
+      </c>
+      <c r="AZ4" s="1">
+        <v>0</v>
+      </c>
+      <c r="BA4" s="1">
+        <v>0</v>
+      </c>
+      <c r="BB4" s="1">
+        <v>0</v>
+      </c>
+      <c r="BC4" s="1">
+        <v>0</v>
+      </c>
+      <c r="BD4" s="1">
+        <v>0</v>
+      </c>
+      <c r="BE4" s="1">
+        <v>0</v>
+      </c>
+      <c r="BF4" s="1">
+        <v>0</v>
+      </c>
+      <c r="BG4" s="1">
+        <v>0</v>
+      </c>
+      <c r="BH4" s="1">
+        <v>0</v>
+      </c>
+      <c r="BI4" s="1">
+        <v>0</v>
+      </c>
+      <c r="BJ4" s="1">
+        <v>0</v>
+      </c>
+      <c r="BK4" s="1">
+        <v>0</v>
+      </c>
+      <c r="BL4" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:64">
+      <c r="A5" s="1">
+        <v>0</v>
+      </c>
+      <c r="B5" s="1">
+        <v>0</v>
+      </c>
+      <c r="C5" s="1">
+        <v>0</v>
+      </c>
+      <c r="D5" s="1">
+        <v>0</v>
+      </c>
+      <c r="E5" s="1">
+        <v>0</v>
+      </c>
+      <c r="F5" s="1">
+        <v>0</v>
+      </c>
+      <c r="G5" s="1">
+        <v>0</v>
+      </c>
+      <c r="H5" s="1">
+        <v>0</v>
+      </c>
+      <c r="I5" s="1">
+        <v>0</v>
+      </c>
+      <c r="J5" s="1">
+        <v>0</v>
+      </c>
+      <c r="K5" s="1">
+        <v>0</v>
+      </c>
+      <c r="L5" s="1">
+        <v>0</v>
+      </c>
+      <c r="M5" s="1">
+        <v>0</v>
+      </c>
+      <c r="N5" s="1">
+        <v>0</v>
+      </c>
+      <c r="O5" s="1">
+        <v>0</v>
+      </c>
+      <c r="P5" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="1">
+        <v>0</v>
+      </c>
+      <c r="R5" s="1">
+        <v>0</v>
+      </c>
+      <c r="S5" s="1">
+        <v>0</v>
+      </c>
+      <c r="T5" s="1">
+        <v>0</v>
+      </c>
+      <c r="U5" s="1">
+        <v>1</v>
+      </c>
+      <c r="V5" s="1">
+        <v>0</v>
+      </c>
+      <c r="W5" s="1">
+        <v>0</v>
+      </c>
+      <c r="X5" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y5" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z5" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA5" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB5" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC5" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD5" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE5" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF5" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG5" s="1">
+        <v>0</v>
+      </c>
+      <c r="AH5" s="1">
+        <v>0</v>
+      </c>
+      <c r="AI5" s="1">
+        <v>0</v>
+      </c>
+      <c r="AJ5" s="1">
+        <v>0</v>
+      </c>
+      <c r="AK5" s="1">
+        <v>0</v>
+      </c>
+      <c r="AL5" s="1">
+        <v>0</v>
+      </c>
+      <c r="AM5" s="1">
+        <v>0</v>
+      </c>
+      <c r="AN5" s="1">
+        <v>0</v>
+      </c>
+      <c r="AO5" s="1">
+        <v>0</v>
+      </c>
+      <c r="AP5" s="1">
+        <v>0</v>
+      </c>
+      <c r="AQ5" s="1">
+        <v>0</v>
+      </c>
+      <c r="AR5" s="1">
+        <v>0</v>
+      </c>
+      <c r="AS5" s="1">
+        <v>0</v>
+      </c>
+      <c r="AT5" s="1">
+        <v>0</v>
+      </c>
+      <c r="AU5" s="1">
+        <v>0</v>
+      </c>
+      <c r="AV5" s="1">
+        <v>0</v>
+      </c>
+      <c r="AW5" s="1">
+        <v>0</v>
+      </c>
+      <c r="AX5" s="1">
+        <v>0</v>
+      </c>
+      <c r="AY5" s="1">
+        <v>0</v>
+      </c>
+      <c r="AZ5" s="1">
+        <v>0</v>
+      </c>
+      <c r="BA5" s="1">
+        <v>0</v>
+      </c>
+      <c r="BB5" s="1">
+        <v>0</v>
+      </c>
+      <c r="BC5" s="1">
+        <v>0</v>
+      </c>
+      <c r="BD5" s="1">
+        <v>0</v>
+      </c>
+      <c r="BE5" s="1">
+        <v>0</v>
+      </c>
+      <c r="BF5" s="1">
+        <v>0</v>
+      </c>
+      <c r="BG5" s="1">
+        <v>0</v>
+      </c>
+      <c r="BH5" s="1">
+        <v>0</v>
+      </c>
+      <c r="BI5" s="1">
+        <v>0</v>
+      </c>
+      <c r="BJ5" s="1">
+        <v>0</v>
+      </c>
+      <c r="BK5" s="1">
+        <v>0</v>
+      </c>
+      <c r="BL5" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:64">
+      <c r="A6" s="1">
+        <v>0</v>
+      </c>
+      <c r="B6" s="1">
+        <v>0</v>
+      </c>
+      <c r="C6" s="1">
+        <v>0</v>
+      </c>
+      <c r="D6" s="1">
+        <v>0</v>
+      </c>
+      <c r="E6" s="1">
+        <v>0</v>
+      </c>
+      <c r="F6" s="1">
+        <v>0</v>
+      </c>
+      <c r="G6" s="1">
+        <v>0</v>
+      </c>
+      <c r="H6" s="1">
+        <v>0</v>
+      </c>
+      <c r="I6" s="1">
+        <v>0</v>
+      </c>
+      <c r="J6" s="1">
+        <v>0</v>
+      </c>
+      <c r="K6" s="1">
+        <v>0</v>
+      </c>
+      <c r="L6" s="1">
+        <v>0</v>
+      </c>
+      <c r="M6" s="1">
+        <v>0</v>
+      </c>
+      <c r="N6" s="1">
+        <v>0</v>
+      </c>
+      <c r="O6" s="1">
+        <v>0</v>
+      </c>
+      <c r="P6" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="1">
+        <v>0</v>
+      </c>
+      <c r="R6" s="1">
+        <v>0</v>
+      </c>
+      <c r="S6" s="1">
+        <v>0</v>
+      </c>
+      <c r="T6" s="1">
+        <v>0</v>
+      </c>
+      <c r="U6" s="1">
+        <v>1</v>
+      </c>
+      <c r="V6" s="1">
+        <v>0</v>
+      </c>
+      <c r="W6" s="1">
+        <v>0</v>
+      </c>
+      <c r="X6" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z6" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB6" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC6" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD6" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE6" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF6" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG6" s="1">
+        <v>0</v>
+      </c>
+      <c r="AH6" s="1">
+        <v>0</v>
+      </c>
+      <c r="AI6" s="1">
+        <v>0</v>
+      </c>
+      <c r="AJ6" s="1">
+        <v>0</v>
+      </c>
+      <c r="AK6" s="1">
+        <v>0</v>
+      </c>
+      <c r="AL6" s="1">
+        <v>0</v>
+      </c>
+      <c r="AM6" s="1">
+        <v>0</v>
+      </c>
+      <c r="AN6" s="1">
+        <v>0</v>
+      </c>
+      <c r="AO6" s="1">
+        <v>0</v>
+      </c>
+      <c r="AP6" s="1">
+        <v>0</v>
+      </c>
+      <c r="AQ6" s="1">
+        <v>0</v>
+      </c>
+      <c r="AR6" s="1">
+        <v>0</v>
+      </c>
+      <c r="AS6" s="1">
+        <v>0</v>
+      </c>
+      <c r="AT6" s="1">
+        <v>0</v>
+      </c>
+      <c r="AU6" s="1">
+        <v>0</v>
+      </c>
+      <c r="AV6" s="1">
+        <v>0</v>
+      </c>
+      <c r="AW6" s="1">
+        <v>0</v>
+      </c>
+      <c r="AX6" s="1">
+        <v>0</v>
+      </c>
+      <c r="AY6" s="1">
+        <v>0</v>
+      </c>
+      <c r="AZ6" s="1">
+        <v>0</v>
+      </c>
+      <c r="BA6" s="1">
+        <v>0</v>
+      </c>
+      <c r="BB6" s="1">
+        <v>0</v>
+      </c>
+      <c r="BC6" s="1">
+        <v>0</v>
+      </c>
+      <c r="BD6" s="1">
+        <v>0</v>
+      </c>
+      <c r="BE6" s="1">
+        <v>0</v>
+      </c>
+      <c r="BF6" s="1">
+        <v>0</v>
+      </c>
+      <c r="BG6" s="1">
+        <v>0</v>
+      </c>
+      <c r="BH6" s="1">
+        <v>0</v>
+      </c>
+      <c r="BI6" s="1">
+        <v>0</v>
+      </c>
+      <c r="BJ6" s="1">
+        <v>0</v>
+      </c>
+      <c r="BK6" s="1">
+        <v>0</v>
+      </c>
+      <c r="BL6" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:64">
+      <c r="A7" s="1">
+        <v>0</v>
+      </c>
+      <c r="B7" s="1">
+        <v>0</v>
+      </c>
+      <c r="C7" s="1">
+        <v>0</v>
+      </c>
+      <c r="D7" s="1">
+        <v>0</v>
+      </c>
+      <c r="E7" s="1">
+        <v>0</v>
+      </c>
+      <c r="F7" s="1">
+        <v>0</v>
+      </c>
+      <c r="G7" s="1">
+        <v>0</v>
+      </c>
+      <c r="H7" s="1">
+        <v>0</v>
+      </c>
+      <c r="I7" s="1">
+        <v>0</v>
+      </c>
+      <c r="J7" s="1">
+        <v>0</v>
+      </c>
+      <c r="K7" s="1">
+        <v>0</v>
+      </c>
+      <c r="L7" s="1">
+        <v>0</v>
+      </c>
+      <c r="M7" s="1">
+        <v>0</v>
+      </c>
+      <c r="N7" s="1">
+        <v>0</v>
+      </c>
+      <c r="O7" s="1">
+        <v>0</v>
+      </c>
+      <c r="P7" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="1">
+        <v>0</v>
+      </c>
+      <c r="R7" s="1">
+        <v>0</v>
+      </c>
+      <c r="S7" s="1">
+        <v>0</v>
+      </c>
+      <c r="T7" s="1">
+        <v>0</v>
+      </c>
+      <c r="U7" s="1">
+        <v>1</v>
+      </c>
+      <c r="V7" s="1">
+        <v>0</v>
+      </c>
+      <c r="W7" s="1">
+        <v>0</v>
+      </c>
+      <c r="X7" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z7" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA7" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB7" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC7" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD7" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE7" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF7" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG7" s="1">
+        <v>0</v>
+      </c>
+      <c r="AH7" s="1">
+        <v>0</v>
+      </c>
+      <c r="AI7" s="1">
+        <v>0</v>
+      </c>
+      <c r="AJ7" s="1">
+        <v>0</v>
+      </c>
+      <c r="AK7" s="1">
+        <v>0</v>
+      </c>
+      <c r="AL7" s="1">
+        <v>0</v>
+      </c>
+      <c r="AM7" s="1">
+        <v>0</v>
+      </c>
+      <c r="AN7" s="1">
+        <v>0</v>
+      </c>
+      <c r="AO7" s="1">
+        <v>0</v>
+      </c>
+      <c r="AP7" s="1">
+        <v>0</v>
+      </c>
+      <c r="AQ7" s="1">
+        <v>0</v>
+      </c>
+      <c r="AR7" s="1">
+        <v>0</v>
+      </c>
+      <c r="AS7" s="1">
+        <v>0</v>
+      </c>
+      <c r="AT7" s="1">
+        <v>0</v>
+      </c>
+      <c r="AU7" s="1">
+        <v>0</v>
+      </c>
+      <c r="AV7" s="1">
+        <v>0</v>
+      </c>
+      <c r="AW7" s="1">
+        <v>0</v>
+      </c>
+      <c r="AX7" s="1">
+        <v>0</v>
+      </c>
+      <c r="AY7" s="1">
+        <v>0</v>
+      </c>
+      <c r="AZ7" s="1">
+        <v>0</v>
+      </c>
+      <c r="BA7" s="1">
+        <v>0</v>
+      </c>
+      <c r="BB7" s="1">
+        <v>0</v>
+      </c>
+      <c r="BC7" s="1">
+        <v>0</v>
+      </c>
+      <c r="BD7" s="1">
+        <v>0</v>
+      </c>
+      <c r="BE7" s="1">
+        <v>0</v>
+      </c>
+      <c r="BF7" s="1">
+        <v>0</v>
+      </c>
+      <c r="BG7" s="1">
+        <v>0</v>
+      </c>
+      <c r="BH7" s="1">
+        <v>0</v>
+      </c>
+      <c r="BI7" s="1">
+        <v>0</v>
+      </c>
+      <c r="BJ7" s="1">
+        <v>0</v>
+      </c>
+      <c r="BK7" s="1">
+        <v>0</v>
+      </c>
+      <c r="BL7" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:64">
+      <c r="A8" s="1">
+        <v>0</v>
+      </c>
+      <c r="B8" s="1">
+        <v>0</v>
+      </c>
+      <c r="C8" s="1">
+        <v>0</v>
+      </c>
+      <c r="D8" s="1">
+        <v>0</v>
+      </c>
+      <c r="E8" s="1">
+        <v>0</v>
+      </c>
+      <c r="F8" s="1">
+        <v>0</v>
+      </c>
+      <c r="G8" s="1">
+        <v>0</v>
+      </c>
+      <c r="H8" s="1">
+        <v>0</v>
+      </c>
+      <c r="I8" s="1">
+        <v>0</v>
+      </c>
+      <c r="J8" s="1">
+        <v>0</v>
+      </c>
+      <c r="K8" s="1">
+        <v>0</v>
+      </c>
+      <c r="L8" s="1">
+        <v>0</v>
+      </c>
+      <c r="M8" s="1">
+        <v>0</v>
+      </c>
+      <c r="N8" s="1">
+        <v>0</v>
+      </c>
+      <c r="O8" s="1">
+        <v>0</v>
+      </c>
+      <c r="P8" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="1">
+        <v>0</v>
+      </c>
+      <c r="R8" s="1">
+        <v>0</v>
+      </c>
+      <c r="S8" s="1">
+        <v>0</v>
+      </c>
+      <c r="T8" s="1">
+        <v>0</v>
+      </c>
+      <c r="U8" s="1">
+        <v>1</v>
+      </c>
+      <c r="V8" s="1">
+        <v>0</v>
+      </c>
+      <c r="W8" s="1">
+        <v>0</v>
+      </c>
+      <c r="X8" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z8" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA8" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB8" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC8" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD8" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE8" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF8" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG8" s="1">
+        <v>0</v>
+      </c>
+      <c r="AH8" s="1">
+        <v>0</v>
+      </c>
+      <c r="AI8" s="1">
+        <v>0</v>
+      </c>
+      <c r="AJ8" s="1">
+        <v>0</v>
+      </c>
+      <c r="AK8" s="1">
+        <v>0</v>
+      </c>
+      <c r="AL8" s="1">
+        <v>0</v>
+      </c>
+      <c r="AM8" s="1">
+        <v>0</v>
+      </c>
+      <c r="AN8" s="1">
+        <v>0</v>
+      </c>
+      <c r="AO8" s="1">
+        <v>0</v>
+      </c>
+      <c r="AP8" s="1">
+        <v>0</v>
+      </c>
+      <c r="AQ8" s="1">
+        <v>0</v>
+      </c>
+      <c r="AR8" s="1">
+        <v>0</v>
+      </c>
+      <c r="AS8" s="1">
+        <v>0</v>
+      </c>
+      <c r="AT8" s="1">
+        <v>0</v>
+      </c>
+      <c r="AU8" s="1">
+        <v>0</v>
+      </c>
+      <c r="AV8" s="1">
+        <v>0</v>
+      </c>
+      <c r="AW8" s="1">
+        <v>0</v>
+      </c>
+      <c r="AX8" s="1">
+        <v>0</v>
+      </c>
+      <c r="AY8" s="1">
+        <v>0</v>
+      </c>
+      <c r="AZ8" s="1">
+        <v>0</v>
+      </c>
+      <c r="BA8" s="1">
+        <v>0</v>
+      </c>
+      <c r="BB8" s="1">
+        <v>0</v>
+      </c>
+      <c r="BC8" s="1">
+        <v>0</v>
+      </c>
+      <c r="BD8" s="1">
+        <v>0</v>
+      </c>
+      <c r="BE8" s="1">
+        <v>0</v>
+      </c>
+      <c r="BF8" s="1">
+        <v>0</v>
+      </c>
+      <c r="BG8" s="1">
+        <v>0</v>
+      </c>
+      <c r="BH8" s="1">
+        <v>0</v>
+      </c>
+      <c r="BI8" s="1">
+        <v>0</v>
+      </c>
+      <c r="BJ8" s="1">
+        <v>0</v>
+      </c>
+      <c r="BK8" s="1">
+        <v>0</v>
+      </c>
+      <c r="BL8" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:64">
+      <c r="A9" s="1">
+        <v>0</v>
+      </c>
+      <c r="B9" s="1">
+        <v>0</v>
+      </c>
+      <c r="C9" s="1">
+        <v>0</v>
+      </c>
+      <c r="D9" s="1">
+        <v>0</v>
+      </c>
+      <c r="E9" s="1">
+        <v>0</v>
+      </c>
+      <c r="F9" s="1">
+        <v>0</v>
+      </c>
+      <c r="G9" s="1">
+        <v>0</v>
+      </c>
+      <c r="H9" s="1">
+        <v>0</v>
+      </c>
+      <c r="I9" s="1">
+        <v>0</v>
+      </c>
+      <c r="J9" s="1">
+        <v>0</v>
+      </c>
+      <c r="K9" s="1">
+        <v>0</v>
+      </c>
+      <c r="L9" s="1">
+        <v>0</v>
+      </c>
+      <c r="M9" s="1">
+        <v>0</v>
+      </c>
+      <c r="N9" s="1">
+        <v>0</v>
+      </c>
+      <c r="O9" s="1">
+        <v>0</v>
+      </c>
+      <c r="P9" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="1">
+        <v>0</v>
+      </c>
+      <c r="R9" s="1">
+        <v>0</v>
+      </c>
+      <c r="S9" s="1">
+        <v>0</v>
+      </c>
+      <c r="T9" s="1">
+        <v>0</v>
+      </c>
+      <c r="U9" s="1">
+        <v>1</v>
+      </c>
+      <c r="V9" s="1">
+        <v>0</v>
+      </c>
+      <c r="W9" s="1">
+        <v>0</v>
+      </c>
+      <c r="X9" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z9" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA9" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB9" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC9" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD9" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE9" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF9" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG9" s="1">
+        <v>0</v>
+      </c>
+      <c r="AH9" s="1">
+        <v>0</v>
+      </c>
+      <c r="AI9" s="1">
+        <v>0</v>
+      </c>
+      <c r="AJ9" s="1">
+        <v>0</v>
+      </c>
+      <c r="AK9" s="1">
+        <v>0</v>
+      </c>
+      <c r="AL9" s="1">
+        <v>0</v>
+      </c>
+      <c r="AM9" s="1">
+        <v>0</v>
+      </c>
+      <c r="AN9" s="1">
+        <v>0</v>
+      </c>
+      <c r="AO9" s="1">
+        <v>0</v>
+      </c>
+      <c r="AP9" s="1">
+        <v>0</v>
+      </c>
+      <c r="AQ9" s="1">
+        <v>0</v>
+      </c>
+      <c r="AR9" s="1">
+        <v>0</v>
+      </c>
+      <c r="AS9" s="1">
+        <v>0</v>
+      </c>
+      <c r="AT9" s="1">
+        <v>0</v>
+      </c>
+      <c r="AU9" s="1">
+        <v>0</v>
+      </c>
+      <c r="AV9" s="1">
+        <v>0</v>
+      </c>
+      <c r="AW9" s="1">
+        <v>0</v>
+      </c>
+      <c r="AX9" s="1">
+        <v>0</v>
+      </c>
+      <c r="AY9" s="1">
+        <v>0</v>
+      </c>
+      <c r="AZ9" s="1">
+        <v>0</v>
+      </c>
+      <c r="BA9" s="1">
+        <v>0</v>
+      </c>
+      <c r="BB9" s="1">
+        <v>0</v>
+      </c>
+      <c r="BC9" s="1">
+        <v>0</v>
+      </c>
+      <c r="BD9" s="1">
+        <v>0</v>
+      </c>
+      <c r="BE9" s="1">
+        <v>0</v>
+      </c>
+      <c r="BF9" s="1">
+        <v>0</v>
+      </c>
+      <c r="BG9" s="1">
+        <v>0</v>
+      </c>
+      <c r="BH9" s="1">
+        <v>0</v>
+      </c>
+      <c r="BI9" s="1">
+        <v>0</v>
+      </c>
+      <c r="BJ9" s="1">
+        <v>0</v>
+      </c>
+      <c r="BK9" s="1">
+        <v>0</v>
+      </c>
+      <c r="BL9" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:64">
+      <c r="A10" s="1">
+        <v>0</v>
+      </c>
+      <c r="B10" s="1">
+        <v>0</v>
+      </c>
+      <c r="C10" s="1">
+        <v>0</v>
+      </c>
+      <c r="D10" s="1">
+        <v>0</v>
+      </c>
+      <c r="E10" s="1">
+        <v>0</v>
+      </c>
+      <c r="F10" s="1">
+        <v>0</v>
+      </c>
+      <c r="G10" s="1">
+        <v>0</v>
+      </c>
+      <c r="H10" s="1">
+        <v>0</v>
+      </c>
+      <c r="I10" s="1">
+        <v>0</v>
+      </c>
+      <c r="J10" s="1">
+        <v>0</v>
+      </c>
+      <c r="K10" s="1">
+        <v>0</v>
+      </c>
+      <c r="L10" s="1">
+        <v>0</v>
+      </c>
+      <c r="M10" s="1">
+        <v>0</v>
+      </c>
+      <c r="N10" s="1">
+        <v>0</v>
+      </c>
+      <c r="O10" s="1">
+        <v>0</v>
+      </c>
+      <c r="P10" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="1">
+        <v>0</v>
+      </c>
+      <c r="R10" s="1">
+        <v>0</v>
+      </c>
+      <c r="S10" s="1">
+        <v>0</v>
+      </c>
+      <c r="T10" s="1">
+        <v>0</v>
+      </c>
+      <c r="U10" s="1">
+        <v>0</v>
+      </c>
+      <c r="V10" s="1">
+        <v>0</v>
+      </c>
+      <c r="W10" s="1">
+        <v>0</v>
+      </c>
+      <c r="X10" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y10" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z10" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA10" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB10" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC10" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD10" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE10" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF10" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG10" s="1">
+        <v>0</v>
+      </c>
+      <c r="AH10" s="1">
+        <v>0</v>
+      </c>
+      <c r="AI10" s="1">
+        <v>0</v>
+      </c>
+      <c r="AJ10" s="1">
+        <v>0</v>
+      </c>
+      <c r="AK10" s="1">
+        <v>0</v>
+      </c>
+      <c r="AL10" s="1">
+        <v>0</v>
+      </c>
+      <c r="AM10" s="1">
+        <v>0</v>
+      </c>
+      <c r="AN10" s="1">
+        <v>0</v>
+      </c>
+      <c r="AO10" s="1">
+        <v>0</v>
+      </c>
+      <c r="AP10" s="1">
+        <v>0</v>
+      </c>
+      <c r="AQ10" s="1">
+        <v>0</v>
+      </c>
+      <c r="AR10" s="1">
+        <v>0</v>
+      </c>
+      <c r="AS10" s="1">
+        <v>0</v>
+      </c>
+      <c r="AT10" s="1">
+        <v>0</v>
+      </c>
+      <c r="AU10" s="1">
+        <v>0</v>
+      </c>
+      <c r="AV10" s="1">
+        <v>0</v>
+      </c>
+      <c r="AW10" s="1">
+        <v>0</v>
+      </c>
+      <c r="AX10" s="1">
+        <v>0</v>
+      </c>
+      <c r="AY10" s="1">
+        <v>0</v>
+      </c>
+      <c r="AZ10" s="1">
+        <v>0</v>
+      </c>
+      <c r="BA10" s="1">
+        <v>0</v>
+      </c>
+      <c r="BB10" s="1">
+        <v>0</v>
+      </c>
+      <c r="BC10" s="1">
+        <v>0</v>
+      </c>
+      <c r="BD10" s="1">
+        <v>0</v>
+      </c>
+      <c r="BE10" s="1">
+        <v>0</v>
+      </c>
+      <c r="BF10" s="1">
+        <v>0</v>
+      </c>
+      <c r="BG10" s="1">
+        <v>0</v>
+      </c>
+      <c r="BH10" s="1">
+        <v>0</v>
+      </c>
+      <c r="BI10" s="1">
+        <v>0</v>
+      </c>
+      <c r="BJ10" s="1">
+        <v>0</v>
+      </c>
+      <c r="BK10" s="1">
+        <v>0</v>
+      </c>
+      <c r="BL10" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:64">
+      <c r="A11" s="2">
+        <v>2</v>
+      </c>
+      <c r="B11" s="2">
+        <v>2</v>
+      </c>
+      <c r="C11" s="2">
+        <v>2</v>
+      </c>
+      <c r="D11" s="2">
+        <v>2</v>
+      </c>
+      <c r="E11" s="2">
+        <v>2</v>
+      </c>
+      <c r="F11" s="2">
+        <v>2</v>
+      </c>
+      <c r="G11" s="2">
+        <v>2</v>
+      </c>
+      <c r="H11" s="2">
+        <v>2</v>
+      </c>
+      <c r="I11" s="2">
+        <v>2</v>
+      </c>
+      <c r="J11" s="2">
+        <v>2</v>
+      </c>
+      <c r="K11" s="2">
+        <v>2</v>
+      </c>
+      <c r="L11" s="2">
+        <v>2</v>
+      </c>
+      <c r="M11" s="2">
+        <v>2</v>
+      </c>
+      <c r="N11" s="2">
+        <v>2</v>
+      </c>
+      <c r="O11" s="2">
+        <v>2</v>
+      </c>
+      <c r="P11" s="2">
+        <v>2</v>
+      </c>
+      <c r="Q11" s="2">
+        <v>2</v>
+      </c>
+      <c r="R11" s="2">
+        <v>2</v>
+      </c>
+      <c r="S11" s="2">
+        <v>2</v>
+      </c>
+      <c r="T11" s="2">
+        <v>2</v>
+      </c>
+      <c r="U11" s="2">
+        <v>2</v>
+      </c>
+      <c r="V11" s="2">
+        <v>2</v>
+      </c>
+      <c r="W11" s="2">
+        <v>2</v>
+      </c>
+      <c r="X11" s="2">
+        <v>2</v>
+      </c>
+      <c r="Y11" s="2">
+        <v>2</v>
+      </c>
+      <c r="Z11" s="2">
+        <v>2</v>
+      </c>
+      <c r="AA11" s="2">
+        <v>2</v>
+      </c>
+      <c r="AB11" s="2">
+        <v>2</v>
+      </c>
+      <c r="AC11" s="2">
+        <v>2</v>
+      </c>
+      <c r="AD11" s="2">
+        <v>2</v>
+      </c>
+      <c r="AE11" s="2">
+        <v>2</v>
+      </c>
+      <c r="AF11" s="2">
+        <v>2</v>
+      </c>
+      <c r="AG11" s="2">
+        <v>2</v>
+      </c>
+      <c r="AH11" s="2">
+        <v>2</v>
+      </c>
+      <c r="AI11" s="2">
+        <v>2</v>
+      </c>
+      <c r="AJ11" s="2">
+        <v>2</v>
+      </c>
+      <c r="AK11" s="2">
+        <v>2</v>
+      </c>
+      <c r="AL11" s="2">
+        <v>2</v>
+      </c>
+      <c r="AM11" s="2">
+        <v>2</v>
+      </c>
+      <c r="AN11" s="2">
+        <v>2</v>
+      </c>
+      <c r="AO11" s="2">
+        <v>2</v>
+      </c>
+      <c r="AP11" s="2">
+        <v>2</v>
+      </c>
+      <c r="AQ11" s="2">
+        <v>2</v>
+      </c>
+      <c r="AR11" s="2">
+        <v>2</v>
+      </c>
+      <c r="AS11" s="2">
+        <v>2</v>
+      </c>
+      <c r="AT11" s="2">
+        <v>2</v>
+      </c>
+      <c r="AU11" s="2">
+        <v>2</v>
+      </c>
+      <c r="AV11" s="2">
+        <v>2</v>
+      </c>
+      <c r="AW11" s="2">
+        <v>2</v>
+      </c>
+      <c r="AX11" s="2">
+        <v>2</v>
+      </c>
+      <c r="AY11" s="2">
+        <v>2</v>
+      </c>
+      <c r="AZ11" s="2">
+        <v>2</v>
+      </c>
+      <c r="BA11" s="2">
+        <v>2</v>
+      </c>
+      <c r="BB11" s="2">
+        <v>2</v>
+      </c>
+      <c r="BC11" s="2">
+        <v>2</v>
+      </c>
+      <c r="BD11" s="2">
+        <v>2</v>
+      </c>
+      <c r="BE11" s="2">
+        <v>2</v>
+      </c>
+      <c r="BF11" s="2">
+        <v>2</v>
+      </c>
+      <c r="BG11" s="2">
+        <v>2</v>
+      </c>
+      <c r="BH11" s="2">
+        <v>2</v>
+      </c>
+      <c r="BI11" s="2">
+        <v>2</v>
+      </c>
+      <c r="BJ11" s="2">
+        <v>2</v>
+      </c>
+      <c r="BK11" s="2">
+        <v>2</v>
+      </c>
+      <c r="BL11" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:64">
+      <c r="A12" s="3">
+        <v>1</v>
+      </c>
+      <c r="B12" s="3">
+        <v>1</v>
+      </c>
+      <c r="C12" s="3">
+        <v>1</v>
+      </c>
+      <c r="D12" s="3">
+        <v>1</v>
+      </c>
+      <c r="E12" s="3">
+        <v>1</v>
+      </c>
+      <c r="F12" s="3">
+        <v>1</v>
+      </c>
+      <c r="G12" s="3">
+        <v>1</v>
+      </c>
+      <c r="H12" s="3">
+        <v>1</v>
+      </c>
+      <c r="I12" s="3">
+        <v>1</v>
+      </c>
+      <c r="J12" s="3">
+        <v>1</v>
+      </c>
+      <c r="K12" s="3">
+        <v>1</v>
+      </c>
+      <c r="L12" s="3">
+        <v>1</v>
+      </c>
+      <c r="M12" s="3">
+        <v>1</v>
+      </c>
+      <c r="N12" s="3">
+        <v>1</v>
+      </c>
+      <c r="O12" s="3">
+        <v>1</v>
+      </c>
+      <c r="P12" s="3">
+        <v>1</v>
+      </c>
+      <c r="Q12" s="3">
+        <v>1</v>
+      </c>
+      <c r="R12" s="3">
+        <v>1</v>
+      </c>
+      <c r="S12" s="3">
+        <v>1</v>
+      </c>
+      <c r="T12" s="3">
+        <v>1</v>
+      </c>
+      <c r="U12" s="3">
+        <v>1</v>
+      </c>
+      <c r="V12" s="3">
+        <v>1</v>
+      </c>
+      <c r="W12" s="3">
+        <v>1</v>
+      </c>
+      <c r="X12" s="3">
+        <v>1</v>
+      </c>
+      <c r="Y12" s="3">
+        <v>1</v>
+      </c>
+      <c r="Z12" s="3">
+        <v>1</v>
+      </c>
+      <c r="AA12" s="3">
+        <v>1</v>
+      </c>
+      <c r="AB12" s="3">
+        <v>1</v>
+      </c>
+      <c r="AC12" s="3">
+        <v>1</v>
+      </c>
+      <c r="AD12" s="3">
+        <v>1</v>
+      </c>
+      <c r="AE12" s="3">
+        <v>1</v>
+      </c>
+      <c r="AF12" s="3">
+        <v>1</v>
+      </c>
+      <c r="AG12" s="3">
+        <v>1</v>
+      </c>
+      <c r="AH12" s="3">
+        <v>1</v>
+      </c>
+      <c r="AI12" s="3">
+        <v>1</v>
+      </c>
+      <c r="AJ12" s="3">
+        <v>1</v>
+      </c>
+      <c r="AK12" s="3">
+        <v>1</v>
+      </c>
+      <c r="AL12" s="3">
+        <v>1</v>
+      </c>
+      <c r="AM12" s="3">
+        <v>1</v>
+      </c>
+      <c r="AN12" s="3">
+        <v>1</v>
+      </c>
+      <c r="AO12" s="3">
+        <v>1</v>
+      </c>
+      <c r="AP12" s="3">
+        <v>1</v>
+      </c>
+      <c r="AQ12" s="3">
+        <v>1</v>
+      </c>
+      <c r="AR12" s="3">
+        <v>1</v>
+      </c>
+      <c r="AS12" s="3">
+        <v>1</v>
+      </c>
+      <c r="AT12" s="3">
+        <v>1</v>
+      </c>
+      <c r="AU12" s="3">
+        <v>1</v>
+      </c>
+      <c r="AV12" s="3">
+        <v>1</v>
+      </c>
+      <c r="AW12" s="3">
+        <v>1</v>
+      </c>
+      <c r="AX12" s="3">
+        <v>1</v>
+      </c>
+      <c r="AY12" s="3">
+        <v>1</v>
+      </c>
+      <c r="AZ12" s="3">
+        <v>1</v>
+      </c>
+      <c r="BA12" s="3">
+        <v>1</v>
+      </c>
+      <c r="BB12" s="3">
+        <v>1</v>
+      </c>
+      <c r="BC12" s="3">
+        <v>1</v>
+      </c>
+      <c r="BD12" s="3">
+        <v>1</v>
+      </c>
+      <c r="BE12" s="3">
+        <v>1</v>
+      </c>
+      <c r="BF12" s="3">
+        <v>1</v>
+      </c>
+      <c r="BG12" s="3">
+        <v>1</v>
+      </c>
+      <c r="BH12" s="3">
+        <v>1</v>
+      </c>
+      <c r="BI12" s="3">
+        <v>1</v>
+      </c>
+      <c r="BJ12" s="3">
+        <v>1</v>
+      </c>
+      <c r="BK12" s="3">
+        <v>1</v>
+      </c>
+      <c r="BL12" s="3">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8ECD2F2A-5FF6-491E-9BB3-D819CA18D9B7}">
   <dimension ref="A1:AF12"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="32" width="3.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:32">
       <c r="A1">
         <v>0</v>
       </c>
@@ -1749,7 +5287,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:32">
       <c r="A2">
         <v>0</v>
       </c>
@@ -1847,7 +5385,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:32">
       <c r="A3">
         <v>0</v>
       </c>
@@ -1945,7 +5483,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:32">
       <c r="A4">
         <v>0</v>
       </c>
@@ -2043,7 +5581,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:32">
       <c r="A5">
         <v>0</v>
       </c>
@@ -2141,7 +5679,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:32">
       <c r="A6">
         <v>0</v>
       </c>
@@ -2239,7 +5777,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:32">
       <c r="A7">
         <v>0</v>
       </c>
@@ -2337,7 +5875,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:32">
       <c r="A8">
         <v>0</v>
       </c>
@@ -2435,7 +5973,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:32">
       <c r="A9">
         <v>0</v>
       </c>
@@ -2533,7 +6071,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:32">
       <c r="A10">
         <v>0</v>
       </c>
@@ -2631,7 +6169,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:32">
       <c r="A11">
         <v>2</v>
       </c>
@@ -2729,7 +6267,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:32">
       <c r="A12">
         <v>1</v>
       </c>

--- a/Src/Map/MapData/Map.xlsx
+++ b/Src/Map/MapData/Map.xlsx
@@ -5,17 +5,18 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ゲーム開発1\TeamDevlop\Src\Map\MapData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ゲーム開発1\チーム確認用\Src\Map\MapData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B32B6396-4751-445E-81D6-3BCA34749958}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0E3319B-04C3-4725-AF24-9FCEDF5D959A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{53B5AEAB-04AE-4965-81BC-49E785C84905}"/>
+    <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11295" activeTab="3" xr2:uid="{53B5AEAB-04AE-4965-81BC-49E785C84905}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="3" r:id="rId1"/>
+    <sheet name="SelectStage(Stage0)" sheetId="3" r:id="rId1"/>
     <sheet name="Stage1" sheetId="1" r:id="rId2"/>
     <sheet name="Stage2" sheetId="2" r:id="rId3"/>
+    <sheet name="TestStagte(Stage10)" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,10 +39,6 @@
     </ext>
   </extLst>
 </workbook>
-</file>
-
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -132,37 +129,86 @@
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="10">
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FF00B050"/>
+          <bgColor rgb="FF92D050"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="5"/>
+          <bgColor rgb="FF993300"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="5"/>
+          <bgColor rgb="FF92D050"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="9"/>
+          <bgColor rgb="FF993300"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor auto="1"/>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor auto="1"/>
+          <bgColor rgb="FF993300"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF993300"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
         </patternFill>
       </fill>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FF993300"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -172,6 +218,123 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>33</xdr:col>
+      <xdr:colOff>145676</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>190499</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>42</xdr:col>
+      <xdr:colOff>100852</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>100851</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="正方形/長方形 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A808B614-AB55-C678-B90A-D1CC287459F2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9760323" y="661146"/>
+          <a:ext cx="2577353" cy="2498911"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1600"/>
+            <a:t>0:</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1600"/>
+            <a:t>なし</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1600"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1600"/>
+            <a:t>1:</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1600"/>
+            <a:t>つち</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1600"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1600"/>
+            <a:t>2:</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1600"/>
+            <a:t>くさ</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1600"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1600"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1600"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1600"/>
+            <a:t>10;stage1</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1600"/>
+            <a:t>11:stage2</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1726,7 +1889,7 @@
         <v>0</v>
       </c>
       <c r="V7" s="1">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="W7" s="1">
         <v>0</v>
@@ -1911,7 +2074,7 @@
         <v>0</v>
       </c>
       <c r="S8" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T8" s="1">
         <v>2</v>
@@ -2090,7 +2253,7 @@
         <v>0</v>
       </c>
       <c r="N9" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O9" s="1">
         <v>0</v>
@@ -2290,7 +2453,7 @@
         <v>2</v>
       </c>
       <c r="P10" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q10" s="1">
         <v>0</v>
@@ -2484,7 +2647,7 @@
         <v>1</v>
       </c>
       <c r="P11" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q11" s="2">
         <v>2</v>
@@ -2828,14 +2991,21 @@
   </sheetData>
   <phoneticPr fontId="1"/>
   <conditionalFormatting sqref="A1:BL12">
-    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="1" operator="equal">
+      <formula>10</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="8" priority="2" operator="equal">
+      <formula>11</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="7" priority="3" operator="equal">
       <formula>2</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="4" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -3297,7 +3467,7 @@
         <v>0</v>
       </c>
       <c r="U3" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V3" s="1">
         <v>0</v>
@@ -3491,7 +3661,7 @@
         <v>0</v>
       </c>
       <c r="U4" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V4" s="1">
         <v>0</v>
@@ -3685,7 +3855,7 @@
         <v>0</v>
       </c>
       <c r="U5" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V5" s="1">
         <v>0</v>
@@ -3879,7 +4049,7 @@
         <v>0</v>
       </c>
       <c r="U6" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V6" s="1">
         <v>0</v>
@@ -3930,13 +4100,13 @@
         <v>0</v>
       </c>
       <c r="AL6" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM6" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AN6" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AO6" s="1">
         <v>0</v>
@@ -4073,7 +4243,7 @@
         <v>0</v>
       </c>
       <c r="U7" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V7" s="1">
         <v>0</v>
@@ -4124,13 +4294,13 @@
         <v>0</v>
       </c>
       <c r="AL7" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM7" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN7" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO7" s="1">
         <v>0</v>
@@ -4267,7 +4437,7 @@
         <v>0</v>
       </c>
       <c r="U8" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V8" s="1">
         <v>0</v>
@@ -4300,13 +4470,13 @@
         <v>0</v>
       </c>
       <c r="AF8" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG8" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH8" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AI8" s="1">
         <v>0</v>
@@ -4318,13 +4488,13 @@
         <v>0</v>
       </c>
       <c r="AL8" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM8" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN8" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO8" s="1">
         <v>0</v>
@@ -4461,7 +4631,7 @@
         <v>0</v>
       </c>
       <c r="U9" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V9" s="1">
         <v>0</v>
@@ -4512,13 +4682,13 @@
         <v>0</v>
       </c>
       <c r="AL9" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM9" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN9" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO9" s="1">
         <v>0</v>
@@ -4658,28 +4828,28 @@
         <v>0</v>
       </c>
       <c r="V10" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W10" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X10" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y10" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z10" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA10" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB10" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC10" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD10" s="1">
         <v>0</v>
@@ -4706,13 +4876,13 @@
         <v>0</v>
       </c>
       <c r="AL10" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM10" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN10" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO10" s="1">
         <v>0</v>
@@ -4788,408 +4958,416 @@
       </c>
     </row>
     <row r="11" spans="1:64">
-      <c r="A11" s="2">
-        <v>2</v>
-      </c>
-      <c r="B11" s="2">
-        <v>2</v>
-      </c>
-      <c r="C11" s="2">
-        <v>2</v>
-      </c>
-      <c r="D11" s="2">
-        <v>2</v>
-      </c>
-      <c r="E11" s="2">
-        <v>2</v>
-      </c>
-      <c r="F11" s="2">
-        <v>2</v>
-      </c>
-      <c r="G11" s="2">
-        <v>2</v>
-      </c>
-      <c r="H11" s="2">
-        <v>2</v>
-      </c>
-      <c r="I11" s="2">
-        <v>2</v>
-      </c>
-      <c r="J11" s="2">
-        <v>2</v>
-      </c>
-      <c r="K11" s="2">
-        <v>2</v>
-      </c>
-      <c r="L11" s="2">
-        <v>2</v>
-      </c>
-      <c r="M11" s="2">
-        <v>2</v>
-      </c>
-      <c r="N11" s="2">
-        <v>2</v>
-      </c>
-      <c r="O11" s="2">
-        <v>2</v>
-      </c>
-      <c r="P11" s="2">
-        <v>2</v>
-      </c>
-      <c r="Q11" s="2">
-        <v>2</v>
-      </c>
-      <c r="R11" s="2">
-        <v>2</v>
-      </c>
-      <c r="S11" s="2">
-        <v>2</v>
-      </c>
-      <c r="T11" s="2">
-        <v>2</v>
-      </c>
-      <c r="U11" s="2">
-        <v>2</v>
-      </c>
-      <c r="V11" s="2">
-        <v>2</v>
-      </c>
-      <c r="W11" s="2">
-        <v>2</v>
-      </c>
-      <c r="X11" s="2">
-        <v>2</v>
-      </c>
-      <c r="Y11" s="2">
-        <v>2</v>
-      </c>
-      <c r="Z11" s="2">
-        <v>2</v>
-      </c>
-      <c r="AA11" s="2">
-        <v>2</v>
-      </c>
-      <c r="AB11" s="2">
-        <v>2</v>
-      </c>
-      <c r="AC11" s="2">
-        <v>2</v>
-      </c>
-      <c r="AD11" s="2">
-        <v>2</v>
-      </c>
-      <c r="AE11" s="2">
-        <v>2</v>
-      </c>
-      <c r="AF11" s="2">
-        <v>2</v>
-      </c>
-      <c r="AG11" s="2">
-        <v>2</v>
-      </c>
-      <c r="AH11" s="2">
-        <v>2</v>
-      </c>
-      <c r="AI11" s="2">
-        <v>2</v>
-      </c>
-      <c r="AJ11" s="2">
-        <v>2</v>
-      </c>
-      <c r="AK11" s="2">
-        <v>2</v>
-      </c>
-      <c r="AL11" s="2">
-        <v>2</v>
-      </c>
-      <c r="AM11" s="2">
-        <v>2</v>
-      </c>
-      <c r="AN11" s="2">
-        <v>2</v>
-      </c>
-      <c r="AO11" s="2">
-        <v>2</v>
-      </c>
-      <c r="AP11" s="2">
-        <v>2</v>
-      </c>
-      <c r="AQ11" s="2">
-        <v>2</v>
-      </c>
-      <c r="AR11" s="2">
-        <v>2</v>
-      </c>
-      <c r="AS11" s="2">
-        <v>2</v>
-      </c>
-      <c r="AT11" s="2">
-        <v>2</v>
-      </c>
-      <c r="AU11" s="2">
-        <v>2</v>
-      </c>
-      <c r="AV11" s="2">
-        <v>2</v>
-      </c>
-      <c r="AW11" s="2">
-        <v>2</v>
-      </c>
-      <c r="AX11" s="2">
-        <v>2</v>
-      </c>
-      <c r="AY11" s="2">
-        <v>2</v>
-      </c>
-      <c r="AZ11" s="2">
-        <v>2</v>
-      </c>
-      <c r="BA11" s="2">
-        <v>2</v>
-      </c>
-      <c r="BB11" s="2">
-        <v>2</v>
-      </c>
-      <c r="BC11" s="2">
-        <v>2</v>
-      </c>
-      <c r="BD11" s="2">
-        <v>2</v>
-      </c>
-      <c r="BE11" s="2">
-        <v>2</v>
-      </c>
-      <c r="BF11" s="2">
-        <v>2</v>
-      </c>
-      <c r="BG11" s="2">
-        <v>2</v>
-      </c>
-      <c r="BH11" s="2">
-        <v>2</v>
-      </c>
-      <c r="BI11" s="2">
-        <v>2</v>
-      </c>
-      <c r="BJ11" s="2">
-        <v>2</v>
-      </c>
-      <c r="BK11" s="2">
-        <v>2</v>
-      </c>
-      <c r="BL11" s="2">
+      <c r="A11" s="1">
+        <v>2</v>
+      </c>
+      <c r="B11" s="1">
+        <v>2</v>
+      </c>
+      <c r="C11" s="1">
+        <v>2</v>
+      </c>
+      <c r="D11" s="1">
+        <v>2</v>
+      </c>
+      <c r="E11" s="1">
+        <v>2</v>
+      </c>
+      <c r="F11" s="1">
+        <v>2</v>
+      </c>
+      <c r="G11" s="1">
+        <v>2</v>
+      </c>
+      <c r="H11" s="1">
+        <v>2</v>
+      </c>
+      <c r="I11" s="1">
+        <v>2</v>
+      </c>
+      <c r="J11" s="1">
+        <v>2</v>
+      </c>
+      <c r="K11" s="1">
+        <v>2</v>
+      </c>
+      <c r="L11" s="1">
+        <v>2</v>
+      </c>
+      <c r="M11" s="1">
+        <v>2</v>
+      </c>
+      <c r="N11" s="1">
+        <v>2</v>
+      </c>
+      <c r="O11" s="1">
+        <v>2</v>
+      </c>
+      <c r="P11" s="1">
+        <v>2</v>
+      </c>
+      <c r="Q11" s="1">
+        <v>2</v>
+      </c>
+      <c r="R11" s="1">
+        <v>2</v>
+      </c>
+      <c r="S11" s="1">
+        <v>2</v>
+      </c>
+      <c r="T11" s="1">
+        <v>2</v>
+      </c>
+      <c r="U11" s="1">
+        <v>2</v>
+      </c>
+      <c r="V11" s="1">
+        <v>1</v>
+      </c>
+      <c r="W11" s="1">
+        <v>1</v>
+      </c>
+      <c r="X11" s="1">
+        <v>1</v>
+      </c>
+      <c r="Y11" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z11" s="1">
+        <v>1</v>
+      </c>
+      <c r="AA11" s="1">
+        <v>1</v>
+      </c>
+      <c r="AB11" s="1">
+        <v>1</v>
+      </c>
+      <c r="AC11" s="1">
+        <v>1</v>
+      </c>
+      <c r="AD11" s="1">
+        <v>2</v>
+      </c>
+      <c r="AE11" s="1">
+        <v>2</v>
+      </c>
+      <c r="AF11" s="1">
+        <v>2</v>
+      </c>
+      <c r="AG11" s="1">
+        <v>2</v>
+      </c>
+      <c r="AH11" s="1">
+        <v>2</v>
+      </c>
+      <c r="AI11" s="1">
+        <v>2</v>
+      </c>
+      <c r="AJ11" s="1">
+        <v>2</v>
+      </c>
+      <c r="AK11" s="1">
+        <v>2</v>
+      </c>
+      <c r="AL11" s="1">
+        <v>1</v>
+      </c>
+      <c r="AM11" s="1">
+        <v>1</v>
+      </c>
+      <c r="AN11" s="1">
+        <v>1</v>
+      </c>
+      <c r="AO11" s="1">
+        <v>2</v>
+      </c>
+      <c r="AP11" s="1">
+        <v>2</v>
+      </c>
+      <c r="AQ11" s="1">
+        <v>2</v>
+      </c>
+      <c r="AR11" s="1">
+        <v>2</v>
+      </c>
+      <c r="AS11" s="1">
+        <v>2</v>
+      </c>
+      <c r="AT11" s="1">
+        <v>2</v>
+      </c>
+      <c r="AU11" s="1">
+        <v>2</v>
+      </c>
+      <c r="AV11" s="1">
+        <v>2</v>
+      </c>
+      <c r="AW11" s="1">
+        <v>2</v>
+      </c>
+      <c r="AX11" s="1">
+        <v>2</v>
+      </c>
+      <c r="AY11" s="1">
+        <v>2</v>
+      </c>
+      <c r="AZ11" s="1">
+        <v>2</v>
+      </c>
+      <c r="BA11" s="1">
+        <v>2</v>
+      </c>
+      <c r="BB11" s="1">
+        <v>2</v>
+      </c>
+      <c r="BC11" s="1">
+        <v>2</v>
+      </c>
+      <c r="BD11" s="1">
+        <v>2</v>
+      </c>
+      <c r="BE11" s="1">
+        <v>2</v>
+      </c>
+      <c r="BF11" s="1">
+        <v>2</v>
+      </c>
+      <c r="BG11" s="1">
+        <v>2</v>
+      </c>
+      <c r="BH11" s="1">
+        <v>2</v>
+      </c>
+      <c r="BI11" s="1">
+        <v>2</v>
+      </c>
+      <c r="BJ11" s="1">
+        <v>2</v>
+      </c>
+      <c r="BK11" s="1">
+        <v>2</v>
+      </c>
+      <c r="BL11" s="1">
         <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:64">
-      <c r="A12" s="3">
-        <v>1</v>
-      </c>
-      <c r="B12" s="3">
-        <v>1</v>
-      </c>
-      <c r="C12" s="3">
-        <v>1</v>
-      </c>
-      <c r="D12" s="3">
-        <v>1</v>
-      </c>
-      <c r="E12" s="3">
-        <v>1</v>
-      </c>
-      <c r="F12" s="3">
-        <v>1</v>
-      </c>
-      <c r="G12" s="3">
-        <v>1</v>
-      </c>
-      <c r="H12" s="3">
-        <v>1</v>
-      </c>
-      <c r="I12" s="3">
-        <v>1</v>
-      </c>
-      <c r="J12" s="3">
-        <v>1</v>
-      </c>
-      <c r="K12" s="3">
-        <v>1</v>
-      </c>
-      <c r="L12" s="3">
-        <v>1</v>
-      </c>
-      <c r="M12" s="3">
-        <v>1</v>
-      </c>
-      <c r="N12" s="3">
-        <v>1</v>
-      </c>
-      <c r="O12" s="3">
-        <v>1</v>
-      </c>
-      <c r="P12" s="3">
-        <v>1</v>
-      </c>
-      <c r="Q12" s="3">
-        <v>1</v>
-      </c>
-      <c r="R12" s="3">
-        <v>1</v>
-      </c>
-      <c r="S12" s="3">
-        <v>1</v>
-      </c>
-      <c r="T12" s="3">
-        <v>1</v>
-      </c>
-      <c r="U12" s="3">
-        <v>1</v>
-      </c>
-      <c r="V12" s="3">
-        <v>1</v>
-      </c>
-      <c r="W12" s="3">
-        <v>1</v>
-      </c>
-      <c r="X12" s="3">
-        <v>1</v>
-      </c>
-      <c r="Y12" s="3">
-        <v>1</v>
-      </c>
-      <c r="Z12" s="3">
-        <v>1</v>
-      </c>
-      <c r="AA12" s="3">
-        <v>1</v>
-      </c>
-      <c r="AB12" s="3">
-        <v>1</v>
-      </c>
-      <c r="AC12" s="3">
-        <v>1</v>
-      </c>
-      <c r="AD12" s="3">
-        <v>1</v>
-      </c>
-      <c r="AE12" s="3">
-        <v>1</v>
-      </c>
-      <c r="AF12" s="3">
-        <v>1</v>
-      </c>
-      <c r="AG12" s="3">
-        <v>1</v>
-      </c>
-      <c r="AH12" s="3">
-        <v>1</v>
-      </c>
-      <c r="AI12" s="3">
-        <v>1</v>
-      </c>
-      <c r="AJ12" s="3">
-        <v>1</v>
-      </c>
-      <c r="AK12" s="3">
-        <v>1</v>
-      </c>
-      <c r="AL12" s="3">
-        <v>1</v>
-      </c>
-      <c r="AM12" s="3">
-        <v>1</v>
-      </c>
-      <c r="AN12" s="3">
-        <v>1</v>
-      </c>
-      <c r="AO12" s="3">
-        <v>1</v>
-      </c>
-      <c r="AP12" s="3">
-        <v>1</v>
-      </c>
-      <c r="AQ12" s="3">
-        <v>1</v>
-      </c>
-      <c r="AR12" s="3">
-        <v>1</v>
-      </c>
-      <c r="AS12" s="3">
-        <v>1</v>
-      </c>
-      <c r="AT12" s="3">
-        <v>1</v>
-      </c>
-      <c r="AU12" s="3">
-        <v>1</v>
-      </c>
-      <c r="AV12" s="3">
-        <v>1</v>
-      </c>
-      <c r="AW12" s="3">
-        <v>1</v>
-      </c>
-      <c r="AX12" s="3">
-        <v>1</v>
-      </c>
-      <c r="AY12" s="3">
-        <v>1</v>
-      </c>
-      <c r="AZ12" s="3">
-        <v>1</v>
-      </c>
-      <c r="BA12" s="3">
-        <v>1</v>
-      </c>
-      <c r="BB12" s="3">
-        <v>1</v>
-      </c>
-      <c r="BC12" s="3">
-        <v>1</v>
-      </c>
-      <c r="BD12" s="3">
-        <v>1</v>
-      </c>
-      <c r="BE12" s="3">
-        <v>1</v>
-      </c>
-      <c r="BF12" s="3">
-        <v>1</v>
-      </c>
-      <c r="BG12" s="3">
-        <v>1</v>
-      </c>
-      <c r="BH12" s="3">
-        <v>1</v>
-      </c>
-      <c r="BI12" s="3">
-        <v>1</v>
-      </c>
-      <c r="BJ12" s="3">
-        <v>1</v>
-      </c>
-      <c r="BK12" s="3">
-        <v>1</v>
-      </c>
-      <c r="BL12" s="3">
+      <c r="A12" s="1">
+        <v>1</v>
+      </c>
+      <c r="B12" s="1">
+        <v>1</v>
+      </c>
+      <c r="C12" s="1">
+        <v>1</v>
+      </c>
+      <c r="D12" s="1">
+        <v>1</v>
+      </c>
+      <c r="E12" s="1">
+        <v>1</v>
+      </c>
+      <c r="F12" s="1">
+        <v>1</v>
+      </c>
+      <c r="G12" s="1">
+        <v>1</v>
+      </c>
+      <c r="H12" s="1">
+        <v>1</v>
+      </c>
+      <c r="I12" s="1">
+        <v>1</v>
+      </c>
+      <c r="J12" s="1">
+        <v>1</v>
+      </c>
+      <c r="K12" s="1">
+        <v>1</v>
+      </c>
+      <c r="L12" s="1">
+        <v>1</v>
+      </c>
+      <c r="M12" s="1">
+        <v>1</v>
+      </c>
+      <c r="N12" s="1">
+        <v>1</v>
+      </c>
+      <c r="O12" s="1">
+        <v>1</v>
+      </c>
+      <c r="P12" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q12" s="1">
+        <v>1</v>
+      </c>
+      <c r="R12" s="1">
+        <v>1</v>
+      </c>
+      <c r="S12" s="1">
+        <v>1</v>
+      </c>
+      <c r="T12" s="1">
+        <v>1</v>
+      </c>
+      <c r="U12" s="1">
+        <v>1</v>
+      </c>
+      <c r="V12" s="1">
+        <v>1</v>
+      </c>
+      <c r="W12" s="1">
+        <v>1</v>
+      </c>
+      <c r="X12" s="1">
+        <v>1</v>
+      </c>
+      <c r="Y12" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z12" s="1">
+        <v>1</v>
+      </c>
+      <c r="AA12" s="1">
+        <v>1</v>
+      </c>
+      <c r="AB12" s="1">
+        <v>1</v>
+      </c>
+      <c r="AC12" s="1">
+        <v>1</v>
+      </c>
+      <c r="AD12" s="1">
+        <v>1</v>
+      </c>
+      <c r="AE12" s="1">
+        <v>1</v>
+      </c>
+      <c r="AF12" s="1">
+        <v>1</v>
+      </c>
+      <c r="AG12" s="1">
+        <v>1</v>
+      </c>
+      <c r="AH12" s="1">
+        <v>1</v>
+      </c>
+      <c r="AI12" s="1">
+        <v>1</v>
+      </c>
+      <c r="AJ12" s="1">
+        <v>1</v>
+      </c>
+      <c r="AK12" s="1">
+        <v>1</v>
+      </c>
+      <c r="AL12" s="1">
+        <v>1</v>
+      </c>
+      <c r="AM12" s="1">
+        <v>1</v>
+      </c>
+      <c r="AN12" s="1">
+        <v>1</v>
+      </c>
+      <c r="AO12" s="1">
+        <v>1</v>
+      </c>
+      <c r="AP12" s="1">
+        <v>1</v>
+      </c>
+      <c r="AQ12" s="1">
+        <v>1</v>
+      </c>
+      <c r="AR12" s="1">
+        <v>1</v>
+      </c>
+      <c r="AS12" s="1">
+        <v>1</v>
+      </c>
+      <c r="AT12" s="1">
+        <v>1</v>
+      </c>
+      <c r="AU12" s="1">
+        <v>1</v>
+      </c>
+      <c r="AV12" s="1">
+        <v>1</v>
+      </c>
+      <c r="AW12" s="1">
+        <v>1</v>
+      </c>
+      <c r="AX12" s="1">
+        <v>1</v>
+      </c>
+      <c r="AY12" s="1">
+        <v>1</v>
+      </c>
+      <c r="AZ12" s="1">
+        <v>1</v>
+      </c>
+      <c r="BA12" s="1">
+        <v>1</v>
+      </c>
+      <c r="BB12" s="1">
+        <v>1</v>
+      </c>
+      <c r="BC12" s="1">
+        <v>1</v>
+      </c>
+      <c r="BD12" s="1">
+        <v>1</v>
+      </c>
+      <c r="BE12" s="1">
+        <v>1</v>
+      </c>
+      <c r="BF12" s="1">
+        <v>1</v>
+      </c>
+      <c r="BG12" s="1">
+        <v>1</v>
+      </c>
+      <c r="BH12" s="1">
+        <v>1</v>
+      </c>
+      <c r="BI12" s="1">
+        <v>1</v>
+      </c>
+      <c r="BJ12" s="1">
+        <v>1</v>
+      </c>
+      <c r="BK12" s="1">
+        <v>1</v>
+      </c>
+      <c r="BL12" s="1">
         <v>1</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
+  <conditionalFormatting sqref="A1:BL12">
+    <cfRule type="cellIs" dxfId="5" priority="1" operator="equal">
+      <formula>1</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="4" priority="2" operator="equal">
+      <formula>2</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8ECD2F2A-5FF6-491E-9BB3-D819CA18D9B7}">
-  <dimension ref="A1:AF12"/>
+  <dimension ref="A1:BL12"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="32" width="3.875" customWidth="1"/>
+    <col min="1" max="64" width="3.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32">
+    <row r="1" spans="1:64">
       <c r="A1">
         <v>0</v>
       </c>
@@ -5286,8 +5464,104 @@
       <c r="AF1">
         <v>0</v>
       </c>
+      <c r="AG1">
+        <v>0</v>
+      </c>
+      <c r="AH1">
+        <v>0</v>
+      </c>
+      <c r="AI1">
+        <v>0</v>
+      </c>
+      <c r="AJ1">
+        <v>0</v>
+      </c>
+      <c r="AK1">
+        <v>0</v>
+      </c>
+      <c r="AL1">
+        <v>0</v>
+      </c>
+      <c r="AM1">
+        <v>0</v>
+      </c>
+      <c r="AN1">
+        <v>0</v>
+      </c>
+      <c r="AO1">
+        <v>0</v>
+      </c>
+      <c r="AP1">
+        <v>0</v>
+      </c>
+      <c r="AQ1">
+        <v>0</v>
+      </c>
+      <c r="AR1">
+        <v>0</v>
+      </c>
+      <c r="AS1">
+        <v>0</v>
+      </c>
+      <c r="AT1">
+        <v>0</v>
+      </c>
+      <c r="AU1">
+        <v>0</v>
+      </c>
+      <c r="AV1">
+        <v>0</v>
+      </c>
+      <c r="AW1">
+        <v>0</v>
+      </c>
+      <c r="AX1">
+        <v>0</v>
+      </c>
+      <c r="AY1">
+        <v>0</v>
+      </c>
+      <c r="AZ1">
+        <v>0</v>
+      </c>
+      <c r="BA1">
+        <v>0</v>
+      </c>
+      <c r="BB1">
+        <v>0</v>
+      </c>
+      <c r="BC1">
+        <v>0</v>
+      </c>
+      <c r="BD1">
+        <v>0</v>
+      </c>
+      <c r="BE1">
+        <v>0</v>
+      </c>
+      <c r="BF1">
+        <v>0</v>
+      </c>
+      <c r="BG1">
+        <v>0</v>
+      </c>
+      <c r="BH1">
+        <v>0</v>
+      </c>
+      <c r="BI1">
+        <v>0</v>
+      </c>
+      <c r="BJ1">
+        <v>0</v>
+      </c>
+      <c r="BK1">
+        <v>0</v>
+      </c>
+      <c r="BL1">
+        <v>0</v>
+      </c>
     </row>
-    <row r="2" spans="1:32">
+    <row r="2" spans="1:64">
       <c r="A2">
         <v>0</v>
       </c>
@@ -5384,8 +5658,104 @@
       <c r="AF2">
         <v>0</v>
       </c>
+      <c r="AG2">
+        <v>0</v>
+      </c>
+      <c r="AH2">
+        <v>0</v>
+      </c>
+      <c r="AI2">
+        <v>0</v>
+      </c>
+      <c r="AJ2">
+        <v>0</v>
+      </c>
+      <c r="AK2">
+        <v>0</v>
+      </c>
+      <c r="AL2">
+        <v>0</v>
+      </c>
+      <c r="AM2">
+        <v>0</v>
+      </c>
+      <c r="AN2">
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <v>0</v>
+      </c>
+      <c r="AP2">
+        <v>0</v>
+      </c>
+      <c r="AQ2">
+        <v>0</v>
+      </c>
+      <c r="AR2">
+        <v>0</v>
+      </c>
+      <c r="AS2">
+        <v>0</v>
+      </c>
+      <c r="AT2">
+        <v>0</v>
+      </c>
+      <c r="AU2">
+        <v>0</v>
+      </c>
+      <c r="AV2">
+        <v>0</v>
+      </c>
+      <c r="AW2">
+        <v>0</v>
+      </c>
+      <c r="AX2">
+        <v>0</v>
+      </c>
+      <c r="AY2">
+        <v>0</v>
+      </c>
+      <c r="AZ2">
+        <v>0</v>
+      </c>
+      <c r="BA2">
+        <v>0</v>
+      </c>
+      <c r="BB2">
+        <v>0</v>
+      </c>
+      <c r="BC2">
+        <v>0</v>
+      </c>
+      <c r="BD2">
+        <v>0</v>
+      </c>
+      <c r="BE2">
+        <v>0</v>
+      </c>
+      <c r="BF2">
+        <v>0</v>
+      </c>
+      <c r="BG2">
+        <v>0</v>
+      </c>
+      <c r="BH2">
+        <v>0</v>
+      </c>
+      <c r="BI2">
+        <v>0</v>
+      </c>
+      <c r="BJ2">
+        <v>0</v>
+      </c>
+      <c r="BK2">
+        <v>0</v>
+      </c>
+      <c r="BL2">
+        <v>0</v>
+      </c>
     </row>
-    <row r="3" spans="1:32">
+    <row r="3" spans="1:64">
       <c r="A3">
         <v>0</v>
       </c>
@@ -5482,8 +5852,104 @@
       <c r="AF3">
         <v>0</v>
       </c>
+      <c r="AG3">
+        <v>0</v>
+      </c>
+      <c r="AH3">
+        <v>0</v>
+      </c>
+      <c r="AI3">
+        <v>0</v>
+      </c>
+      <c r="AJ3">
+        <v>0</v>
+      </c>
+      <c r="AK3">
+        <v>0</v>
+      </c>
+      <c r="AL3">
+        <v>0</v>
+      </c>
+      <c r="AM3">
+        <v>0</v>
+      </c>
+      <c r="AN3">
+        <v>0</v>
+      </c>
+      <c r="AO3">
+        <v>0</v>
+      </c>
+      <c r="AP3">
+        <v>0</v>
+      </c>
+      <c r="AQ3">
+        <v>0</v>
+      </c>
+      <c r="AR3">
+        <v>0</v>
+      </c>
+      <c r="AS3">
+        <v>0</v>
+      </c>
+      <c r="AT3">
+        <v>0</v>
+      </c>
+      <c r="AU3">
+        <v>0</v>
+      </c>
+      <c r="AV3">
+        <v>0</v>
+      </c>
+      <c r="AW3">
+        <v>0</v>
+      </c>
+      <c r="AX3">
+        <v>0</v>
+      </c>
+      <c r="AY3">
+        <v>0</v>
+      </c>
+      <c r="AZ3">
+        <v>0</v>
+      </c>
+      <c r="BA3">
+        <v>0</v>
+      </c>
+      <c r="BB3">
+        <v>0</v>
+      </c>
+      <c r="BC3">
+        <v>0</v>
+      </c>
+      <c r="BD3">
+        <v>0</v>
+      </c>
+      <c r="BE3">
+        <v>0</v>
+      </c>
+      <c r="BF3">
+        <v>0</v>
+      </c>
+      <c r="BG3">
+        <v>0</v>
+      </c>
+      <c r="BH3">
+        <v>0</v>
+      </c>
+      <c r="BI3">
+        <v>0</v>
+      </c>
+      <c r="BJ3">
+        <v>0</v>
+      </c>
+      <c r="BK3">
+        <v>0</v>
+      </c>
+      <c r="BL3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="4" spans="1:32">
+    <row r="4" spans="1:64">
       <c r="A4">
         <v>0</v>
       </c>
@@ -5580,8 +6046,104 @@
       <c r="AF4">
         <v>0</v>
       </c>
+      <c r="AG4">
+        <v>0</v>
+      </c>
+      <c r="AH4">
+        <v>0</v>
+      </c>
+      <c r="AI4">
+        <v>0</v>
+      </c>
+      <c r="AJ4">
+        <v>0</v>
+      </c>
+      <c r="AK4">
+        <v>0</v>
+      </c>
+      <c r="AL4">
+        <v>0</v>
+      </c>
+      <c r="AM4">
+        <v>0</v>
+      </c>
+      <c r="AN4">
+        <v>2</v>
+      </c>
+      <c r="AO4">
+        <v>2</v>
+      </c>
+      <c r="AP4">
+        <v>2</v>
+      </c>
+      <c r="AQ4">
+        <v>2</v>
+      </c>
+      <c r="AR4">
+        <v>0</v>
+      </c>
+      <c r="AS4">
+        <v>0</v>
+      </c>
+      <c r="AT4">
+        <v>0</v>
+      </c>
+      <c r="AU4">
+        <v>0</v>
+      </c>
+      <c r="AV4">
+        <v>0</v>
+      </c>
+      <c r="AW4">
+        <v>0</v>
+      </c>
+      <c r="AX4">
+        <v>0</v>
+      </c>
+      <c r="AY4">
+        <v>0</v>
+      </c>
+      <c r="AZ4">
+        <v>0</v>
+      </c>
+      <c r="BA4">
+        <v>0</v>
+      </c>
+      <c r="BB4">
+        <v>0</v>
+      </c>
+      <c r="BC4">
+        <v>0</v>
+      </c>
+      <c r="BD4">
+        <v>0</v>
+      </c>
+      <c r="BE4">
+        <v>0</v>
+      </c>
+      <c r="BF4">
+        <v>0</v>
+      </c>
+      <c r="BG4">
+        <v>0</v>
+      </c>
+      <c r="BH4">
+        <v>0</v>
+      </c>
+      <c r="BI4">
+        <v>0</v>
+      </c>
+      <c r="BJ4">
+        <v>0</v>
+      </c>
+      <c r="BK4">
+        <v>0</v>
+      </c>
+      <c r="BL4">
+        <v>0</v>
+      </c>
     </row>
-    <row r="5" spans="1:32">
+    <row r="5" spans="1:64">
       <c r="A5">
         <v>0</v>
       </c>
@@ -5678,8 +6240,104 @@
       <c r="AF5">
         <v>0</v>
       </c>
+      <c r="AG5">
+        <v>0</v>
+      </c>
+      <c r="AH5">
+        <v>0</v>
+      </c>
+      <c r="AI5">
+        <v>0</v>
+      </c>
+      <c r="AJ5">
+        <v>0</v>
+      </c>
+      <c r="AK5">
+        <v>0</v>
+      </c>
+      <c r="AL5">
+        <v>0</v>
+      </c>
+      <c r="AM5">
+        <v>2</v>
+      </c>
+      <c r="AN5">
+        <v>1</v>
+      </c>
+      <c r="AO5">
+        <v>1</v>
+      </c>
+      <c r="AP5">
+        <v>1</v>
+      </c>
+      <c r="AQ5">
+        <v>1</v>
+      </c>
+      <c r="AR5">
+        <v>2</v>
+      </c>
+      <c r="AS5">
+        <v>0</v>
+      </c>
+      <c r="AT5">
+        <v>0</v>
+      </c>
+      <c r="AU5">
+        <v>0</v>
+      </c>
+      <c r="AV5">
+        <v>0</v>
+      </c>
+      <c r="AW5">
+        <v>0</v>
+      </c>
+      <c r="AX5">
+        <v>0</v>
+      </c>
+      <c r="AY5">
+        <v>0</v>
+      </c>
+      <c r="AZ5">
+        <v>0</v>
+      </c>
+      <c r="BA5">
+        <v>0</v>
+      </c>
+      <c r="BB5">
+        <v>0</v>
+      </c>
+      <c r="BC5">
+        <v>0</v>
+      </c>
+      <c r="BD5">
+        <v>0</v>
+      </c>
+      <c r="BE5">
+        <v>0</v>
+      </c>
+      <c r="BF5">
+        <v>0</v>
+      </c>
+      <c r="BG5">
+        <v>0</v>
+      </c>
+      <c r="BH5">
+        <v>0</v>
+      </c>
+      <c r="BI5">
+        <v>0</v>
+      </c>
+      <c r="BJ5">
+        <v>0</v>
+      </c>
+      <c r="BK5">
+        <v>0</v>
+      </c>
+      <c r="BL5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="6" spans="1:32">
+    <row r="6" spans="1:64">
       <c r="A6">
         <v>0</v>
       </c>
@@ -5776,8 +6434,104 @@
       <c r="AF6">
         <v>0</v>
       </c>
+      <c r="AG6">
+        <v>0</v>
+      </c>
+      <c r="AH6">
+        <v>0</v>
+      </c>
+      <c r="AI6">
+        <v>0</v>
+      </c>
+      <c r="AJ6">
+        <v>0</v>
+      </c>
+      <c r="AK6">
+        <v>0</v>
+      </c>
+      <c r="AL6">
+        <v>2</v>
+      </c>
+      <c r="AM6">
+        <v>1</v>
+      </c>
+      <c r="AN6">
+        <v>1</v>
+      </c>
+      <c r="AO6">
+        <v>1</v>
+      </c>
+      <c r="AP6">
+        <v>1</v>
+      </c>
+      <c r="AQ6">
+        <v>1</v>
+      </c>
+      <c r="AR6">
+        <v>1</v>
+      </c>
+      <c r="AS6">
+        <v>0</v>
+      </c>
+      <c r="AT6">
+        <v>0</v>
+      </c>
+      <c r="AU6">
+        <v>0</v>
+      </c>
+      <c r="AV6">
+        <v>0</v>
+      </c>
+      <c r="AW6">
+        <v>0</v>
+      </c>
+      <c r="AX6">
+        <v>0</v>
+      </c>
+      <c r="AY6">
+        <v>0</v>
+      </c>
+      <c r="AZ6">
+        <v>0</v>
+      </c>
+      <c r="BA6">
+        <v>0</v>
+      </c>
+      <c r="BB6">
+        <v>0</v>
+      </c>
+      <c r="BC6">
+        <v>0</v>
+      </c>
+      <c r="BD6">
+        <v>0</v>
+      </c>
+      <c r="BE6">
+        <v>0</v>
+      </c>
+      <c r="BF6">
+        <v>0</v>
+      </c>
+      <c r="BG6">
+        <v>0</v>
+      </c>
+      <c r="BH6">
+        <v>0</v>
+      </c>
+      <c r="BI6">
+        <v>0</v>
+      </c>
+      <c r="BJ6">
+        <v>0</v>
+      </c>
+      <c r="BK6">
+        <v>0</v>
+      </c>
+      <c r="BL6">
+        <v>0</v>
+      </c>
     </row>
-    <row r="7" spans="1:32">
+    <row r="7" spans="1:64">
       <c r="A7">
         <v>0</v>
       </c>
@@ -5839,19 +6593,19 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -5874,8 +6628,104 @@
       <c r="AF7">
         <v>0</v>
       </c>
+      <c r="AG7">
+        <v>0</v>
+      </c>
+      <c r="AH7">
+        <v>0</v>
+      </c>
+      <c r="AI7">
+        <v>0</v>
+      </c>
+      <c r="AJ7">
+        <v>0</v>
+      </c>
+      <c r="AK7">
+        <v>0</v>
+      </c>
+      <c r="AL7">
+        <v>1</v>
+      </c>
+      <c r="AM7">
+        <v>1</v>
+      </c>
+      <c r="AN7">
+        <v>1</v>
+      </c>
+      <c r="AO7">
+        <v>1</v>
+      </c>
+      <c r="AP7">
+        <v>1</v>
+      </c>
+      <c r="AQ7">
+        <v>1</v>
+      </c>
+      <c r="AR7">
+        <v>1</v>
+      </c>
+      <c r="AS7">
+        <v>2</v>
+      </c>
+      <c r="AT7">
+        <v>0</v>
+      </c>
+      <c r="AU7">
+        <v>0</v>
+      </c>
+      <c r="AV7">
+        <v>0</v>
+      </c>
+      <c r="AW7">
+        <v>0</v>
+      </c>
+      <c r="AX7">
+        <v>0</v>
+      </c>
+      <c r="AY7">
+        <v>0</v>
+      </c>
+      <c r="AZ7">
+        <v>0</v>
+      </c>
+      <c r="BA7">
+        <v>0</v>
+      </c>
+      <c r="BB7">
+        <v>0</v>
+      </c>
+      <c r="BC7">
+        <v>0</v>
+      </c>
+      <c r="BD7">
+        <v>0</v>
+      </c>
+      <c r="BE7">
+        <v>0</v>
+      </c>
+      <c r="BF7">
+        <v>0</v>
+      </c>
+      <c r="BG7">
+        <v>0</v>
+      </c>
+      <c r="BH7">
+        <v>0</v>
+      </c>
+      <c r="BI7">
+        <v>0</v>
+      </c>
+      <c r="BJ7">
+        <v>0</v>
+      </c>
+      <c r="BK7">
+        <v>0</v>
+      </c>
+      <c r="BL7">
+        <v>0</v>
+      </c>
     </row>
-    <row r="8" spans="1:32">
+    <row r="8" spans="1:64">
       <c r="A8">
         <v>0</v>
       </c>
@@ -5972,8 +6822,104 @@
       <c r="AF8">
         <v>0</v>
       </c>
+      <c r="AG8">
+        <v>0</v>
+      </c>
+      <c r="AH8">
+        <v>0</v>
+      </c>
+      <c r="AI8">
+        <v>0</v>
+      </c>
+      <c r="AJ8">
+        <v>2</v>
+      </c>
+      <c r="AK8">
+        <v>2</v>
+      </c>
+      <c r="AL8">
+        <v>1</v>
+      </c>
+      <c r="AM8">
+        <v>1</v>
+      </c>
+      <c r="AN8">
+        <v>1</v>
+      </c>
+      <c r="AO8">
+        <v>1</v>
+      </c>
+      <c r="AP8">
+        <v>1</v>
+      </c>
+      <c r="AQ8">
+        <v>1</v>
+      </c>
+      <c r="AR8">
+        <v>1</v>
+      </c>
+      <c r="AS8">
+        <v>1</v>
+      </c>
+      <c r="AT8">
+        <v>2</v>
+      </c>
+      <c r="AU8">
+        <v>0</v>
+      </c>
+      <c r="AV8">
+        <v>0</v>
+      </c>
+      <c r="AW8">
+        <v>0</v>
+      </c>
+      <c r="AX8">
+        <v>0</v>
+      </c>
+      <c r="AY8">
+        <v>0</v>
+      </c>
+      <c r="AZ8">
+        <v>0</v>
+      </c>
+      <c r="BA8">
+        <v>0</v>
+      </c>
+      <c r="BB8">
+        <v>0</v>
+      </c>
+      <c r="BC8">
+        <v>0</v>
+      </c>
+      <c r="BD8">
+        <v>0</v>
+      </c>
+      <c r="BE8">
+        <v>0</v>
+      </c>
+      <c r="BF8">
+        <v>0</v>
+      </c>
+      <c r="BG8">
+        <v>0</v>
+      </c>
+      <c r="BH8">
+        <v>0</v>
+      </c>
+      <c r="BI8">
+        <v>0</v>
+      </c>
+      <c r="BJ8">
+        <v>0</v>
+      </c>
+      <c r="BK8">
+        <v>0</v>
+      </c>
+      <c r="BL8">
+        <v>0</v>
+      </c>
     </row>
-    <row r="9" spans="1:32">
+    <row r="9" spans="1:64">
       <c r="A9">
         <v>0</v>
       </c>
@@ -6070,8 +7016,104 @@
       <c r="AF9">
         <v>0</v>
       </c>
+      <c r="AG9">
+        <v>0</v>
+      </c>
+      <c r="AH9">
+        <v>0</v>
+      </c>
+      <c r="AI9">
+        <v>0</v>
+      </c>
+      <c r="AJ9">
+        <v>1</v>
+      </c>
+      <c r="AK9">
+        <v>1</v>
+      </c>
+      <c r="AL9">
+        <v>1</v>
+      </c>
+      <c r="AM9">
+        <v>1</v>
+      </c>
+      <c r="AN9">
+        <v>1</v>
+      </c>
+      <c r="AO9">
+        <v>1</v>
+      </c>
+      <c r="AP9">
+        <v>1</v>
+      </c>
+      <c r="AQ9">
+        <v>1</v>
+      </c>
+      <c r="AR9">
+        <v>1</v>
+      </c>
+      <c r="AS9">
+        <v>1</v>
+      </c>
+      <c r="AT9">
+        <v>1</v>
+      </c>
+      <c r="AU9">
+        <v>0</v>
+      </c>
+      <c r="AV9">
+        <v>0</v>
+      </c>
+      <c r="AW9">
+        <v>0</v>
+      </c>
+      <c r="AX9">
+        <v>0</v>
+      </c>
+      <c r="AY9">
+        <v>0</v>
+      </c>
+      <c r="AZ9">
+        <v>0</v>
+      </c>
+      <c r="BA9">
+        <v>0</v>
+      </c>
+      <c r="BB9">
+        <v>0</v>
+      </c>
+      <c r="BC9">
+        <v>0</v>
+      </c>
+      <c r="BD9">
+        <v>0</v>
+      </c>
+      <c r="BE9">
+        <v>0</v>
+      </c>
+      <c r="BF9">
+        <v>0</v>
+      </c>
+      <c r="BG9">
+        <v>0</v>
+      </c>
+      <c r="BH9">
+        <v>0</v>
+      </c>
+      <c r="BI9">
+        <v>0</v>
+      </c>
+      <c r="BJ9">
+        <v>0</v>
+      </c>
+      <c r="BK9">
+        <v>0</v>
+      </c>
+      <c r="BL9">
+        <v>0</v>
+      </c>
     </row>
-    <row r="10" spans="1:32">
+    <row r="10" spans="1:64">
       <c r="A10">
         <v>0</v>
       </c>
@@ -6168,8 +7210,104 @@
       <c r="AF10">
         <v>0</v>
       </c>
+      <c r="AG10">
+        <v>0</v>
+      </c>
+      <c r="AH10">
+        <v>0</v>
+      </c>
+      <c r="AI10">
+        <v>2</v>
+      </c>
+      <c r="AJ10">
+        <v>1</v>
+      </c>
+      <c r="AK10">
+        <v>1</v>
+      </c>
+      <c r="AL10">
+        <v>1</v>
+      </c>
+      <c r="AM10">
+        <v>1</v>
+      </c>
+      <c r="AN10">
+        <v>1</v>
+      </c>
+      <c r="AO10">
+        <v>1</v>
+      </c>
+      <c r="AP10">
+        <v>1</v>
+      </c>
+      <c r="AQ10">
+        <v>1</v>
+      </c>
+      <c r="AR10">
+        <v>1</v>
+      </c>
+      <c r="AS10">
+        <v>1</v>
+      </c>
+      <c r="AT10">
+        <v>1</v>
+      </c>
+      <c r="AU10">
+        <v>0</v>
+      </c>
+      <c r="AV10">
+        <v>0</v>
+      </c>
+      <c r="AW10">
+        <v>0</v>
+      </c>
+      <c r="AX10">
+        <v>0</v>
+      </c>
+      <c r="AY10">
+        <v>0</v>
+      </c>
+      <c r="AZ10">
+        <v>0</v>
+      </c>
+      <c r="BA10">
+        <v>0</v>
+      </c>
+      <c r="BB10">
+        <v>0</v>
+      </c>
+      <c r="BC10">
+        <v>0</v>
+      </c>
+      <c r="BD10">
+        <v>0</v>
+      </c>
+      <c r="BE10">
+        <v>0</v>
+      </c>
+      <c r="BF10">
+        <v>0</v>
+      </c>
+      <c r="BG10">
+        <v>0</v>
+      </c>
+      <c r="BH10">
+        <v>0</v>
+      </c>
+      <c r="BI10">
+        <v>0</v>
+      </c>
+      <c r="BJ10">
+        <v>0</v>
+      </c>
+      <c r="BK10">
+        <v>0</v>
+      </c>
+      <c r="BL10">
+        <v>0</v>
+      </c>
     </row>
-    <row r="11" spans="1:32">
+    <row r="11" spans="1:64">
       <c r="A11">
         <v>2</v>
       </c>
@@ -6228,46 +7366,142 @@
         <v>2</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF11">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="AG11">
+        <v>2</v>
+      </c>
+      <c r="AH11">
+        <v>2</v>
+      </c>
+      <c r="AI11">
+        <v>1</v>
+      </c>
+      <c r="AJ11">
+        <v>1</v>
+      </c>
+      <c r="AK11">
+        <v>1</v>
+      </c>
+      <c r="AL11">
+        <v>1</v>
+      </c>
+      <c r="AM11">
+        <v>1</v>
+      </c>
+      <c r="AN11">
+        <v>1</v>
+      </c>
+      <c r="AO11">
+        <v>1</v>
+      </c>
+      <c r="AP11">
+        <v>1</v>
+      </c>
+      <c r="AQ11">
+        <v>1</v>
+      </c>
+      <c r="AR11">
+        <v>1</v>
+      </c>
+      <c r="AS11">
+        <v>1</v>
+      </c>
+      <c r="AT11">
+        <v>1</v>
+      </c>
+      <c r="AU11">
+        <v>2</v>
+      </c>
+      <c r="AV11">
+        <v>2</v>
+      </c>
+      <c r="AW11">
+        <v>2</v>
+      </c>
+      <c r="AX11">
+        <v>2</v>
+      </c>
+      <c r="AY11">
+        <v>2</v>
+      </c>
+      <c r="AZ11">
+        <v>2</v>
+      </c>
+      <c r="BA11">
+        <v>2</v>
+      </c>
+      <c r="BB11">
+        <v>2</v>
+      </c>
+      <c r="BC11">
+        <v>2</v>
+      </c>
+      <c r="BD11">
+        <v>2</v>
+      </c>
+      <c r="BE11">
+        <v>2</v>
+      </c>
+      <c r="BF11">
+        <v>2</v>
+      </c>
+      <c r="BG11">
+        <v>2</v>
+      </c>
+      <c r="BH11">
+        <v>2</v>
+      </c>
+      <c r="BI11">
+        <v>2</v>
+      </c>
+      <c r="BJ11">
+        <v>2</v>
+      </c>
+      <c r="BK11">
+        <v>2</v>
+      </c>
+      <c r="BL11">
+        <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:32">
+    <row r="12" spans="1:64">
       <c r="A12">
         <v>1</v>
       </c>
@@ -6362,12 +7596,2458 @@
         <v>1</v>
       </c>
       <c r="AF12">
+        <v>1</v>
+      </c>
+      <c r="AG12">
+        <v>1</v>
+      </c>
+      <c r="AH12">
+        <v>1</v>
+      </c>
+      <c r="AI12">
+        <v>1</v>
+      </c>
+      <c r="AJ12">
+        <v>1</v>
+      </c>
+      <c r="AK12">
+        <v>1</v>
+      </c>
+      <c r="AL12">
+        <v>1</v>
+      </c>
+      <c r="AM12">
+        <v>1</v>
+      </c>
+      <c r="AN12">
+        <v>1</v>
+      </c>
+      <c r="AO12">
+        <v>1</v>
+      </c>
+      <c r="AP12">
+        <v>1</v>
+      </c>
+      <c r="AQ12">
+        <v>1</v>
+      </c>
+      <c r="AR12">
+        <v>1</v>
+      </c>
+      <c r="AS12">
+        <v>1</v>
+      </c>
+      <c r="AT12">
+        <v>1</v>
+      </c>
+      <c r="AU12">
+        <v>1</v>
+      </c>
+      <c r="AV12">
+        <v>1</v>
+      </c>
+      <c r="AW12">
+        <v>1</v>
+      </c>
+      <c r="AX12">
+        <v>1</v>
+      </c>
+      <c r="AY12">
+        <v>1</v>
+      </c>
+      <c r="AZ12">
+        <v>1</v>
+      </c>
+      <c r="BA12">
+        <v>1</v>
+      </c>
+      <c r="BB12">
+        <v>1</v>
+      </c>
+      <c r="BC12">
+        <v>1</v>
+      </c>
+      <c r="BD12">
+        <v>1</v>
+      </c>
+      <c r="BE12">
+        <v>1</v>
+      </c>
+      <c r="BF12">
+        <v>1</v>
+      </c>
+      <c r="BG12">
+        <v>1</v>
+      </c>
+      <c r="BH12">
+        <v>1</v>
+      </c>
+      <c r="BI12">
+        <v>1</v>
+      </c>
+      <c r="BJ12">
+        <v>1</v>
+      </c>
+      <c r="BK12">
+        <v>1</v>
+      </c>
+      <c r="BL12">
         <v>1</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
-  <conditionalFormatting sqref="A1:AF12">
+  <conditionalFormatting sqref="A1:BL12">
+    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
+      <formula>1</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
+      <formula>2</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A93122F1-E456-4803-98E9-BB8BF76DA44E}">
+  <dimension ref="A1:BL12"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
+  <cols>
+    <col min="1" max="64" width="3.875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:64">
+      <c r="A1">
+        <v>2</v>
+      </c>
+      <c r="B1">
+        <v>0</v>
+      </c>
+      <c r="C1">
+        <v>0</v>
+      </c>
+      <c r="D1">
+        <v>0</v>
+      </c>
+      <c r="E1">
+        <v>0</v>
+      </c>
+      <c r="F1">
+        <v>0</v>
+      </c>
+      <c r="G1">
+        <v>0</v>
+      </c>
+      <c r="H1">
+        <v>0</v>
+      </c>
+      <c r="I1">
+        <v>0</v>
+      </c>
+      <c r="J1">
+        <v>0</v>
+      </c>
+      <c r="K1">
+        <v>0</v>
+      </c>
+      <c r="L1">
+        <v>0</v>
+      </c>
+      <c r="M1">
+        <v>0</v>
+      </c>
+      <c r="N1">
+        <v>0</v>
+      </c>
+      <c r="O1">
+        <v>0</v>
+      </c>
+      <c r="P1">
+        <v>0</v>
+      </c>
+      <c r="Q1">
+        <v>0</v>
+      </c>
+      <c r="R1">
+        <v>0</v>
+      </c>
+      <c r="S1">
+        <v>0</v>
+      </c>
+      <c r="T1">
+        <v>0</v>
+      </c>
+      <c r="U1">
+        <v>0</v>
+      </c>
+      <c r="V1">
+        <v>0</v>
+      </c>
+      <c r="W1">
+        <v>0</v>
+      </c>
+      <c r="X1">
+        <v>0</v>
+      </c>
+      <c r="Y1">
+        <v>0</v>
+      </c>
+      <c r="Z1">
+        <v>0</v>
+      </c>
+      <c r="AA1">
+        <v>0</v>
+      </c>
+      <c r="AB1">
+        <v>0</v>
+      </c>
+      <c r="AC1">
+        <v>0</v>
+      </c>
+      <c r="AD1">
+        <v>0</v>
+      </c>
+      <c r="AE1">
+        <v>0</v>
+      </c>
+      <c r="AF1">
+        <v>0</v>
+      </c>
+      <c r="AG1">
+        <v>0</v>
+      </c>
+      <c r="AH1">
+        <v>0</v>
+      </c>
+      <c r="AI1">
+        <v>0</v>
+      </c>
+      <c r="AJ1">
+        <v>0</v>
+      </c>
+      <c r="AK1">
+        <v>0</v>
+      </c>
+      <c r="AL1">
+        <v>0</v>
+      </c>
+      <c r="AM1">
+        <v>0</v>
+      </c>
+      <c r="AN1">
+        <v>0</v>
+      </c>
+      <c r="AO1">
+        <v>0</v>
+      </c>
+      <c r="AP1">
+        <v>0</v>
+      </c>
+      <c r="AQ1">
+        <v>0</v>
+      </c>
+      <c r="AR1">
+        <v>0</v>
+      </c>
+      <c r="AS1">
+        <v>0</v>
+      </c>
+      <c r="AT1">
+        <v>0</v>
+      </c>
+      <c r="AU1">
+        <v>0</v>
+      </c>
+      <c r="AV1">
+        <v>0</v>
+      </c>
+      <c r="AW1">
+        <v>0</v>
+      </c>
+      <c r="AX1">
+        <v>0</v>
+      </c>
+      <c r="AY1">
+        <v>0</v>
+      </c>
+      <c r="AZ1">
+        <v>0</v>
+      </c>
+      <c r="BA1">
+        <v>0</v>
+      </c>
+      <c r="BB1">
+        <v>0</v>
+      </c>
+      <c r="BC1">
+        <v>0</v>
+      </c>
+      <c r="BD1">
+        <v>0</v>
+      </c>
+      <c r="BE1">
+        <v>0</v>
+      </c>
+      <c r="BF1">
+        <v>0</v>
+      </c>
+      <c r="BG1">
+        <v>0</v>
+      </c>
+      <c r="BH1">
+        <v>0</v>
+      </c>
+      <c r="BI1">
+        <v>0</v>
+      </c>
+      <c r="BJ1">
+        <v>0</v>
+      </c>
+      <c r="BK1">
+        <v>0</v>
+      </c>
+      <c r="BL1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:64">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>0</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2">
+        <v>0</v>
+      </c>
+      <c r="Q2">
+        <v>0</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0</v>
+      </c>
+      <c r="T2">
+        <v>0</v>
+      </c>
+      <c r="U2">
+        <v>0</v>
+      </c>
+      <c r="V2">
+        <v>0</v>
+      </c>
+      <c r="W2">
+        <v>0</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+      <c r="AA2">
+        <v>0</v>
+      </c>
+      <c r="AB2">
+        <v>0</v>
+      </c>
+      <c r="AC2">
+        <v>0</v>
+      </c>
+      <c r="AD2">
+        <v>0</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>0</v>
+      </c>
+      <c r="AG2">
+        <v>0</v>
+      </c>
+      <c r="AH2">
+        <v>0</v>
+      </c>
+      <c r="AI2">
+        <v>0</v>
+      </c>
+      <c r="AJ2">
+        <v>0</v>
+      </c>
+      <c r="AK2">
+        <v>0</v>
+      </c>
+      <c r="AL2">
+        <v>0</v>
+      </c>
+      <c r="AM2">
+        <v>0</v>
+      </c>
+      <c r="AN2">
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <v>0</v>
+      </c>
+      <c r="AP2">
+        <v>0</v>
+      </c>
+      <c r="AQ2">
+        <v>0</v>
+      </c>
+      <c r="AR2">
+        <v>0</v>
+      </c>
+      <c r="AS2">
+        <v>0</v>
+      </c>
+      <c r="AT2">
+        <v>0</v>
+      </c>
+      <c r="AU2">
+        <v>0</v>
+      </c>
+      <c r="AV2">
+        <v>0</v>
+      </c>
+      <c r="AW2">
+        <v>0</v>
+      </c>
+      <c r="AX2">
+        <v>0</v>
+      </c>
+      <c r="AY2">
+        <v>0</v>
+      </c>
+      <c r="AZ2">
+        <v>0</v>
+      </c>
+      <c r="BA2">
+        <v>0</v>
+      </c>
+      <c r="BB2">
+        <v>0</v>
+      </c>
+      <c r="BC2">
+        <v>0</v>
+      </c>
+      <c r="BD2">
+        <v>0</v>
+      </c>
+      <c r="BE2">
+        <v>0</v>
+      </c>
+      <c r="BF2">
+        <v>0</v>
+      </c>
+      <c r="BG2">
+        <v>0</v>
+      </c>
+      <c r="BH2">
+        <v>0</v>
+      </c>
+      <c r="BI2">
+        <v>0</v>
+      </c>
+      <c r="BJ2">
+        <v>0</v>
+      </c>
+      <c r="BK2">
+        <v>0</v>
+      </c>
+      <c r="BL2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:64">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>0</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <v>0</v>
+      </c>
+      <c r="Q3">
+        <v>0</v>
+      </c>
+      <c r="R3">
+        <v>0</v>
+      </c>
+      <c r="S3">
+        <v>0</v>
+      </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <v>0</v>
+      </c>
+      <c r="V3">
+        <v>0</v>
+      </c>
+      <c r="W3">
+        <v>0</v>
+      </c>
+      <c r="X3">
+        <v>0</v>
+      </c>
+      <c r="Y3">
+        <v>0</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+      <c r="AA3">
+        <v>0</v>
+      </c>
+      <c r="AB3">
+        <v>0</v>
+      </c>
+      <c r="AC3">
+        <v>0</v>
+      </c>
+      <c r="AD3">
+        <v>0</v>
+      </c>
+      <c r="AE3">
+        <v>0</v>
+      </c>
+      <c r="AF3">
+        <v>0</v>
+      </c>
+      <c r="AG3">
+        <v>0</v>
+      </c>
+      <c r="AH3">
+        <v>0</v>
+      </c>
+      <c r="AI3">
+        <v>0</v>
+      </c>
+      <c r="AJ3">
+        <v>0</v>
+      </c>
+      <c r="AK3">
+        <v>0</v>
+      </c>
+      <c r="AL3">
+        <v>0</v>
+      </c>
+      <c r="AM3">
+        <v>0</v>
+      </c>
+      <c r="AN3">
+        <v>0</v>
+      </c>
+      <c r="AO3">
+        <v>0</v>
+      </c>
+      <c r="AP3">
+        <v>0</v>
+      </c>
+      <c r="AQ3">
+        <v>0</v>
+      </c>
+      <c r="AR3">
+        <v>0</v>
+      </c>
+      <c r="AS3">
+        <v>0</v>
+      </c>
+      <c r="AT3">
+        <v>0</v>
+      </c>
+      <c r="AU3">
+        <v>0</v>
+      </c>
+      <c r="AV3">
+        <v>0</v>
+      </c>
+      <c r="AW3">
+        <v>0</v>
+      </c>
+      <c r="AX3">
+        <v>0</v>
+      </c>
+      <c r="AY3">
+        <v>0</v>
+      </c>
+      <c r="AZ3">
+        <v>0</v>
+      </c>
+      <c r="BA3">
+        <v>0</v>
+      </c>
+      <c r="BB3">
+        <v>0</v>
+      </c>
+      <c r="BC3">
+        <v>0</v>
+      </c>
+      <c r="BD3">
+        <v>0</v>
+      </c>
+      <c r="BE3">
+        <v>0</v>
+      </c>
+      <c r="BF3">
+        <v>0</v>
+      </c>
+      <c r="BG3">
+        <v>0</v>
+      </c>
+      <c r="BH3">
+        <v>0</v>
+      </c>
+      <c r="BI3">
+        <v>0</v>
+      </c>
+      <c r="BJ3">
+        <v>0</v>
+      </c>
+      <c r="BK3">
+        <v>0</v>
+      </c>
+      <c r="BL3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:64">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4">
+        <v>0</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>0</v>
+      </c>
+      <c r="Q4">
+        <v>0</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>0</v>
+      </c>
+      <c r="V4">
+        <v>0</v>
+      </c>
+      <c r="W4">
+        <v>0</v>
+      </c>
+      <c r="X4">
+        <v>0</v>
+      </c>
+      <c r="Y4">
+        <v>0</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+      <c r="AA4">
+        <v>0</v>
+      </c>
+      <c r="AB4">
+        <v>0</v>
+      </c>
+      <c r="AC4">
+        <v>0</v>
+      </c>
+      <c r="AD4">
+        <v>0</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>0</v>
+      </c>
+      <c r="AG4">
+        <v>0</v>
+      </c>
+      <c r="AH4">
+        <v>0</v>
+      </c>
+      <c r="AI4">
+        <v>0</v>
+      </c>
+      <c r="AJ4">
+        <v>0</v>
+      </c>
+      <c r="AK4">
+        <v>0</v>
+      </c>
+      <c r="AL4">
+        <v>0</v>
+      </c>
+      <c r="AM4">
+        <v>0</v>
+      </c>
+      <c r="AN4">
+        <v>0</v>
+      </c>
+      <c r="AO4">
+        <v>0</v>
+      </c>
+      <c r="AP4">
+        <v>0</v>
+      </c>
+      <c r="AQ4">
+        <v>0</v>
+      </c>
+      <c r="AR4">
+        <v>0</v>
+      </c>
+      <c r="AS4">
+        <v>0</v>
+      </c>
+      <c r="AT4">
+        <v>0</v>
+      </c>
+      <c r="AU4">
+        <v>0</v>
+      </c>
+      <c r="AV4">
+        <v>0</v>
+      </c>
+      <c r="AW4">
+        <v>0</v>
+      </c>
+      <c r="AX4">
+        <v>0</v>
+      </c>
+      <c r="AY4">
+        <v>0</v>
+      </c>
+      <c r="AZ4">
+        <v>0</v>
+      </c>
+      <c r="BA4">
+        <v>0</v>
+      </c>
+      <c r="BB4">
+        <v>0</v>
+      </c>
+      <c r="BC4">
+        <v>0</v>
+      </c>
+      <c r="BD4">
+        <v>0</v>
+      </c>
+      <c r="BE4">
+        <v>0</v>
+      </c>
+      <c r="BF4">
+        <v>0</v>
+      </c>
+      <c r="BG4">
+        <v>0</v>
+      </c>
+      <c r="BH4">
+        <v>0</v>
+      </c>
+      <c r="BI4">
+        <v>0</v>
+      </c>
+      <c r="BJ4">
+        <v>0</v>
+      </c>
+      <c r="BK4">
+        <v>0</v>
+      </c>
+      <c r="BL4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:64">
+      <c r="A5">
+        <v>1</v>
+      </c>
+      <c r="B5">
+        <v>0</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>0</v>
+      </c>
+      <c r="Q5">
+        <v>0</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>0</v>
+      </c>
+      <c r="V5">
+        <v>0</v>
+      </c>
+      <c r="W5">
+        <v>0</v>
+      </c>
+      <c r="X5">
+        <v>0</v>
+      </c>
+      <c r="Y5">
+        <v>0</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+      <c r="AA5">
+        <v>0</v>
+      </c>
+      <c r="AB5">
+        <v>0</v>
+      </c>
+      <c r="AC5">
+        <v>0</v>
+      </c>
+      <c r="AD5">
+        <v>0</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>0</v>
+      </c>
+      <c r="AG5">
+        <v>0</v>
+      </c>
+      <c r="AH5">
+        <v>0</v>
+      </c>
+      <c r="AI5">
+        <v>0</v>
+      </c>
+      <c r="AJ5">
+        <v>0</v>
+      </c>
+      <c r="AK5">
+        <v>0</v>
+      </c>
+      <c r="AL5">
+        <v>0</v>
+      </c>
+      <c r="AM5">
+        <v>0</v>
+      </c>
+      <c r="AN5">
+        <v>0</v>
+      </c>
+      <c r="AO5">
+        <v>0</v>
+      </c>
+      <c r="AP5">
+        <v>0</v>
+      </c>
+      <c r="AQ5">
+        <v>0</v>
+      </c>
+      <c r="AR5">
+        <v>0</v>
+      </c>
+      <c r="AS5">
+        <v>0</v>
+      </c>
+      <c r="AT5">
+        <v>0</v>
+      </c>
+      <c r="AU5">
+        <v>0</v>
+      </c>
+      <c r="AV5">
+        <v>0</v>
+      </c>
+      <c r="AW5">
+        <v>0</v>
+      </c>
+      <c r="AX5">
+        <v>0</v>
+      </c>
+      <c r="AY5">
+        <v>0</v>
+      </c>
+      <c r="AZ5">
+        <v>0</v>
+      </c>
+      <c r="BA5">
+        <v>0</v>
+      </c>
+      <c r="BB5">
+        <v>0</v>
+      </c>
+      <c r="BC5">
+        <v>0</v>
+      </c>
+      <c r="BD5">
+        <v>0</v>
+      </c>
+      <c r="BE5">
+        <v>0</v>
+      </c>
+      <c r="BF5">
+        <v>0</v>
+      </c>
+      <c r="BG5">
+        <v>0</v>
+      </c>
+      <c r="BH5">
+        <v>0</v>
+      </c>
+      <c r="BI5">
+        <v>0</v>
+      </c>
+      <c r="BJ5">
+        <v>0</v>
+      </c>
+      <c r="BK5">
+        <v>0</v>
+      </c>
+      <c r="BL5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:64">
+      <c r="A6">
+        <v>1</v>
+      </c>
+      <c r="B6">
+        <v>0</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>0</v>
+      </c>
+      <c r="Q6">
+        <v>0</v>
+      </c>
+      <c r="R6">
+        <v>0</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <v>0</v>
+      </c>
+      <c r="V6">
+        <v>0</v>
+      </c>
+      <c r="W6">
+        <v>0</v>
+      </c>
+      <c r="X6">
+        <v>0</v>
+      </c>
+      <c r="Y6">
+        <v>0</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+      <c r="AA6">
+        <v>0</v>
+      </c>
+      <c r="AB6">
+        <v>0</v>
+      </c>
+      <c r="AC6">
+        <v>0</v>
+      </c>
+      <c r="AD6">
+        <v>0</v>
+      </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
+      <c r="AF6">
+        <v>0</v>
+      </c>
+      <c r="AG6">
+        <v>0</v>
+      </c>
+      <c r="AH6">
+        <v>0</v>
+      </c>
+      <c r="AI6">
+        <v>0</v>
+      </c>
+      <c r="AJ6">
+        <v>0</v>
+      </c>
+      <c r="AK6">
+        <v>0</v>
+      </c>
+      <c r="AL6">
+        <v>0</v>
+      </c>
+      <c r="AM6">
+        <v>0</v>
+      </c>
+      <c r="AN6">
+        <v>0</v>
+      </c>
+      <c r="AO6">
+        <v>0</v>
+      </c>
+      <c r="AP6">
+        <v>0</v>
+      </c>
+      <c r="AQ6">
+        <v>0</v>
+      </c>
+      <c r="AR6">
+        <v>0</v>
+      </c>
+      <c r="AS6">
+        <v>0</v>
+      </c>
+      <c r="AT6">
+        <v>0</v>
+      </c>
+      <c r="AU6">
+        <v>0</v>
+      </c>
+      <c r="AV6">
+        <v>0</v>
+      </c>
+      <c r="AW6">
+        <v>0</v>
+      </c>
+      <c r="AX6">
+        <v>0</v>
+      </c>
+      <c r="AY6">
+        <v>0</v>
+      </c>
+      <c r="AZ6">
+        <v>0</v>
+      </c>
+      <c r="BA6">
+        <v>0</v>
+      </c>
+      <c r="BB6">
+        <v>0</v>
+      </c>
+      <c r="BC6">
+        <v>0</v>
+      </c>
+      <c r="BD6">
+        <v>0</v>
+      </c>
+      <c r="BE6">
+        <v>0</v>
+      </c>
+      <c r="BF6">
+        <v>0</v>
+      </c>
+      <c r="BG6">
+        <v>0</v>
+      </c>
+      <c r="BH6">
+        <v>0</v>
+      </c>
+      <c r="BI6">
+        <v>0</v>
+      </c>
+      <c r="BJ6">
+        <v>0</v>
+      </c>
+      <c r="BK6">
+        <v>0</v>
+      </c>
+      <c r="BL6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:64">
+      <c r="A7">
+        <v>1</v>
+      </c>
+      <c r="B7">
+        <v>0</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>0</v>
+      </c>
+      <c r="Q7">
+        <v>0</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <v>0</v>
+      </c>
+      <c r="V7">
+        <v>0</v>
+      </c>
+      <c r="W7">
+        <v>0</v>
+      </c>
+      <c r="X7">
+        <v>0</v>
+      </c>
+      <c r="Y7">
+        <v>0</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+      <c r="AA7">
+        <v>0</v>
+      </c>
+      <c r="AB7">
+        <v>0</v>
+      </c>
+      <c r="AC7">
+        <v>0</v>
+      </c>
+      <c r="AD7">
+        <v>0</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
+      <c r="AF7">
+        <v>0</v>
+      </c>
+      <c r="AG7">
+        <v>0</v>
+      </c>
+      <c r="AH7">
+        <v>0</v>
+      </c>
+      <c r="AI7">
+        <v>0</v>
+      </c>
+      <c r="AJ7">
+        <v>0</v>
+      </c>
+      <c r="AK7">
+        <v>0</v>
+      </c>
+      <c r="AL7">
+        <v>0</v>
+      </c>
+      <c r="AM7">
+        <v>0</v>
+      </c>
+      <c r="AN7">
+        <v>0</v>
+      </c>
+      <c r="AO7">
+        <v>0</v>
+      </c>
+      <c r="AP7">
+        <v>0</v>
+      </c>
+      <c r="AQ7">
+        <v>0</v>
+      </c>
+      <c r="AR7">
+        <v>0</v>
+      </c>
+      <c r="AS7">
+        <v>0</v>
+      </c>
+      <c r="AT7">
+        <v>0</v>
+      </c>
+      <c r="AU7">
+        <v>0</v>
+      </c>
+      <c r="AV7">
+        <v>0</v>
+      </c>
+      <c r="AW7">
+        <v>0</v>
+      </c>
+      <c r="AX7">
+        <v>0</v>
+      </c>
+      <c r="AY7">
+        <v>0</v>
+      </c>
+      <c r="AZ7">
+        <v>0</v>
+      </c>
+      <c r="BA7">
+        <v>0</v>
+      </c>
+      <c r="BB7">
+        <v>0</v>
+      </c>
+      <c r="BC7">
+        <v>0</v>
+      </c>
+      <c r="BD7">
+        <v>0</v>
+      </c>
+      <c r="BE7">
+        <v>0</v>
+      </c>
+      <c r="BF7">
+        <v>0</v>
+      </c>
+      <c r="BG7">
+        <v>0</v>
+      </c>
+      <c r="BH7">
+        <v>0</v>
+      </c>
+      <c r="BI7">
+        <v>0</v>
+      </c>
+      <c r="BJ7">
+        <v>0</v>
+      </c>
+      <c r="BK7">
+        <v>0</v>
+      </c>
+      <c r="BL7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:64">
+      <c r="A8">
+        <v>1</v>
+      </c>
+      <c r="B8">
+        <v>0</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>2</v>
+      </c>
+      <c r="N8">
+        <v>2</v>
+      </c>
+      <c r="O8">
+        <v>2</v>
+      </c>
+      <c r="P8">
+        <v>0</v>
+      </c>
+      <c r="Q8">
+        <v>0</v>
+      </c>
+      <c r="R8">
+        <v>0</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <v>0</v>
+      </c>
+      <c r="V8">
+        <v>0</v>
+      </c>
+      <c r="W8">
+        <v>0</v>
+      </c>
+      <c r="X8">
+        <v>0</v>
+      </c>
+      <c r="Y8">
+        <v>0</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+      <c r="AA8">
+        <v>0</v>
+      </c>
+      <c r="AB8">
+        <v>0</v>
+      </c>
+      <c r="AC8">
+        <v>0</v>
+      </c>
+      <c r="AD8">
+        <v>0</v>
+      </c>
+      <c r="AE8">
+        <v>0</v>
+      </c>
+      <c r="AF8">
+        <v>0</v>
+      </c>
+      <c r="AG8">
+        <v>0</v>
+      </c>
+      <c r="AH8">
+        <v>0</v>
+      </c>
+      <c r="AI8">
+        <v>0</v>
+      </c>
+      <c r="AJ8">
+        <v>0</v>
+      </c>
+      <c r="AK8">
+        <v>0</v>
+      </c>
+      <c r="AL8">
+        <v>0</v>
+      </c>
+      <c r="AM8">
+        <v>0</v>
+      </c>
+      <c r="AN8">
+        <v>0</v>
+      </c>
+      <c r="AO8">
+        <v>0</v>
+      </c>
+      <c r="AP8">
+        <v>0</v>
+      </c>
+      <c r="AQ8">
+        <v>0</v>
+      </c>
+      <c r="AR8">
+        <v>0</v>
+      </c>
+      <c r="AS8">
+        <v>0</v>
+      </c>
+      <c r="AT8">
+        <v>0</v>
+      </c>
+      <c r="AU8">
+        <v>0</v>
+      </c>
+      <c r="AV8">
+        <v>0</v>
+      </c>
+      <c r="AW8">
+        <v>0</v>
+      </c>
+      <c r="AX8">
+        <v>0</v>
+      </c>
+      <c r="AY8">
+        <v>0</v>
+      </c>
+      <c r="AZ8">
+        <v>0</v>
+      </c>
+      <c r="BA8">
+        <v>0</v>
+      </c>
+      <c r="BB8">
+        <v>0</v>
+      </c>
+      <c r="BC8">
+        <v>0</v>
+      </c>
+      <c r="BD8">
+        <v>0</v>
+      </c>
+      <c r="BE8">
+        <v>0</v>
+      </c>
+      <c r="BF8">
+        <v>0</v>
+      </c>
+      <c r="BG8">
+        <v>0</v>
+      </c>
+      <c r="BH8">
+        <v>0</v>
+      </c>
+      <c r="BI8">
+        <v>0</v>
+      </c>
+      <c r="BJ8">
+        <v>0</v>
+      </c>
+      <c r="BK8">
+        <v>0</v>
+      </c>
+      <c r="BL8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:64">
+      <c r="A9">
+        <v>1</v>
+      </c>
+      <c r="B9">
+        <v>2</v>
+      </c>
+      <c r="C9">
+        <v>2</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>2</v>
+      </c>
+      <c r="I9">
+        <v>2</v>
+      </c>
+      <c r="J9">
+        <v>2</v>
+      </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9">
+        <v>0</v>
+      </c>
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9">
+        <v>0</v>
+      </c>
+      <c r="Q9">
+        <v>0</v>
+      </c>
+      <c r="R9">
+        <v>0</v>
+      </c>
+      <c r="S9">
+        <v>0</v>
+      </c>
+      <c r="T9">
+        <v>0</v>
+      </c>
+      <c r="U9">
+        <v>0</v>
+      </c>
+      <c r="V9">
+        <v>0</v>
+      </c>
+      <c r="W9">
+        <v>0</v>
+      </c>
+      <c r="X9">
+        <v>0</v>
+      </c>
+      <c r="Y9">
+        <v>0</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+      <c r="AA9">
+        <v>0</v>
+      </c>
+      <c r="AB9">
+        <v>0</v>
+      </c>
+      <c r="AC9">
+        <v>0</v>
+      </c>
+      <c r="AD9">
+        <v>0</v>
+      </c>
+      <c r="AE9">
+        <v>0</v>
+      </c>
+      <c r="AF9">
+        <v>0</v>
+      </c>
+      <c r="AG9">
+        <v>0</v>
+      </c>
+      <c r="AH9">
+        <v>0</v>
+      </c>
+      <c r="AI9">
+        <v>0</v>
+      </c>
+      <c r="AJ9">
+        <v>0</v>
+      </c>
+      <c r="AK9">
+        <v>0</v>
+      </c>
+      <c r="AL9">
+        <v>0</v>
+      </c>
+      <c r="AM9">
+        <v>0</v>
+      </c>
+      <c r="AN9">
+        <v>0</v>
+      </c>
+      <c r="AO9">
+        <v>0</v>
+      </c>
+      <c r="AP9">
+        <v>0</v>
+      </c>
+      <c r="AQ9">
+        <v>0</v>
+      </c>
+      <c r="AR9">
+        <v>0</v>
+      </c>
+      <c r="AS9">
+        <v>0</v>
+      </c>
+      <c r="AT9">
+        <v>0</v>
+      </c>
+      <c r="AU9">
+        <v>0</v>
+      </c>
+      <c r="AV9">
+        <v>0</v>
+      </c>
+      <c r="AW9">
+        <v>0</v>
+      </c>
+      <c r="AX9">
+        <v>0</v>
+      </c>
+      <c r="AY9">
+        <v>0</v>
+      </c>
+      <c r="AZ9">
+        <v>0</v>
+      </c>
+      <c r="BA9">
+        <v>0</v>
+      </c>
+      <c r="BB9">
+        <v>0</v>
+      </c>
+      <c r="BC9">
+        <v>0</v>
+      </c>
+      <c r="BD9">
+        <v>0</v>
+      </c>
+      <c r="BE9">
+        <v>0</v>
+      </c>
+      <c r="BF9">
+        <v>0</v>
+      </c>
+      <c r="BG9">
+        <v>0</v>
+      </c>
+      <c r="BH9">
+        <v>0</v>
+      </c>
+      <c r="BI9">
+        <v>0</v>
+      </c>
+      <c r="BJ9">
+        <v>0</v>
+      </c>
+      <c r="BK9">
+        <v>0</v>
+      </c>
+      <c r="BL9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:64">
+      <c r="A10">
+        <v>1</v>
+      </c>
+      <c r="B10">
+        <v>0</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>1</v>
+      </c>
+      <c r="I10">
+        <v>1</v>
+      </c>
+      <c r="J10">
+        <v>1</v>
+      </c>
+      <c r="K10">
+        <v>0</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10">
+        <v>0</v>
+      </c>
+      <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="P10">
+        <v>0</v>
+      </c>
+      <c r="Q10">
+        <v>0</v>
+      </c>
+      <c r="R10">
+        <v>0</v>
+      </c>
+      <c r="S10">
+        <v>0</v>
+      </c>
+      <c r="T10">
+        <v>0</v>
+      </c>
+      <c r="U10">
+        <v>0</v>
+      </c>
+      <c r="V10">
+        <v>0</v>
+      </c>
+      <c r="W10">
+        <v>0</v>
+      </c>
+      <c r="X10">
+        <v>0</v>
+      </c>
+      <c r="Y10">
+        <v>0</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+      <c r="AA10">
+        <v>0</v>
+      </c>
+      <c r="AB10">
+        <v>0</v>
+      </c>
+      <c r="AC10">
+        <v>0</v>
+      </c>
+      <c r="AD10">
+        <v>0</v>
+      </c>
+      <c r="AE10">
+        <v>0</v>
+      </c>
+      <c r="AF10">
+        <v>0</v>
+      </c>
+      <c r="AG10">
+        <v>0</v>
+      </c>
+      <c r="AH10">
+        <v>0</v>
+      </c>
+      <c r="AI10">
+        <v>0</v>
+      </c>
+      <c r="AJ10">
+        <v>0</v>
+      </c>
+      <c r="AK10">
+        <v>0</v>
+      </c>
+      <c r="AL10">
+        <v>0</v>
+      </c>
+      <c r="AM10">
+        <v>0</v>
+      </c>
+      <c r="AN10">
+        <v>0</v>
+      </c>
+      <c r="AO10">
+        <v>0</v>
+      </c>
+      <c r="AP10">
+        <v>0</v>
+      </c>
+      <c r="AQ10">
+        <v>0</v>
+      </c>
+      <c r="AR10">
+        <v>0</v>
+      </c>
+      <c r="AS10">
+        <v>0</v>
+      </c>
+      <c r="AT10">
+        <v>0</v>
+      </c>
+      <c r="AU10">
+        <v>0</v>
+      </c>
+      <c r="AV10">
+        <v>0</v>
+      </c>
+      <c r="AW10">
+        <v>0</v>
+      </c>
+      <c r="AX10">
+        <v>0</v>
+      </c>
+      <c r="AY10">
+        <v>0</v>
+      </c>
+      <c r="AZ10">
+        <v>0</v>
+      </c>
+      <c r="BA10">
+        <v>0</v>
+      </c>
+      <c r="BB10">
+        <v>0</v>
+      </c>
+      <c r="BC10">
+        <v>0</v>
+      </c>
+      <c r="BD10">
+        <v>0</v>
+      </c>
+      <c r="BE10">
+        <v>0</v>
+      </c>
+      <c r="BF10">
+        <v>0</v>
+      </c>
+      <c r="BG10">
+        <v>0</v>
+      </c>
+      <c r="BH10">
+        <v>0</v>
+      </c>
+      <c r="BI10">
+        <v>0</v>
+      </c>
+      <c r="BJ10">
+        <v>0</v>
+      </c>
+      <c r="BK10">
+        <v>0</v>
+      </c>
+      <c r="BL10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:64">
+      <c r="A11">
+        <v>1</v>
+      </c>
+      <c r="B11">
+        <v>0</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>1</v>
+      </c>
+      <c r="I11">
+        <v>1</v>
+      </c>
+      <c r="J11">
+        <v>1</v>
+      </c>
+      <c r="K11">
+        <v>2</v>
+      </c>
+      <c r="L11">
+        <v>2</v>
+      </c>
+      <c r="M11">
+        <v>2</v>
+      </c>
+      <c r="N11">
+        <v>2</v>
+      </c>
+      <c r="O11">
+        <v>2</v>
+      </c>
+      <c r="P11">
+        <v>2</v>
+      </c>
+      <c r="Q11">
+        <v>2</v>
+      </c>
+      <c r="R11">
+        <v>2</v>
+      </c>
+      <c r="S11">
+        <v>2</v>
+      </c>
+      <c r="T11">
+        <v>2</v>
+      </c>
+      <c r="U11">
+        <v>2</v>
+      </c>
+      <c r="V11">
+        <v>2</v>
+      </c>
+      <c r="W11">
+        <v>2</v>
+      </c>
+      <c r="X11">
+        <v>2</v>
+      </c>
+      <c r="Y11">
+        <v>2</v>
+      </c>
+      <c r="Z11">
+        <v>2</v>
+      </c>
+      <c r="AA11">
+        <v>2</v>
+      </c>
+      <c r="AB11">
+        <v>2</v>
+      </c>
+      <c r="AC11">
+        <v>2</v>
+      </c>
+      <c r="AD11">
+        <v>2</v>
+      </c>
+      <c r="AE11">
+        <v>2</v>
+      </c>
+      <c r="AF11">
+        <v>2</v>
+      </c>
+      <c r="AG11">
+        <v>2</v>
+      </c>
+      <c r="AH11">
+        <v>2</v>
+      </c>
+      <c r="AI11">
+        <v>2</v>
+      </c>
+      <c r="AJ11">
+        <v>2</v>
+      </c>
+      <c r="AK11">
+        <v>2</v>
+      </c>
+      <c r="AL11">
+        <v>2</v>
+      </c>
+      <c r="AM11">
+        <v>2</v>
+      </c>
+      <c r="AN11">
+        <v>2</v>
+      </c>
+      <c r="AO11">
+        <v>2</v>
+      </c>
+      <c r="AP11">
+        <v>2</v>
+      </c>
+      <c r="AQ11">
+        <v>2</v>
+      </c>
+      <c r="AR11">
+        <v>2</v>
+      </c>
+      <c r="AS11">
+        <v>2</v>
+      </c>
+      <c r="AT11">
+        <v>2</v>
+      </c>
+      <c r="AU11">
+        <v>2</v>
+      </c>
+      <c r="AV11">
+        <v>2</v>
+      </c>
+      <c r="AW11">
+        <v>2</v>
+      </c>
+      <c r="AX11">
+        <v>2</v>
+      </c>
+      <c r="AY11">
+        <v>2</v>
+      </c>
+      <c r="AZ11">
+        <v>2</v>
+      </c>
+      <c r="BA11">
+        <v>2</v>
+      </c>
+      <c r="BB11">
+        <v>2</v>
+      </c>
+      <c r="BC11">
+        <v>2</v>
+      </c>
+      <c r="BD11">
+        <v>2</v>
+      </c>
+      <c r="BE11">
+        <v>2</v>
+      </c>
+      <c r="BF11">
+        <v>2</v>
+      </c>
+      <c r="BG11">
+        <v>2</v>
+      </c>
+      <c r="BH11">
+        <v>2</v>
+      </c>
+      <c r="BI11">
+        <v>2</v>
+      </c>
+      <c r="BJ11">
+        <v>2</v>
+      </c>
+      <c r="BK11">
+        <v>2</v>
+      </c>
+      <c r="BL11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:64">
+      <c r="A12">
+        <v>1</v>
+      </c>
+      <c r="B12">
+        <v>0</v>
+      </c>
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>1</v>
+      </c>
+      <c r="I12">
+        <v>1</v>
+      </c>
+      <c r="J12">
+        <v>1</v>
+      </c>
+      <c r="K12">
+        <v>1</v>
+      </c>
+      <c r="L12">
+        <v>1</v>
+      </c>
+      <c r="M12">
+        <v>1</v>
+      </c>
+      <c r="N12">
+        <v>1</v>
+      </c>
+      <c r="O12">
+        <v>1</v>
+      </c>
+      <c r="P12">
+        <v>1</v>
+      </c>
+      <c r="Q12">
+        <v>1</v>
+      </c>
+      <c r="R12">
+        <v>1</v>
+      </c>
+      <c r="S12">
+        <v>1</v>
+      </c>
+      <c r="T12">
+        <v>1</v>
+      </c>
+      <c r="U12">
+        <v>1</v>
+      </c>
+      <c r="V12">
+        <v>1</v>
+      </c>
+      <c r="W12">
+        <v>1</v>
+      </c>
+      <c r="X12">
+        <v>1</v>
+      </c>
+      <c r="Y12">
+        <v>1</v>
+      </c>
+      <c r="Z12">
+        <v>1</v>
+      </c>
+      <c r="AA12">
+        <v>1</v>
+      </c>
+      <c r="AB12">
+        <v>1</v>
+      </c>
+      <c r="AC12">
+        <v>1</v>
+      </c>
+      <c r="AD12">
+        <v>1</v>
+      </c>
+      <c r="AE12">
+        <v>1</v>
+      </c>
+      <c r="AF12">
+        <v>1</v>
+      </c>
+      <c r="AG12">
+        <v>1</v>
+      </c>
+      <c r="AH12">
+        <v>1</v>
+      </c>
+      <c r="AI12">
+        <v>1</v>
+      </c>
+      <c r="AJ12">
+        <v>1</v>
+      </c>
+      <c r="AK12">
+        <v>1</v>
+      </c>
+      <c r="AL12">
+        <v>1</v>
+      </c>
+      <c r="AM12">
+        <v>1</v>
+      </c>
+      <c r="AN12">
+        <v>1</v>
+      </c>
+      <c r="AO12">
+        <v>1</v>
+      </c>
+      <c r="AP12">
+        <v>1</v>
+      </c>
+      <c r="AQ12">
+        <v>1</v>
+      </c>
+      <c r="AR12">
+        <v>1</v>
+      </c>
+      <c r="AS12">
+        <v>1</v>
+      </c>
+      <c r="AT12">
+        <v>1</v>
+      </c>
+      <c r="AU12">
+        <v>1</v>
+      </c>
+      <c r="AV12">
+        <v>1</v>
+      </c>
+      <c r="AW12">
+        <v>1</v>
+      </c>
+      <c r="AX12">
+        <v>1</v>
+      </c>
+      <c r="AY12">
+        <v>1</v>
+      </c>
+      <c r="AZ12">
+        <v>1</v>
+      </c>
+      <c r="BA12">
+        <v>1</v>
+      </c>
+      <c r="BB12">
+        <v>1</v>
+      </c>
+      <c r="BC12">
+        <v>1</v>
+      </c>
+      <c r="BD12">
+        <v>1</v>
+      </c>
+      <c r="BE12">
+        <v>1</v>
+      </c>
+      <c r="BF12">
+        <v>1</v>
+      </c>
+      <c r="BG12">
+        <v>1</v>
+      </c>
+      <c r="BH12">
+        <v>1</v>
+      </c>
+      <c r="BI12">
+        <v>1</v>
+      </c>
+      <c r="BJ12">
+        <v>1</v>
+      </c>
+      <c r="BK12">
+        <v>1</v>
+      </c>
+      <c r="BL12">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <conditionalFormatting sqref="A1:BL12">
     <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
       <formula>1</formula>
     </cfRule>

--- a/Src/Map/MapData/Map.xlsx
+++ b/Src/Map/MapData/Map.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ゲーム開発1\チーム確認用\Src\Map\MapData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jeffr\Desktop\kobedenshi\1年\quartet\スケルトンプログラム\Src\Map\MapData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0E3319B-04C3-4725-AF24-9FCEDF5D959A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{463AA7F8-B8A3-4A72-9211-9705A60E7793}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11295" activeTab="3" xr2:uid="{53B5AEAB-04AE-4965-81BC-49E785C84905}"/>
+    <workbookView xWindow="3380" yWindow="3380" windowWidth="19200" windowHeight="11170" activeTab="3" xr2:uid="{53B5AEAB-04AE-4965-81BC-49E785C84905}"/>
   </bookViews>
   <sheets>
     <sheet name="SelectStage(Stage0)" sheetId="3" r:id="rId1"/>
@@ -47,14 +47,14 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="游ゴシック"/>
+      <name val="新細明體"/>
       <family val="2"/>
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="6"/>
-      <name val="游ゴシック"/>
+      <name val="新細明體"/>
       <family val="2"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -62,14 +62,14 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="游ゴシック"/>
+      <name val="新細明體"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <name val="游ゴシック"/>
+      <name val="新細明體"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -127,7 +127,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="一般" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="10">
     <dxf>
@@ -338,7 +338,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 佈景主題">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -655,9 +655,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4282726-38FC-445F-8486-AD0C629F4764}">
   <dimension ref="A1:BL12"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="81" width="3.875" customWidth="1"/>
+    <col min="1" max="81" width="3.8984375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:64">
@@ -3012,9 +3012,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF26DA9C-D84B-469D-BB4C-3116DB6599CB}">
   <dimension ref="A1:BL12"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="64" width="3.875" customWidth="1"/>
+    <col min="1" max="64" width="3.8984375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:64">
@@ -5362,9 +5362,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8ECD2F2A-5FF6-491E-9BB3-D819CA18D9B7}">
   <dimension ref="A1:BL12"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="64" width="3.875" customWidth="1"/>
+    <col min="1" max="64" width="3.8984375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:64">
@@ -7712,9 +7712,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A93122F1-E456-4803-98E9-BB8BF76DA44E}">
   <dimension ref="A1:BL12"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="64" width="3.875" customWidth="1"/>
+    <col min="1" max="64" width="3.8984375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:64">
@@ -9274,10 +9274,10 @@
         <v>1</v>
       </c>
       <c r="B9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D9">
         <v>0</v>
@@ -9292,13 +9292,13 @@
         <v>0</v>
       </c>
       <c r="H9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K9">
         <v>0</v>
@@ -9468,31 +9468,31 @@
         <v>1</v>
       </c>
       <c r="B10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K10">
         <v>0</v>
@@ -9662,22 +9662,22 @@
         <v>1</v>
       </c>
       <c r="B11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11">
         <v>1</v>
@@ -9856,22 +9856,22 @@
         <v>1</v>
       </c>
       <c r="B12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H12">
         <v>1</v>
